--- a/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="1145">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">55</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">Taunt</t>
@@ -240,6 +240,21 @@
   </si>
   <si>
     <t xml:space="preserve">#1は勇ましい歌を歌い始めた。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hymn of The End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おわりの歌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1 begin(s) to sing a sad song.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1は悲しい歌を歌い始めた。</t>
   </si>
   <si>
     <t xml:space="preserve">23</t>
@@ -1488,6 +1503,15 @@
   </si>
   <si>
     <t xml:space="preserve">#1は擬態を解いた！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadowform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影被り</t>
   </si>
   <si>
     <t xml:space="preserve">99</t>
@@ -2394,6 +2418,9 @@
     <t xml:space="preserve">EA 23.220</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.270</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 16.1</t>
   </si>
   <si>
@@ -2460,6 +2487,9 @@
     <t xml:space="preserve">EA 23.257</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.268</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.239</t>
   </si>
   <si>
@@ -2514,6 +2544,9 @@
     <t xml:space="preserve">勇气之歌</t>
   </si>
   <si>
+    <t xml:space="preserve">终结之歌</t>
+  </si>
+  <si>
     <t xml:space="preserve">呼吸困难</t>
   </si>
   <si>
@@ -2634,6 +2667,9 @@
     <t xml:space="preserve">拟态</t>
   </si>
   <si>
+    <t xml:space="preserve">身缠暗影</t>
+  </si>
+  <si>
     <t xml:space="preserve">极速难驭</t>
   </si>
   <si>
@@ -3067,6 +3103,9 @@
   </si>
   <si>
     <t xml:space="preserve">#1开始唱激昂之歌了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1开始唱悲伤之歌了。</t>
   </si>
   <si>
     <t xml:space="preserve">#1中了毒。
@@ -3618,10 +3657,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="C3" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3630,7 +3669,7 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="G3" t="s">
         <v>24</v>
@@ -3639,7 +3678,7 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="J3" t="s">
         <v>26</v>
@@ -3648,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -3659,7 +3698,7 @@
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="S3" t="s">
         <v>30</v>
@@ -3673,10 +3712,10 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="C4" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -3685,7 +3724,7 @@
         <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
@@ -3694,7 +3733,7 @@
         <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="J4" t="s">
         <v>33</v>
@@ -3703,7 +3742,7 @@
         <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -3714,7 +3753,7 @@
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="S4" t="s">
         <v>39</v>
@@ -3728,10 +3767,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="C5" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
@@ -3740,7 +3779,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="G5" t="s">
         <v>44</v>
@@ -3749,7 +3788,7 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="J5" t="s">
         <v>42</v>
@@ -3758,7 +3797,7 @@
         <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -3769,7 +3808,7 @@
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="S5" t="s">
         <v>48</v>
@@ -3783,10 +3822,10 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="C6" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -3795,7 +3834,7 @@
         <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="G6" t="s">
         <v>53</v>
@@ -3804,7 +3843,7 @@
         <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="J6" t="s">
         <v>51</v>
@@ -3813,7 +3852,7 @@
         <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="M6" t="s">
         <v>55</v>
@@ -3824,7 +3863,7 @@
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="S6" t="s">
         <v>57</v>
@@ -3838,10 +3877,10 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="C7" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -3850,7 +3889,7 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="G7" t="s">
         <v>62</v>
@@ -3859,7 +3898,7 @@
         <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="J7" t="s">
         <v>60</v>
@@ -3868,7 +3907,7 @@
         <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="M7" t="s">
         <v>64</v>
@@ -3879,7 +3918,7 @@
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="S7" t="s">
         <v>66</v>
@@ -3893,10 +3932,10 @@
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="C8" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="D8" t="s">
         <v>69</v>
@@ -3905,7 +3944,7 @@
         <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="G8" t="s">
         <v>71</v>
@@ -3914,7 +3953,7 @@
         <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="J8" t="s">
         <v>69</v>
@@ -3923,7 +3962,7 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="M8" t="s">
         <v>73</v>
@@ -3934,7 +3973,7 @@
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="S8" t="s">
         <v>66</v>
@@ -3948,10 +3987,10 @@
         <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>833</v>
       </c>
       <c r="D9" t="s">
         <v>76</v>
@@ -3960,1833 +3999,1847 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="G9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s">
+        <v>833</v>
+      </c>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M9" t="s">
         <v>78</v>
       </c>
-      <c r="H9" t="s">
+      <c r="N9" t="s">
         <v>79</v>
       </c>
-      <c r="I9" t="s">
-        <v>980</v>
-      </c>
-      <c r="J9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1008</v>
-      </c>
-      <c r="M9" t="s">
-        <v>82</v>
-      </c>
-      <c r="N9" t="s">
-        <v>83</v>
-      </c>
-      <c r="O9" t="s">
-        <v>1074</v>
-      </c>
-      <c r="P9" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>85</v>
-      </c>
+      <c r="P9"/>
+      <c r="Q9"/>
       <c r="R9" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
       <c r="S9" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="T9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>792</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" t="s">
+        <v>915</v>
+      </c>
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" t="s">
+        <v>992</v>
+      </c>
+      <c r="J10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="M10" t="s">
+        <v>87</v>
+      </c>
+      <c r="N10" t="s">
         <v>88</v>
       </c>
-      <c r="B10" t="s">
-        <v>784</v>
-      </c>
-      <c r="C10" t="s">
-        <v>823</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="O10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P10" t="s">
         <v>89</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>90</v>
       </c>
-      <c r="F10" t="s">
-        <v>904</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="R10" t="s">
+        <v>1097</v>
+      </c>
+      <c r="S10" t="s">
         <v>91</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
         <v>92</v>
       </c>
-      <c r="I10" t="s">
-        <v>981</v>
-      </c>
-      <c r="J10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" t="s">
-        <v>94</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1009</v>
-      </c>
-      <c r="M10" t="s">
-        <v>95</v>
-      </c>
-      <c r="N10" t="s">
-        <v>96</v>
-      </c>
-      <c r="O10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="P10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>98</v>
-      </c>
-      <c r="S10"/>
-      <c r="T10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>793</v>
+      </c>
+      <c r="C11" t="s">
+        <v>834</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" t="s">
+        <v>916</v>
+      </c>
+      <c r="G11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" t="s">
+        <v>993</v>
+      </c>
+      <c r="J11" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" t="s">
         <v>99</v>
       </c>
-      <c r="B11" t="s">
-        <v>783</v>
-      </c>
-      <c r="C11" t="s">
-        <v>824</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="L11" t="s">
+        <v>1022</v>
+      </c>
+      <c r="M11" t="s">
         <v>100</v>
       </c>
-      <c r="E11" t="s">
+      <c r="N11" t="s">
         <v>101</v>
       </c>
-      <c r="F11" t="s">
-        <v>905</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="O11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="P11" t="s">
         <v>102</v>
       </c>
-      <c r="H11" t="s">
+      <c r="Q11" t="s">
         <v>103</v>
       </c>
-      <c r="I11" t="s">
-        <v>824</v>
-      </c>
-      <c r="J11" t="s">
-        <v>100</v>
-      </c>
-      <c r="K11" t="s">
-        <v>101</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1010</v>
-      </c>
-      <c r="M11" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" t="s">
-        <v>105</v>
-      </c>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="S11" t="s">
-        <v>106</v>
-      </c>
-      <c r="T11" t="s">
-        <v>107</v>
-      </c>
+      <c r="S11"/>
+      <c r="T11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>792</v>
+      </c>
+      <c r="C12" t="s">
+        <v>835</v>
+      </c>
+      <c r="D12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" t="s">
+        <v>917</v>
+      </c>
+      <c r="G12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" t="s">
         <v>108</v>
       </c>
-      <c r="B12" t="s">
-        <v>783</v>
-      </c>
-      <c r="C12" t="s">
-        <v>825</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="I12" t="s">
+        <v>835</v>
+      </c>
+      <c r="J12" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M12" t="s">
         <v>109</v>
       </c>
-      <c r="E12" t="s">
+      <c r="N12" t="s">
         <v>110</v>
-      </c>
-      <c r="F12" t="s">
-        <v>906</v>
-      </c>
-      <c r="G12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" t="s">
-        <v>112</v>
-      </c>
-      <c r="I12" t="s">
-        <v>825</v>
-      </c>
-      <c r="J12" t="s">
-        <v>109</v>
-      </c>
-      <c r="K12" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" t="s">
-        <v>1011</v>
-      </c>
-      <c r="M12" t="s">
-        <v>113</v>
-      </c>
-      <c r="N12" t="s">
-        <v>114</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="S12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="T12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" t="s">
+        <v>792</v>
+      </c>
+      <c r="C13" t="s">
+        <v>836</v>
+      </c>
+      <c r="D13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" t="s">
+        <v>918</v>
+      </c>
+      <c r="G13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" t="s">
         <v>117</v>
       </c>
-      <c r="B13" t="s">
-        <v>783</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="I13" t="s">
+        <v>836</v>
+      </c>
+      <c r="J13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K13" t="s">
+        <v>115</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="M13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N13" t="s">
         <v>119</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" t="s">
-        <v>907</v>
-      </c>
-      <c r="G13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" t="s">
-        <v>119</v>
-      </c>
-      <c r="J13" t="s">
-        <v>122</v>
-      </c>
-      <c r="K13" t="s">
-        <v>119</v>
-      </c>
-      <c r="L13" t="s">
-        <v>1012</v>
-      </c>
-      <c r="M13" t="s">
-        <v>123</v>
-      </c>
-      <c r="N13" t="s">
-        <v>124</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="S13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="T13" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" t="s">
+        <v>792</v>
+      </c>
+      <c r="C14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" t="s">
+        <v>919</v>
+      </c>
+      <c r="G14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" t="s">
         <v>127</v>
       </c>
-      <c r="B14" t="s">
-        <v>783</v>
-      </c>
-      <c r="C14" t="s">
-        <v>826</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="K14" t="s">
+        <v>124</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="M14" t="s">
         <v>128</v>
       </c>
-      <c r="E14" t="s">
+      <c r="N14" t="s">
         <v>129</v>
-      </c>
-      <c r="F14" t="s">
-        <v>908</v>
-      </c>
-      <c r="G14" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" t="s">
-        <v>131</v>
-      </c>
-      <c r="I14" t="s">
-        <v>826</v>
-      </c>
-      <c r="J14" t="s">
-        <v>132</v>
-      </c>
-      <c r="K14" t="s">
-        <v>129</v>
-      </c>
-      <c r="L14" t="s">
-        <v>1013</v>
-      </c>
-      <c r="M14" t="s">
-        <v>133</v>
-      </c>
-      <c r="N14" t="s">
-        <v>134</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="S14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="T14" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
+        <v>792</v>
+      </c>
+      <c r="C15" t="s">
+        <v>837</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" t="s">
+        <v>920</v>
+      </c>
+      <c r="G15" t="s">
+        <v>135</v>
+      </c>
+      <c r="H15" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" t="s">
+        <v>837</v>
+      </c>
+      <c r="J15" t="s">
         <v>137</v>
       </c>
-      <c r="B15" t="s">
-        <v>785</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="K15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1026</v>
+      </c>
+      <c r="M15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N15" t="s">
         <v>139</v>
-      </c>
-      <c r="D15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F15" t="s">
-        <v>909</v>
-      </c>
-      <c r="G15" t="s">
-        <v>140</v>
-      </c>
-      <c r="H15" t="s">
-        <v>141</v>
-      </c>
-      <c r="I15" t="s">
-        <v>139</v>
-      </c>
-      <c r="J15" t="s">
-        <v>142</v>
-      </c>
-      <c r="K15" t="s">
-        <v>139</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1014</v>
-      </c>
-      <c r="M15" t="s">
-        <v>143</v>
-      </c>
-      <c r="N15" t="s">
-        <v>144</v>
       </c>
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="S15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="T15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>794</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" t="s">
+        <v>921</v>
+      </c>
+      <c r="G16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" t="s">
         <v>147</v>
       </c>
-      <c r="B16" t="s">
-        <v>783</v>
-      </c>
-      <c r="C16" t="s">
-        <v>827</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="K16" t="s">
+        <v>144</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1027</v>
+      </c>
+      <c r="M16" t="s">
         <v>148</v>
       </c>
-      <c r="E16" t="s">
+      <c r="N16" t="s">
         <v>149</v>
-      </c>
-      <c r="F16" t="s">
-        <v>908</v>
-      </c>
-      <c r="G16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" t="s">
-        <v>827</v>
-      </c>
-      <c r="J16" t="s">
-        <v>150</v>
-      </c>
-      <c r="K16" t="s">
-        <v>149</v>
-      </c>
-      <c r="L16" t="s">
-        <v>1015</v>
-      </c>
-      <c r="M16" t="s">
-        <v>151</v>
-      </c>
-      <c r="N16" t="s">
-        <v>152</v>
       </c>
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="S16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="T16" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s">
+        <v>792</v>
+      </c>
+      <c r="C17" t="s">
+        <v>838</v>
+      </c>
+      <c r="D17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G17" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" t="s">
+        <v>838</v>
+      </c>
+      <c r="J17" t="s">
         <v>155</v>
       </c>
-      <c r="B17" t="s">
-        <v>783</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="K17" t="s">
+        <v>154</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1028</v>
+      </c>
+      <c r="M17" t="s">
+        <v>156</v>
+      </c>
+      <c r="N17" t="s">
         <v>157</v>
-      </c>
-      <c r="D17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" t="s">
-        <v>157</v>
-      </c>
-      <c r="F17" t="s">
-        <v>910</v>
-      </c>
-      <c r="G17" t="s">
-        <v>158</v>
-      </c>
-      <c r="H17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" t="s">
-        <v>157</v>
-      </c>
-      <c r="J17" t="s">
-        <v>160</v>
-      </c>
-      <c r="K17" t="s">
-        <v>157</v>
-      </c>
-      <c r="L17" t="s">
-        <v>1016</v>
-      </c>
-      <c r="M17" t="s">
-        <v>161</v>
-      </c>
-      <c r="N17" t="s">
-        <v>162</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
       <c r="R17" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
       <c r="S17" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="T17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" t="s">
+        <v>792</v>
+      </c>
+      <c r="C18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" t="s">
+        <v>922</v>
+      </c>
+      <c r="G18" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" t="s">
         <v>165</v>
       </c>
-      <c r="B18" t="s">
-        <v>783</v>
-      </c>
-      <c r="C18" t="s">
-        <v>828</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="K18" t="s">
+        <v>162</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M18" t="s">
         <v>166</v>
       </c>
-      <c r="E18" t="s">
+      <c r="N18" t="s">
         <v>167</v>
-      </c>
-      <c r="F18" t="s">
-        <v>911</v>
-      </c>
-      <c r="G18" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" t="s">
-        <v>828</v>
-      </c>
-      <c r="J18" t="s">
-        <v>166</v>
-      </c>
-      <c r="K18" t="s">
-        <v>167</v>
-      </c>
-      <c r="L18" t="s">
-        <v>1017</v>
-      </c>
-      <c r="M18" t="s">
-        <v>170</v>
-      </c>
-      <c r="N18" t="s">
-        <v>171</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="S18" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="T18" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" t="s">
+        <v>792</v>
+      </c>
+      <c r="C19" t="s">
+        <v>839</v>
+      </c>
+      <c r="D19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F19" t="s">
+        <v>923</v>
+      </c>
+      <c r="G19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" t="s">
         <v>174</v>
       </c>
-      <c r="B19" t="s">
-        <v>783</v>
-      </c>
-      <c r="C19" t="s">
-        <v>829</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="I19" t="s">
+        <v>839</v>
+      </c>
+      <c r="J19" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" t="s">
+        <v>172</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1030</v>
+      </c>
+      <c r="M19" t="s">
         <v>175</v>
       </c>
-      <c r="E19" t="s">
+      <c r="N19" t="s">
         <v>176</v>
-      </c>
-      <c r="F19" t="s">
-        <v>912</v>
-      </c>
-      <c r="G19" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" t="s">
-        <v>982</v>
-      </c>
-      <c r="J19" t="s">
-        <v>179</v>
-      </c>
-      <c r="K19" t="s">
-        <v>180</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1018</v>
-      </c>
-      <c r="M19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N19" t="s">
-        <v>182</v>
       </c>
       <c r="P19"/>
       <c r="Q19"/>
       <c r="R19" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="S19" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="T19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" t="s">
+        <v>792</v>
+      </c>
+      <c r="C20" t="s">
+        <v>840</v>
+      </c>
+      <c r="D20" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F20" t="s">
+        <v>924</v>
+      </c>
+      <c r="G20" t="s">
+        <v>182</v>
+      </c>
+      <c r="H20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" t="s">
+        <v>994</v>
+      </c>
+      <c r="J20" t="s">
+        <v>184</v>
+      </c>
+      <c r="K20" t="s">
         <v>185</v>
       </c>
-      <c r="B20" t="s">
-        <v>783</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="L20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M20" t="s">
+        <v>186</v>
+      </c>
+      <c r="N20" t="s">
         <v>187</v>
-      </c>
-      <c r="D20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F20" t="s">
-        <v>913</v>
-      </c>
-      <c r="G20" t="s">
-        <v>188</v>
-      </c>
-      <c r="H20" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" t="s">
-        <v>983</v>
-      </c>
-      <c r="J20" t="s">
-        <v>190</v>
-      </c>
-      <c r="K20" t="s">
-        <v>191</v>
-      </c>
-      <c r="L20" t="s">
-        <v>1019</v>
-      </c>
-      <c r="M20" t="s">
-        <v>192</v>
-      </c>
-      <c r="N20" t="s">
-        <v>193</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
       <c r="R20" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
       <c r="S20" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="T20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>792</v>
+      </c>
+      <c r="C21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" t="s">
+        <v>925</v>
+      </c>
+      <c r="G21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" t="s">
+        <v>194</v>
+      </c>
+      <c r="I21" t="s">
+        <v>995</v>
+      </c>
+      <c r="J21" t="s">
+        <v>195</v>
+      </c>
+      <c r="K21" t="s">
         <v>196</v>
       </c>
-      <c r="B21" t="s">
-        <v>783</v>
-      </c>
-      <c r="C21" t="s">
-        <v>830</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="L21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M21" t="s">
         <v>197</v>
       </c>
-      <c r="E21" t="s">
+      <c r="N21" t="s">
         <v>198</v>
-      </c>
-      <c r="F21" t="s">
-        <v>914</v>
-      </c>
-      <c r="G21" t="s">
-        <v>199</v>
-      </c>
-      <c r="H21" t="s">
-        <v>200</v>
-      </c>
-      <c r="I21" t="s">
-        <v>984</v>
-      </c>
-      <c r="J21" t="s">
-        <v>201</v>
-      </c>
-      <c r="K21" t="s">
-        <v>202</v>
-      </c>
-      <c r="L21" t="s">
-        <v>1020</v>
-      </c>
-      <c r="M21" t="s">
-        <v>203</v>
-      </c>
-      <c r="N21" t="s">
-        <v>204</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
       <c r="R21" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="S21" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="T21" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>201</v>
+      </c>
+      <c r="B22" t="s">
+        <v>792</v>
+      </c>
+      <c r="C22" t="s">
+        <v>841</v>
+      </c>
+      <c r="D22" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" t="s">
+        <v>926</v>
+      </c>
+      <c r="G22" t="s">
+        <v>204</v>
+      </c>
+      <c r="H22" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" t="s">
+        <v>996</v>
+      </c>
+      <c r="J22" t="s">
+        <v>206</v>
+      </c>
+      <c r="K22" t="s">
         <v>207</v>
       </c>
-      <c r="B22" t="s">
-        <v>786</v>
-      </c>
-      <c r="C22" t="s">
-        <v>831</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="L22" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M22" t="s">
         <v>208</v>
       </c>
-      <c r="E22" t="s">
+      <c r="N22" t="s">
         <v>209</v>
-      </c>
-      <c r="F22" t="s">
-        <v>915</v>
-      </c>
-      <c r="G22" t="s">
-        <v>210</v>
-      </c>
-      <c r="H22" t="s">
-        <v>211</v>
-      </c>
-      <c r="I22" t="s">
-        <v>985</v>
-      </c>
-      <c r="J22" t="s">
-        <v>212</v>
-      </c>
-      <c r="K22" t="s">
-        <v>213</v>
-      </c>
-      <c r="L22" t="s">
-        <v>1021</v>
-      </c>
-      <c r="M22" t="s">
-        <v>214</v>
-      </c>
-      <c r="N22" t="s">
-        <v>215</v>
       </c>
       <c r="P22"/>
       <c r="Q22"/>
       <c r="R22" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="S22" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="T22" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" t="s">
+        <v>795</v>
+      </c>
+      <c r="C23" t="s">
+        <v>842</v>
+      </c>
+      <c r="D23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" t="s">
+        <v>214</v>
+      </c>
+      <c r="F23" t="s">
+        <v>927</v>
+      </c>
+      <c r="G23" t="s">
+        <v>215</v>
+      </c>
+      <c r="H23" t="s">
+        <v>216</v>
+      </c>
+      <c r="I23" t="s">
+        <v>997</v>
+      </c>
+      <c r="J23" t="s">
+        <v>217</v>
+      </c>
+      <c r="K23" t="s">
         <v>218</v>
       </c>
-      <c r="B23" t="s">
-        <v>778</v>
-      </c>
-      <c r="C23" t="s">
-        <v>832</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="L23" t="s">
+        <v>1034</v>
+      </c>
+      <c r="M23" t="s">
         <v>219</v>
       </c>
-      <c r="E23" t="s">
+      <c r="N23" t="s">
         <v>220</v>
-      </c>
-      <c r="F23" t="s">
-        <v>916</v>
-      </c>
-      <c r="G23" t="s">
-        <v>221</v>
-      </c>
-      <c r="H23" t="s">
-        <v>222</v>
-      </c>
-      <c r="I23" t="s">
-        <v>986</v>
-      </c>
-      <c r="J23" t="s">
-        <v>223</v>
-      </c>
-      <c r="K23" t="s">
-        <v>224</v>
-      </c>
-      <c r="L23" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M23" t="s">
-        <v>225</v>
-      </c>
-      <c r="N23" t="s">
-        <v>226</v>
       </c>
       <c r="P23"/>
       <c r="Q23"/>
       <c r="R23" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
       <c r="S23" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="T23" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" t="s">
+        <v>786</v>
+      </c>
+      <c r="C24" t="s">
+        <v>843</v>
+      </c>
+      <c r="D24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F24" t="s">
+        <v>928</v>
+      </c>
+      <c r="G24" t="s">
+        <v>226</v>
+      </c>
+      <c r="H24" t="s">
+        <v>227</v>
+      </c>
+      <c r="I24" t="s">
+        <v>998</v>
+      </c>
+      <c r="J24" t="s">
+        <v>228</v>
+      </c>
+      <c r="K24" t="s">
         <v>229</v>
       </c>
-      <c r="B24" t="s">
-        <v>783</v>
-      </c>
-      <c r="C24" t="s">
-        <v>833</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="L24" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M24" t="s">
         <v>230</v>
       </c>
-      <c r="E24" t="s">
+      <c r="N24" t="s">
         <v>231</v>
-      </c>
-      <c r="F24" t="s">
-        <v>917</v>
-      </c>
-      <c r="G24" t="s">
-        <v>232</v>
-      </c>
-      <c r="H24" t="s">
-        <v>233</v>
-      </c>
-      <c r="I24" t="s">
-        <v>833</v>
-      </c>
-      <c r="J24" t="s">
-        <v>230</v>
-      </c>
-      <c r="K24" t="s">
-        <v>231</v>
-      </c>
-      <c r="L24" t="s">
-        <v>1023</v>
-      </c>
-      <c r="M24" t="s">
-        <v>234</v>
-      </c>
-      <c r="N24" t="s">
-        <v>235</v>
       </c>
       <c r="P24"/>
       <c r="Q24"/>
       <c r="R24" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="S24" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="T24" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" t="s">
+        <v>792</v>
+      </c>
+      <c r="C25" t="s">
+        <v>844</v>
+      </c>
+      <c r="D25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" t="s">
+        <v>236</v>
+      </c>
+      <c r="F25" t="s">
+        <v>929</v>
+      </c>
+      <c r="G25" t="s">
+        <v>237</v>
+      </c>
+      <c r="H25" t="s">
         <v>238</v>
       </c>
-      <c r="B25" t="s">
-        <v>787</v>
-      </c>
-      <c r="C25" t="s">
-        <v>834</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="I25" t="s">
+        <v>844</v>
+      </c>
+      <c r="J25" t="s">
+        <v>235</v>
+      </c>
+      <c r="K25" t="s">
+        <v>236</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M25" t="s">
         <v>239</v>
       </c>
-      <c r="E25" t="s">
+      <c r="N25" t="s">
         <v>240</v>
-      </c>
-      <c r="F25" t="s">
-        <v>918</v>
-      </c>
-      <c r="G25" t="s">
-        <v>241</v>
-      </c>
-      <c r="H25" t="s">
-        <v>242</v>
-      </c>
-      <c r="I25" t="s">
-        <v>987</v>
-      </c>
-      <c r="J25" t="s">
-        <v>239</v>
-      </c>
-      <c r="K25" t="s">
-        <v>240</v>
-      </c>
-      <c r="L25" t="s">
-        <v>1024</v>
-      </c>
-      <c r="M25" t="s">
-        <v>243</v>
-      </c>
-      <c r="N25" t="s">
-        <v>244</v>
       </c>
       <c r="P25"/>
       <c r="Q25"/>
-      <c r="S25"/>
-      <c r="T25"/>
+      <c r="R25" t="s">
+        <v>1111</v>
+      </c>
+      <c r="S25" t="s">
+        <v>241</v>
+      </c>
+      <c r="T25" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" t="s">
+        <v>796</v>
+      </c>
+      <c r="C26" t="s">
+        <v>845</v>
+      </c>
+      <c r="D26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" t="s">
         <v>245</v>
       </c>
-      <c r="B26" t="s">
-        <v>788</v>
-      </c>
-      <c r="C26" t="s">
-        <v>835</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
+        <v>930</v>
+      </c>
+      <c r="G26" t="s">
         <v>246</v>
       </c>
-      <c r="E26" t="s">
+      <c r="H26" t="s">
         <v>247</v>
       </c>
-      <c r="F26" t="s">
-        <v>919</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
+        <v>999</v>
+      </c>
+      <c r="J26" t="s">
+        <v>244</v>
+      </c>
+      <c r="K26" t="s">
+        <v>245</v>
+      </c>
+      <c r="L26" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M26" t="s">
         <v>248</v>
       </c>
-      <c r="H26" t="s">
+      <c r="N26" t="s">
         <v>249</v>
-      </c>
-      <c r="I26" t="s">
-        <v>835</v>
-      </c>
-      <c r="J26" t="s">
-        <v>246</v>
-      </c>
-      <c r="K26" t="s">
-        <v>247</v>
-      </c>
-      <c r="L26" t="s">
-        <v>1025</v>
-      </c>
-      <c r="M26" t="s">
-        <v>250</v>
-      </c>
-      <c r="N26" t="s">
-        <v>251</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
-      <c r="R26" t="s">
-        <v>1099</v>
-      </c>
-      <c r="S26" t="s">
-        <v>252</v>
-      </c>
-      <c r="T26" t="s">
-        <v>253</v>
-      </c>
+      <c r="S26"/>
+      <c r="T26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" t="s">
+        <v>797</v>
+      </c>
+      <c r="C27" t="s">
+        <v>846</v>
+      </c>
+      <c r="D27" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" t="s">
+        <v>252</v>
+      </c>
+      <c r="F27" t="s">
+        <v>931</v>
+      </c>
+      <c r="G27" t="s">
+        <v>253</v>
+      </c>
+      <c r="H27" t="s">
         <v>254</v>
       </c>
-      <c r="B27" t="s">
-        <v>789</v>
-      </c>
-      <c r="C27" t="s">
-        <v>836</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="I27" t="s">
+        <v>846</v>
+      </c>
+      <c r="J27" t="s">
+        <v>251</v>
+      </c>
+      <c r="K27" t="s">
+        <v>252</v>
+      </c>
+      <c r="L27" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M27" t="s">
         <v>255</v>
       </c>
-      <c r="E27" t="s">
+      <c r="N27" t="s">
         <v>256</v>
-      </c>
-      <c r="F27" t="s">
-        <v>920</v>
-      </c>
-      <c r="G27" t="s">
-        <v>257</v>
-      </c>
-      <c r="H27" t="s">
-        <v>258</v>
-      </c>
-      <c r="I27" t="s">
-        <v>836</v>
-      </c>
-      <c r="J27" t="s">
-        <v>255</v>
-      </c>
-      <c r="K27" t="s">
-        <v>256</v>
-      </c>
-      <c r="L27" t="s">
-        <v>1026</v>
-      </c>
-      <c r="M27" t="s">
-        <v>259</v>
-      </c>
-      <c r="N27" t="s">
-        <v>260</v>
       </c>
       <c r="P27"/>
       <c r="Q27"/>
       <c r="R27" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="S27" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="T27" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>259</v>
+      </c>
+      <c r="B28" t="s">
+        <v>798</v>
+      </c>
+      <c r="C28" t="s">
+        <v>847</v>
+      </c>
+      <c r="D28" t="s">
+        <v>260</v>
+      </c>
+      <c r="E28" t="s">
+        <v>261</v>
+      </c>
+      <c r="F28" t="s">
+        <v>932</v>
+      </c>
+      <c r="G28" t="s">
+        <v>262</v>
+      </c>
+      <c r="H28" t="s">
         <v>263</v>
       </c>
-      <c r="B28" t="s">
-        <v>778</v>
-      </c>
-      <c r="C28" t="s">
-        <v>837</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="I28" t="s">
+        <v>847</v>
+      </c>
+      <c r="J28" t="s">
+        <v>260</v>
+      </c>
+      <c r="K28" t="s">
+        <v>261</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1039</v>
+      </c>
+      <c r="M28" t="s">
         <v>264</v>
       </c>
-      <c r="E28" t="s">
+      <c r="N28" t="s">
         <v>265</v>
-      </c>
-      <c r="F28" t="s">
-        <v>921</v>
-      </c>
-      <c r="G28" t="s">
-        <v>266</v>
-      </c>
-      <c r="H28" t="s">
-        <v>267</v>
-      </c>
-      <c r="I28" t="s">
-        <v>837</v>
-      </c>
-      <c r="J28" t="s">
-        <v>264</v>
-      </c>
-      <c r="K28" t="s">
-        <v>265</v>
-      </c>
-      <c r="L28" t="s">
-        <v>1027</v>
-      </c>
-      <c r="M28" t="s">
-        <v>268</v>
-      </c>
-      <c r="N28" t="s">
-        <v>269</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
       <c r="R28" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="S28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="T28" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>268</v>
+      </c>
+      <c r="B29" t="s">
+        <v>786</v>
+      </c>
+      <c r="C29" t="s">
+        <v>848</v>
+      </c>
+      <c r="D29" t="s">
+        <v>269</v>
+      </c>
+      <c r="E29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F29" t="s">
+        <v>933</v>
+      </c>
+      <c r="G29" t="s">
+        <v>271</v>
+      </c>
+      <c r="H29" t="s">
         <v>272</v>
       </c>
-      <c r="B29" t="s">
-        <v>790</v>
-      </c>
-      <c r="C29" t="s">
-        <v>838</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="I29" t="s">
+        <v>848</v>
+      </c>
+      <c r="J29" t="s">
+        <v>269</v>
+      </c>
+      <c r="K29" t="s">
+        <v>270</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1040</v>
+      </c>
+      <c r="M29" t="s">
         <v>273</v>
       </c>
-      <c r="E29" t="s">
+      <c r="N29" t="s">
         <v>274</v>
-      </c>
-      <c r="F29" t="s">
-        <v>922</v>
-      </c>
-      <c r="G29" t="s">
-        <v>275</v>
-      </c>
-      <c r="H29" t="s">
-        <v>276</v>
-      </c>
-      <c r="I29" t="s">
-        <v>838</v>
-      </c>
-      <c r="J29" t="s">
-        <v>273</v>
-      </c>
-      <c r="K29" t="s">
-        <v>274</v>
-      </c>
-      <c r="L29" t="s">
-        <v>1028</v>
-      </c>
-      <c r="M29" t="s">
-        <v>277</v>
-      </c>
-      <c r="N29" t="s">
-        <v>278</v>
       </c>
       <c r="P29"/>
       <c r="Q29"/>
       <c r="R29" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="S29" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="T29" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" t="s">
+        <v>799</v>
+      </c>
+      <c r="C30" t="s">
+        <v>849</v>
+      </c>
+      <c r="D30" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" t="s">
+        <v>279</v>
+      </c>
+      <c r="F30" t="s">
+        <v>934</v>
+      </c>
+      <c r="G30" t="s">
+        <v>280</v>
+      </c>
+      <c r="H30" t="s">
         <v>281</v>
       </c>
-      <c r="B30" t="s">
-        <v>790</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="I30" t="s">
+        <v>849</v>
+      </c>
+      <c r="J30" t="s">
+        <v>278</v>
+      </c>
+      <c r="K30" t="s">
+        <v>279</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M30" t="s">
+        <v>282</v>
+      </c>
+      <c r="N30" t="s">
         <v>283</v>
-      </c>
-      <c r="D30" t="s">
-        <v>282</v>
-      </c>
-      <c r="E30" t="s">
-        <v>283</v>
-      </c>
-      <c r="F30" t="s">
-        <v>923</v>
-      </c>
-      <c r="G30" t="s">
-        <v>284</v>
-      </c>
-      <c r="H30" t="s">
-        <v>285</v>
-      </c>
-      <c r="I30" t="s">
-        <v>283</v>
-      </c>
-      <c r="J30" t="s">
-        <v>282</v>
-      </c>
-      <c r="K30" t="s">
-        <v>283</v>
-      </c>
-      <c r="L30" t="s">
-        <v>1029</v>
-      </c>
-      <c r="M30" t="s">
-        <v>286</v>
-      </c>
-      <c r="N30" t="s">
-        <v>287</v>
       </c>
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="S30" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="T30" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B31" t="s">
+        <v>799</v>
+      </c>
+      <c r="C31" t="s">
+        <v>288</v>
+      </c>
+      <c r="D31" t="s">
+        <v>287</v>
+      </c>
+      <c r="E31" t="s">
+        <v>288</v>
+      </c>
+      <c r="F31" t="s">
+        <v>935</v>
+      </c>
+      <c r="G31" t="s">
+        <v>289</v>
+      </c>
+      <c r="H31" t="s">
         <v>290</v>
       </c>
-      <c r="B31" t="s">
-        <v>790</v>
-      </c>
-      <c r="C31" t="s">
-        <v>839</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="I31" t="s">
+        <v>288</v>
+      </c>
+      <c r="J31" t="s">
+        <v>287</v>
+      </c>
+      <c r="K31" t="s">
+        <v>288</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M31" t="s">
         <v>291</v>
       </c>
-      <c r="E31" t="s">
+      <c r="N31" t="s">
         <v>292</v>
-      </c>
-      <c r="F31" t="s">
-        <v>924</v>
-      </c>
-      <c r="G31" t="s">
-        <v>293</v>
-      </c>
-      <c r="H31" t="s">
-        <v>294</v>
-      </c>
-      <c r="I31" t="s">
-        <v>839</v>
-      </c>
-      <c r="J31" t="s">
-        <v>291</v>
-      </c>
-      <c r="K31" t="s">
-        <v>292</v>
-      </c>
-      <c r="L31" t="s">
-        <v>1030</v>
-      </c>
-      <c r="M31" t="s">
-        <v>295</v>
-      </c>
-      <c r="N31" t="s">
-        <v>296</v>
       </c>
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="S31" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="T31" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>295</v>
+      </c>
+      <c r="B32" t="s">
+        <v>799</v>
+      </c>
+      <c r="C32" t="s">
+        <v>850</v>
+      </c>
+      <c r="D32" t="s">
+        <v>296</v>
+      </c>
+      <c r="E32" t="s">
+        <v>297</v>
+      </c>
+      <c r="F32" t="s">
+        <v>936</v>
+      </c>
+      <c r="G32" t="s">
+        <v>298</v>
+      </c>
+      <c r="H32" t="s">
         <v>299</v>
       </c>
-      <c r="B32" t="s">
-        <v>790</v>
-      </c>
-      <c r="C32" t="s">
-        <v>840</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="I32" t="s">
+        <v>850</v>
+      </c>
+      <c r="J32" t="s">
+        <v>296</v>
+      </c>
+      <c r="K32" t="s">
+        <v>297</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1043</v>
+      </c>
+      <c r="M32" t="s">
         <v>300</v>
       </c>
-      <c r="E32" t="s">
+      <c r="N32" t="s">
         <v>301</v>
-      </c>
-      <c r="F32" t="s">
-        <v>925</v>
-      </c>
-      <c r="G32" t="s">
-        <v>302</v>
-      </c>
-      <c r="H32" t="s">
-        <v>303</v>
-      </c>
-      <c r="I32" t="s">
-        <v>840</v>
-      </c>
-      <c r="J32" t="s">
-        <v>300</v>
-      </c>
-      <c r="K32" t="s">
-        <v>301</v>
-      </c>
-      <c r="L32" t="s">
-        <v>1031</v>
-      </c>
-      <c r="M32" t="s">
-        <v>304</v>
-      </c>
-      <c r="N32" t="s">
-        <v>305</v>
       </c>
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="S32" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="T32" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>304</v>
+      </c>
+      <c r="B33" t="s">
+        <v>799</v>
+      </c>
+      <c r="C33" t="s">
+        <v>851</v>
+      </c>
+      <c r="D33" t="s">
+        <v>305</v>
+      </c>
+      <c r="E33" t="s">
+        <v>306</v>
+      </c>
+      <c r="F33" t="s">
+        <v>937</v>
+      </c>
+      <c r="G33" t="s">
+        <v>307</v>
+      </c>
+      <c r="H33" t="s">
         <v>308</v>
       </c>
-      <c r="B33" t="s">
-        <v>783</v>
-      </c>
-      <c r="C33" t="s">
-        <v>841</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="I33" t="s">
+        <v>851</v>
+      </c>
+      <c r="J33" t="s">
+        <v>305</v>
+      </c>
+      <c r="K33" t="s">
+        <v>306</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M33" t="s">
         <v>309</v>
       </c>
-      <c r="E33" t="s">
+      <c r="N33" t="s">
         <v>310</v>
-      </c>
-      <c r="F33" t="s">
-        <v>926</v>
-      </c>
-      <c r="G33" t="s">
-        <v>311</v>
-      </c>
-      <c r="H33" t="s">
-        <v>312</v>
-      </c>
-      <c r="I33" t="s">
-        <v>988</v>
-      </c>
-      <c r="J33" t="s">
-        <v>313</v>
-      </c>
-      <c r="K33" t="s">
-        <v>314</v>
-      </c>
-      <c r="L33" t="s">
-        <v>1032</v>
-      </c>
-      <c r="M33" t="s">
-        <v>315</v>
-      </c>
-      <c r="N33" t="s">
-        <v>316</v>
       </c>
       <c r="P33"/>
       <c r="Q33"/>
       <c r="R33" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="S33" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="T33" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>313</v>
+      </c>
+      <c r="B34" t="s">
+        <v>792</v>
+      </c>
+      <c r="C34" t="s">
+        <v>852</v>
+      </c>
+      <c r="D34" t="s">
+        <v>314</v>
+      </c>
+      <c r="E34" t="s">
+        <v>315</v>
+      </c>
+      <c r="F34" t="s">
+        <v>938</v>
+      </c>
+      <c r="G34" t="s">
+        <v>316</v>
+      </c>
+      <c r="H34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="s">
+        <v>318</v>
+      </c>
+      <c r="K34" t="s">
         <v>319</v>
       </c>
-      <c r="B34" t="s">
-        <v>783</v>
-      </c>
-      <c r="C34" t="s">
-        <v>842</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="L34" t="s">
+        <v>1045</v>
+      </c>
+      <c r="M34" t="s">
         <v>320</v>
       </c>
-      <c r="E34" t="s">
+      <c r="N34" t="s">
         <v>321</v>
-      </c>
-      <c r="F34" t="s">
-        <v>927</v>
-      </c>
-      <c r="G34" t="s">
-        <v>322</v>
-      </c>
-      <c r="H34" t="s">
-        <v>323</v>
-      </c>
-      <c r="I34" t="s">
-        <v>842</v>
-      </c>
-      <c r="J34" t="s">
-        <v>320</v>
-      </c>
-      <c r="K34" t="s">
-        <v>321</v>
-      </c>
-      <c r="L34" t="s">
-        <v>1033</v>
-      </c>
-      <c r="M34" t="s">
-        <v>324</v>
-      </c>
-      <c r="N34" t="s">
-        <v>325</v>
       </c>
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="S34" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="T34" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" t="s">
+        <v>792</v>
+      </c>
+      <c r="C35" t="s">
+        <v>853</v>
+      </c>
+      <c r="D35" t="s">
+        <v>325</v>
+      </c>
+      <c r="E35" t="s">
+        <v>326</v>
+      </c>
+      <c r="F35" t="s">
+        <v>939</v>
+      </c>
+      <c r="G35" t="s">
+        <v>327</v>
+      </c>
+      <c r="H35" t="s">
         <v>328</v>
       </c>
-      <c r="B35" t="s">
-        <v>791</v>
-      </c>
-      <c r="C35" t="s">
-        <v>843</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="I35" t="s">
+        <v>853</v>
+      </c>
+      <c r="J35" t="s">
+        <v>325</v>
+      </c>
+      <c r="K35" t="s">
+        <v>326</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1046</v>
+      </c>
+      <c r="M35" t="s">
         <v>329</v>
       </c>
-      <c r="E35" t="s">
+      <c r="N35" t="s">
         <v>330</v>
-      </c>
-      <c r="F35" t="s">
-        <v>928</v>
-      </c>
-      <c r="G35" t="s">
-        <v>331</v>
-      </c>
-      <c r="H35" t="s">
-        <v>332</v>
-      </c>
-      <c r="I35" t="s">
-        <v>843</v>
-      </c>
-      <c r="J35" t="s">
-        <v>329</v>
-      </c>
-      <c r="K35" t="s">
-        <v>330</v>
-      </c>
-      <c r="L35" t="s">
-        <v>1034</v>
-      </c>
-      <c r="M35" t="s">
-        <v>333</v>
-      </c>
-      <c r="N35" t="s">
-        <v>334</v>
       </c>
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="S35" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="T35" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>333</v>
+      </c>
+      <c r="B36" t="s">
+        <v>800</v>
+      </c>
+      <c r="C36" t="s">
+        <v>854</v>
+      </c>
+      <c r="D36" t="s">
+        <v>334</v>
+      </c>
+      <c r="E36" t="s">
+        <v>335</v>
+      </c>
+      <c r="F36" t="s">
+        <v>940</v>
+      </c>
+      <c r="G36" t="s">
+        <v>336</v>
+      </c>
+      <c r="H36" t="s">
         <v>337</v>
       </c>
-      <c r="B36" t="s">
-        <v>792</v>
-      </c>
-      <c r="C36" t="s">
-        <v>844</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="I36" t="s">
+        <v>854</v>
+      </c>
+      <c r="J36" t="s">
+        <v>334</v>
+      </c>
+      <c r="K36" t="s">
+        <v>335</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M36" t="s">
         <v>338</v>
       </c>
-      <c r="E36" t="s">
+      <c r="N36" t="s">
         <v>339</v>
-      </c>
-      <c r="F36" t="s">
-        <v>929</v>
-      </c>
-      <c r="G36" t="s">
-        <v>340</v>
-      </c>
-      <c r="H36" t="s">
-        <v>341</v>
-      </c>
-      <c r="I36" t="s">
-        <v>844</v>
-      </c>
-      <c r="J36" t="s">
-        <v>342</v>
-      </c>
-      <c r="K36" t="s">
-        <v>339</v>
-      </c>
-      <c r="L36" t="s">
-        <v>1035</v>
-      </c>
-      <c r="M36" t="s">
-        <v>343</v>
-      </c>
-      <c r="N36" t="s">
-        <v>344</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
       <c r="R36" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="S36" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T36" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>342</v>
+      </c>
+      <c r="B37" t="s">
+        <v>801</v>
+      </c>
+      <c r="C37" t="s">
+        <v>855</v>
+      </c>
+      <c r="D37" t="s">
+        <v>343</v>
+      </c>
+      <c r="E37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F37" t="s">
+        <v>941</v>
+      </c>
+      <c r="G37" t="s">
+        <v>345</v>
+      </c>
+      <c r="H37" t="s">
+        <v>346</v>
+      </c>
+      <c r="I37" t="s">
+        <v>855</v>
+      </c>
+      <c r="J37" t="s">
         <v>347</v>
       </c>
-      <c r="B37" t="s">
-        <v>793</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="K37" t="s">
+        <v>344</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1048</v>
+      </c>
+      <c r="M37" t="s">
+        <v>348</v>
+      </c>
+      <c r="N37" t="s">
         <v>349</v>
-      </c>
-      <c r="D37" t="s">
-        <v>348</v>
-      </c>
-      <c r="E37" t="s">
-        <v>349</v>
-      </c>
-      <c r="F37" t="s">
-        <v>930</v>
-      </c>
-      <c r="G37" t="s">
-        <v>350</v>
-      </c>
-      <c r="H37" t="s">
-        <v>351</v>
-      </c>
-      <c r="I37" t="s">
-        <v>349</v>
-      </c>
-      <c r="J37" t="s">
-        <v>348</v>
-      </c>
-      <c r="K37" t="s">
-        <v>349</v>
-      </c>
-      <c r="L37" t="s">
-        <v>1036</v>
-      </c>
-      <c r="M37" t="s">
-        <v>352</v>
-      </c>
-      <c r="N37" t="s">
-        <v>353</v>
       </c>
       <c r="P37"/>
       <c r="Q37"/>
       <c r="R37" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="S37" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="T37" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" t="s">
+        <v>802</v>
+      </c>
+      <c r="C38" t="s">
+        <v>354</v>
+      </c>
+      <c r="D38" t="s">
+        <v>353</v>
+      </c>
+      <c r="E38" t="s">
+        <v>354</v>
+      </c>
+      <c r="F38" t="s">
+        <v>942</v>
+      </c>
+      <c r="G38" t="s">
+        <v>355</v>
+      </c>
+      <c r="H38" t="s">
         <v>356</v>
       </c>
-      <c r="B38" t="s">
-        <v>791</v>
-      </c>
-      <c r="C38" t="s">
-        <v>845</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="I38" t="s">
+        <v>354</v>
+      </c>
+      <c r="J38" t="s">
+        <v>353</v>
+      </c>
+      <c r="K38" t="s">
+        <v>354</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1049</v>
+      </c>
+      <c r="M38" t="s">
         <v>357</v>
       </c>
-      <c r="E38" t="s">
+      <c r="N38" t="s">
         <v>358</v>
-      </c>
-      <c r="F38" t="s">
-        <v>931</v>
-      </c>
-      <c r="G38" t="s">
-        <v>359</v>
-      </c>
-      <c r="H38" t="s">
-        <v>360</v>
-      </c>
-      <c r="I38" t="s">
-        <v>845</v>
-      </c>
-      <c r="J38" t="s">
-        <v>361</v>
-      </c>
-      <c r="K38" t="s">
-        <v>358</v>
-      </c>
-      <c r="L38" t="s">
-        <v>1037</v>
-      </c>
-      <c r="M38" t="s">
-        <v>362</v>
-      </c>
-      <c r="N38" t="s">
-        <v>363</v>
       </c>
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="S38" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="T38" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>361</v>
+      </c>
+      <c r="B39" t="s">
+        <v>800</v>
+      </c>
+      <c r="C39" t="s">
+        <v>856</v>
+      </c>
+      <c r="D39" t="s">
+        <v>362</v>
+      </c>
+      <c r="E39" t="s">
+        <v>363</v>
+      </c>
+      <c r="F39" t="s">
+        <v>943</v>
+      </c>
+      <c r="G39" t="s">
+        <v>364</v>
+      </c>
+      <c r="H39" t="s">
+        <v>365</v>
+      </c>
+      <c r="I39" t="s">
+        <v>856</v>
+      </c>
+      <c r="J39" t="s">
         <v>366</v>
       </c>
-      <c r="B39" t="s">
-        <v>794</v>
-      </c>
-      <c r="C39" t="s">
-        <v>846</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="K39" t="s">
+        <v>363</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M39" t="s">
         <v>367</v>
       </c>
-      <c r="E39" t="s">
+      <c r="N39" t="s">
         <v>368</v>
-      </c>
-      <c r="F39" t="s">
-        <v>932</v>
-      </c>
-      <c r="G39" t="s">
-        <v>369</v>
-      </c>
-      <c r="H39" t="s">
-        <v>370</v>
-      </c>
-      <c r="I39" t="s">
-        <v>846</v>
-      </c>
-      <c r="J39" t="s">
-        <v>367</v>
-      </c>
-      <c r="K39" t="s">
-        <v>368</v>
-      </c>
-      <c r="L39" t="s">
-        <v>1038</v>
-      </c>
-      <c r="M39" t="s">
-        <v>371</v>
-      </c>
-      <c r="N39" t="s">
-        <v>372</v>
       </c>
       <c r="P39"/>
       <c r="Q39"/>
       <c r="R39" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="S39" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="T39" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>371</v>
+      </c>
+      <c r="B40" t="s">
+        <v>803</v>
+      </c>
+      <c r="C40" t="s">
+        <v>857</v>
+      </c>
+      <c r="D40" t="s">
+        <v>372</v>
+      </c>
+      <c r="E40" t="s">
+        <v>373</v>
+      </c>
+      <c r="F40" t="s">
+        <v>944</v>
+      </c>
+      <c r="G40" t="s">
+        <v>374</v>
+      </c>
+      <c r="H40" t="s">
         <v>375</v>
       </c>
-      <c r="B40" t="s">
-        <v>791</v>
-      </c>
-      <c r="C40" t="s">
-        <v>847</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="I40" t="s">
+        <v>857</v>
+      </c>
+      <c r="J40" t="s">
+        <v>372</v>
+      </c>
+      <c r="K40" t="s">
+        <v>373</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M40" t="s">
         <v>376</v>
       </c>
-      <c r="E40" t="s">
+      <c r="N40" t="s">
         <v>377</v>
-      </c>
-      <c r="F40" t="s">
-        <v>933</v>
-      </c>
-      <c r="G40" t="s">
-        <v>378</v>
-      </c>
-      <c r="H40" t="s">
-        <v>379</v>
-      </c>
-      <c r="I40" t="s">
-        <v>847</v>
-      </c>
-      <c r="J40" t="s">
-        <v>376</v>
-      </c>
-      <c r="K40" t="s">
-        <v>377</v>
-      </c>
-      <c r="L40" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M40" t="s">
-        <v>380</v>
-      </c>
-      <c r="N40" t="s">
-        <v>381</v>
       </c>
       <c r="P40"/>
       <c r="Q40"/>
       <c r="R40" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="S40" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="T40" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>380</v>
+      </c>
+      <c r="B41" t="s">
+        <v>800</v>
+      </c>
+      <c r="C41" t="s">
+        <v>858</v>
+      </c>
+      <c r="D41" t="s">
+        <v>381</v>
+      </c>
+      <c r="E41" t="s">
+        <v>382</v>
+      </c>
+      <c r="F41" t="s">
+        <v>945</v>
+      </c>
+      <c r="G41" t="s">
+        <v>383</v>
+      </c>
+      <c r="H41" t="s">
         <v>384</v>
       </c>
-      <c r="B41" t="s">
-        <v>795</v>
-      </c>
-      <c r="C41" t="s">
-        <v>848</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="I41" t="s">
+        <v>858</v>
+      </c>
+      <c r="J41" t="s">
+        <v>381</v>
+      </c>
+      <c r="K41" t="s">
+        <v>382</v>
+      </c>
+      <c r="L41" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M41" t="s">
         <v>385</v>
       </c>
-      <c r="E41" t="s">
+      <c r="N41" t="s">
         <v>386</v>
-      </c>
-      <c r="F41" t="s">
-        <v>934</v>
-      </c>
-      <c r="G41" t="s">
-        <v>387</v>
-      </c>
-      <c r="H41" t="s">
-        <v>388</v>
-      </c>
-      <c r="I41" t="s">
-        <v>848</v>
-      </c>
-      <c r="J41" t="s">
-        <v>385</v>
-      </c>
-      <c r="K41" t="s">
-        <v>386</v>
-      </c>
-      <c r="L41" t="s">
-        <v>1040</v>
-      </c>
-      <c r="M41" t="s">
-        <v>389</v>
-      </c>
-      <c r="N41" t="s">
-        <v>390</v>
       </c>
       <c r="P41"/>
       <c r="Q41"/>
-      <c r="S41"/>
-      <c r="T41"/>
+      <c r="R41" t="s">
+        <v>1126</v>
+      </c>
+      <c r="S41" t="s">
+        <v>387</v>
+      </c>
+      <c r="T41" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>389</v>
+      </c>
+      <c r="B42" t="s">
+        <v>804</v>
+      </c>
+      <c r="C42" t="s">
+        <v>859</v>
+      </c>
+      <c r="D42" t="s">
+        <v>390</v>
+      </c>
+      <c r="E42" t="s">
         <v>391</v>
       </c>
-      <c r="B42" t="s">
-        <v>796</v>
-      </c>
-      <c r="C42" t="s">
-        <v>849</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
+        <v>946</v>
+      </c>
+      <c r="G42" t="s">
         <v>392</v>
       </c>
-      <c r="E42" t="s">
+      <c r="H42" t="s">
         <v>393</v>
       </c>
-      <c r="F42" t="s">
-        <v>935</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
+        <v>859</v>
+      </c>
+      <c r="J42" t="s">
+        <v>390</v>
+      </c>
+      <c r="K42" t="s">
+        <v>391</v>
+      </c>
+      <c r="L42" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M42" t="s">
         <v>394</v>
       </c>
-      <c r="H42" t="s">
+      <c r="N42" t="s">
         <v>395</v>
       </c>
-      <c r="I42" t="s">
-        <v>849</v>
-      </c>
-      <c r="J42" t="s">
-        <v>392</v>
-      </c>
-      <c r="K42" t="s">
-        <v>393</v>
-      </c>
-      <c r="M42"/>
-      <c r="N42"/>
       <c r="P42"/>
       <c r="Q42"/>
       <c r="S42"/>
@@ -5797,10 +5850,10 @@
         <v>396</v>
       </c>
       <c r="B43" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="C43" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="D43" t="s">
         <v>397</v>
@@ -5809,7 +5862,7 @@
         <v>398</v>
       </c>
       <c r="F43" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="G43" t="s">
         <v>399</v>
@@ -5818,7 +5871,7 @@
         <v>400</v>
       </c>
       <c r="I43" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="J43" t="s">
         <v>397</v>
@@ -5838,10 +5891,10 @@
         <v>401</v>
       </c>
       <c r="B44" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="C44" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="D44" t="s">
         <v>402</v>
@@ -5850,7 +5903,7 @@
         <v>403</v>
       </c>
       <c r="F44" t="s">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="G44" t="s">
         <v>404</v>
@@ -5859,7 +5912,7 @@
         <v>405</v>
       </c>
       <c r="I44" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="J44" t="s">
         <v>402</v>
@@ -5867,282 +5920,275 @@
       <c r="K44" t="s">
         <v>403</v>
       </c>
-      <c r="L44" t="s">
-        <v>1041</v>
-      </c>
-      <c r="M44" t="s">
-        <v>406</v>
-      </c>
-      <c r="N44" t="s">
-        <v>407</v>
-      </c>
+      <c r="M44"/>
+      <c r="N44"/>
       <c r="P44"/>
       <c r="Q44"/>
-      <c r="R44" t="s">
-        <v>1114</v>
-      </c>
-      <c r="S44" t="s">
-        <v>408</v>
-      </c>
-      <c r="T44" t="s">
-        <v>409</v>
-      </c>
+      <c r="S44"/>
+      <c r="T44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>406</v>
+      </c>
+      <c r="B45" t="s">
+        <v>807</v>
+      </c>
+      <c r="C45" t="s">
+        <v>862</v>
+      </c>
+      <c r="D45" t="s">
+        <v>407</v>
+      </c>
+      <c r="E45" t="s">
+        <v>408</v>
+      </c>
+      <c r="F45" t="s">
+        <v>949</v>
+      </c>
+      <c r="G45" t="s">
+        <v>409</v>
+      </c>
+      <c r="H45" t="s">
         <v>410</v>
       </c>
-      <c r="B45" t="s">
-        <v>783</v>
-      </c>
-      <c r="C45" t="s">
-        <v>852</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="I45" t="s">
+        <v>862</v>
+      </c>
+      <c r="J45" t="s">
+        <v>407</v>
+      </c>
+      <c r="K45" t="s">
+        <v>408</v>
+      </c>
+      <c r="L45" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M45" t="s">
         <v>411</v>
       </c>
-      <c r="E45" t="s">
+      <c r="N45" t="s">
         <v>412</v>
-      </c>
-      <c r="F45" t="s">
-        <v>938</v>
-      </c>
-      <c r="G45" t="s">
-        <v>413</v>
-      </c>
-      <c r="H45" t="s">
-        <v>414</v>
-      </c>
-      <c r="I45" t="s">
-        <v>852</v>
-      </c>
-      <c r="J45" t="s">
-        <v>415</v>
-      </c>
-      <c r="K45" t="s">
-        <v>412</v>
-      </c>
-      <c r="L45" t="s">
-        <v>1042</v>
-      </c>
-      <c r="M45" t="s">
-        <v>416</v>
-      </c>
-      <c r="N45" t="s">
-        <v>417</v>
       </c>
       <c r="P45"/>
       <c r="Q45"/>
       <c r="R45" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="S45" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="T45" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>415</v>
+      </c>
+      <c r="B46" t="s">
+        <v>792</v>
+      </c>
+      <c r="C46" t="s">
+        <v>863</v>
+      </c>
+      <c r="D46" t="s">
+        <v>416</v>
+      </c>
+      <c r="E46" t="s">
+        <v>417</v>
+      </c>
+      <c r="F46" t="s">
+        <v>950</v>
+      </c>
+      <c r="G46" t="s">
+        <v>418</v>
+      </c>
+      <c r="H46" t="s">
+        <v>419</v>
+      </c>
+      <c r="I46" t="s">
+        <v>863</v>
+      </c>
+      <c r="J46" t="s">
         <v>420</v>
       </c>
-      <c r="B46" t="s">
-        <v>783</v>
-      </c>
-      <c r="C46" t="s">
-        <v>853</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="K46" t="s">
+        <v>417</v>
+      </c>
+      <c r="L46" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M46" t="s">
         <v>421</v>
       </c>
-      <c r="E46" t="s">
+      <c r="N46" t="s">
         <v>422</v>
-      </c>
-      <c r="F46" t="s">
-        <v>939</v>
-      </c>
-      <c r="G46" t="s">
-        <v>423</v>
-      </c>
-      <c r="H46" t="s">
-        <v>424</v>
-      </c>
-      <c r="I46" t="s">
-        <v>853</v>
-      </c>
-      <c r="J46" t="s">
-        <v>421</v>
-      </c>
-      <c r="K46" t="s">
-        <v>422</v>
-      </c>
-      <c r="L46" t="s">
-        <v>1043</v>
-      </c>
-      <c r="M46" t="s">
-        <v>425</v>
-      </c>
-      <c r="N46" t="s">
-        <v>426</v>
       </c>
       <c r="P46"/>
       <c r="Q46"/>
       <c r="R46" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="S46" t="s">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="T46" t="s">
-        <v>327</v>
+        <v>424</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>425</v>
+      </c>
+      <c r="B47" t="s">
+        <v>792</v>
+      </c>
+      <c r="C47" t="s">
+        <v>864</v>
+      </c>
+      <c r="D47" t="s">
+        <v>426</v>
+      </c>
+      <c r="E47" t="s">
         <v>427</v>
       </c>
-      <c r="B47" t="s">
-        <v>783</v>
-      </c>
-      <c r="C47" t="s">
-        <v>854</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
+        <v>951</v>
+      </c>
+      <c r="G47" t="s">
         <v>428</v>
       </c>
-      <c r="E47" t="s">
+      <c r="H47" t="s">
         <v>429</v>
       </c>
-      <c r="F47" t="s">
-        <v>940</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="I47" t="s">
+        <v>864</v>
+      </c>
+      <c r="J47" t="s">
+        <v>426</v>
+      </c>
+      <c r="K47" t="s">
+        <v>427</v>
+      </c>
+      <c r="L47" t="s">
+        <v>1056</v>
+      </c>
+      <c r="M47" t="s">
         <v>430</v>
       </c>
-      <c r="H47" t="s">
+      <c r="N47" t="s">
         <v>431</v>
-      </c>
-      <c r="I47" t="s">
-        <v>854</v>
-      </c>
-      <c r="J47" t="s">
-        <v>428</v>
-      </c>
-      <c r="K47" t="s">
-        <v>429</v>
-      </c>
-      <c r="L47" t="s">
-        <v>1044</v>
-      </c>
-      <c r="M47" t="s">
-        <v>432</v>
-      </c>
-      <c r="N47" t="s">
-        <v>433</v>
       </c>
       <c r="P47"/>
       <c r="Q47"/>
       <c r="R47" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="S47" t="s">
-        <v>434</v>
+        <v>331</v>
       </c>
       <c r="T47" t="s">
-        <v>435</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>432</v>
+      </c>
+      <c r="B48" t="s">
+        <v>792</v>
+      </c>
+      <c r="C48" t="s">
+        <v>865</v>
+      </c>
+      <c r="D48" t="s">
+        <v>433</v>
+      </c>
+      <c r="E48" t="s">
+        <v>434</v>
+      </c>
+      <c r="F48" t="s">
+        <v>952</v>
+      </c>
+      <c r="G48" t="s">
+        <v>435</v>
+      </c>
+      <c r="H48" t="s">
         <v>436</v>
       </c>
-      <c r="B48" t="s">
-        <v>778</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="I48" t="s">
+        <v>865</v>
+      </c>
+      <c r="J48" t="s">
+        <v>433</v>
+      </c>
+      <c r="K48" t="s">
+        <v>434</v>
+      </c>
+      <c r="L48" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M48" t="s">
+        <v>437</v>
+      </c>
+      <c r="N48" t="s">
         <v>438</v>
-      </c>
-      <c r="D48" t="s">
-        <v>437</v>
-      </c>
-      <c r="E48" t="s">
-        <v>438</v>
-      </c>
-      <c r="F48" t="s">
-        <v>941</v>
-      </c>
-      <c r="G48" t="s">
-        <v>439</v>
-      </c>
-      <c r="H48" t="s">
-        <v>440</v>
-      </c>
-      <c r="I48" t="s">
-        <v>438</v>
-      </c>
-      <c r="J48" t="s">
-        <v>437</v>
-      </c>
-      <c r="K48" t="s">
-        <v>438</v>
-      </c>
-      <c r="L48" t="s">
-        <v>1045</v>
-      </c>
-      <c r="M48" t="s">
-        <v>441</v>
-      </c>
-      <c r="N48" t="s">
-        <v>442</v>
       </c>
       <c r="P48"/>
       <c r="Q48"/>
-      <c r="S48"/>
-      <c r="T48"/>
+      <c r="R48" t="s">
+        <v>1130</v>
+      </c>
+      <c r="S48" t="s">
+        <v>439</v>
+      </c>
+      <c r="T48" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>441</v>
+      </c>
+      <c r="B49" t="s">
+        <v>786</v>
+      </c>
+      <c r="C49" t="s">
         <v>443</v>
       </c>
-      <c r="B49" t="s">
-        <v>799</v>
-      </c>
-      <c r="C49" t="s">
-        <v>855</v>
-      </c>
       <c r="D49" t="s">
+        <v>442</v>
+      </c>
+      <c r="E49" t="s">
+        <v>443</v>
+      </c>
+      <c r="F49" t="s">
+        <v>953</v>
+      </c>
+      <c r="G49" t="s">
         <v>444</v>
       </c>
-      <c r="E49" t="s">
+      <c r="H49" t="s">
         <v>445</v>
       </c>
-      <c r="F49" t="s">
-        <v>942</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="I49" t="s">
+        <v>443</v>
+      </c>
+      <c r="J49" t="s">
+        <v>442</v>
+      </c>
+      <c r="K49" t="s">
+        <v>443</v>
+      </c>
+      <c r="L49" t="s">
+        <v>1058</v>
+      </c>
+      <c r="M49" t="s">
         <v>446</v>
       </c>
-      <c r="H49" t="s">
+      <c r="N49" t="s">
         <v>447</v>
-      </c>
-      <c r="I49" t="s">
-        <v>855</v>
-      </c>
-      <c r="J49" t="s">
-        <v>444</v>
-      </c>
-      <c r="K49" t="s">
-        <v>445</v>
-      </c>
-      <c r="L49" t="s">
-        <v>1046</v>
-      </c>
-      <c r="M49" t="s">
-        <v>448</v>
-      </c>
-      <c r="N49" t="s">
-        <v>449</v>
       </c>
       <c r="P49"/>
       <c r="Q49"/>
@@ -6151,490 +6197,518 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>448</v>
+      </c>
+      <c r="B50" t="s">
+        <v>808</v>
+      </c>
+      <c r="C50" t="s">
+        <v>866</v>
+      </c>
+      <c r="D50" t="s">
+        <v>449</v>
+      </c>
+      <c r="E50" t="s">
         <v>450</v>
       </c>
-      <c r="B50" t="s">
-        <v>800</v>
-      </c>
-      <c r="C50" t="s">
-        <v>856</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
+        <v>954</v>
+      </c>
+      <c r="G50" t="s">
         <v>451</v>
       </c>
-      <c r="E50" t="s">
+      <c r="H50" t="s">
         <v>452</v>
       </c>
-      <c r="F50" t="s">
-        <v>943</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="I50" t="s">
+        <v>866</v>
+      </c>
+      <c r="J50" t="s">
+        <v>449</v>
+      </c>
+      <c r="K50" t="s">
+        <v>450</v>
+      </c>
+      <c r="L50" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M50" t="s">
         <v>453</v>
       </c>
-      <c r="H50" t="s">
+      <c r="N50" t="s">
         <v>454</v>
-      </c>
-      <c r="I50" t="s">
-        <v>856</v>
-      </c>
-      <c r="J50" t="s">
-        <v>451</v>
-      </c>
-      <c r="K50" t="s">
-        <v>452</v>
-      </c>
-      <c r="L50" t="s">
-        <v>1047</v>
-      </c>
-      <c r="M50" t="s">
-        <v>455</v>
-      </c>
-      <c r="N50" t="s">
-        <v>456</v>
       </c>
       <c r="P50"/>
       <c r="Q50"/>
-      <c r="R50" t="s">
-        <v>1118</v>
-      </c>
-      <c r="S50" t="s">
-        <v>457</v>
-      </c>
-      <c r="T50" t="s">
-        <v>458</v>
-      </c>
+      <c r="S50"/>
+      <c r="T50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>455</v>
+      </c>
+      <c r="B51" t="s">
+        <v>809</v>
+      </c>
+      <c r="C51" t="s">
+        <v>867</v>
+      </c>
+      <c r="D51" t="s">
+        <v>456</v>
+      </c>
+      <c r="E51" t="s">
+        <v>457</v>
+      </c>
+      <c r="F51" t="s">
+        <v>955</v>
+      </c>
+      <c r="G51" t="s">
+        <v>458</v>
+      </c>
+      <c r="H51" t="s">
         <v>459</v>
       </c>
-      <c r="B51" t="s">
-        <v>801</v>
-      </c>
-      <c r="C51" t="s">
-        <v>857</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="I51" t="s">
+        <v>867</v>
+      </c>
+      <c r="J51" t="s">
+        <v>456</v>
+      </c>
+      <c r="K51" t="s">
+        <v>457</v>
+      </c>
+      <c r="L51" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M51" t="s">
         <v>460</v>
       </c>
-      <c r="E51" t="s">
+      <c r="N51" t="s">
         <v>461</v>
-      </c>
-      <c r="F51" t="s">
-        <v>943</v>
-      </c>
-      <c r="G51" t="s">
-        <v>453</v>
-      </c>
-      <c r="H51" t="s">
-        <v>454</v>
-      </c>
-      <c r="I51" t="s">
-        <v>857</v>
-      </c>
-      <c r="J51" t="s">
-        <v>460</v>
-      </c>
-      <c r="K51" t="s">
-        <v>461</v>
-      </c>
-      <c r="L51" t="s">
-        <v>1048</v>
-      </c>
-      <c r="M51" t="s">
-        <v>462</v>
-      </c>
-      <c r="N51" t="s">
-        <v>463</v>
       </c>
       <c r="P51"/>
       <c r="Q51"/>
       <c r="R51" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="S51" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="T51" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>464</v>
+      </c>
+      <c r="B52" t="s">
+        <v>810</v>
+      </c>
+      <c r="C52" t="s">
+        <v>868</v>
+      </c>
+      <c r="D52" t="s">
+        <v>465</v>
+      </c>
+      <c r="E52" t="s">
         <v>466</v>
       </c>
-      <c r="B52" t="s">
-        <v>800</v>
-      </c>
-      <c r="C52" t="s">
-        <v>858</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
+        <v>955</v>
+      </c>
+      <c r="G52" t="s">
+        <v>458</v>
+      </c>
+      <c r="H52" t="s">
+        <v>459</v>
+      </c>
+      <c r="I52" t="s">
+        <v>868</v>
+      </c>
+      <c r="J52" t="s">
+        <v>465</v>
+      </c>
+      <c r="K52" t="s">
+        <v>466</v>
+      </c>
+      <c r="L52" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M52" t="s">
         <v>467</v>
       </c>
-      <c r="E52" t="s">
+      <c r="N52" t="s">
         <v>468</v>
-      </c>
-      <c r="F52" t="s">
-        <v>944</v>
-      </c>
-      <c r="G52" t="s">
-        <v>469</v>
-      </c>
-      <c r="H52" t="s">
-        <v>470</v>
-      </c>
-      <c r="I52" t="s">
-        <v>858</v>
-      </c>
-      <c r="J52" t="s">
-        <v>467</v>
-      </c>
-      <c r="K52" t="s">
-        <v>468</v>
-      </c>
-      <c r="L52" t="s">
-        <v>1049</v>
-      </c>
-      <c r="M52" t="s">
-        <v>471</v>
-      </c>
-      <c r="N52" t="s">
-        <v>472</v>
       </c>
       <c r="P52"/>
       <c r="Q52"/>
       <c r="R52" t="s">
-        <v>1118</v>
+        <v>1132</v>
       </c>
       <c r="S52" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="T52" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>471</v>
+      </c>
+      <c r="B53" t="s">
+        <v>809</v>
+      </c>
+      <c r="C53" t="s">
+        <v>869</v>
+      </c>
+      <c r="D53" t="s">
+        <v>472</v>
+      </c>
+      <c r="E53" t="s">
         <v>473</v>
       </c>
-      <c r="B53" t="s">
-        <v>800</v>
-      </c>
-      <c r="C53" t="s">
-        <v>859</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>956</v>
+      </c>
+      <c r="G53" t="s">
         <v>474</v>
       </c>
-      <c r="E53" t="s">
+      <c r="H53" t="s">
         <v>475</v>
       </c>
-      <c r="F53" t="s">
-        <v>944</v>
-      </c>
-      <c r="G53" t="s">
-        <v>469</v>
-      </c>
-      <c r="H53" t="s">
-        <v>470</v>
-      </c>
       <c r="I53" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="J53" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K53" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L53" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
       <c r="M53" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N53" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="P53"/>
       <c r="Q53"/>
       <c r="R53" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="S53" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="T53" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>478</v>
+      </c>
+      <c r="B54" t="s">
+        <v>809</v>
+      </c>
+      <c r="C54" t="s">
+        <v>870</v>
+      </c>
+      <c r="D54" t="s">
+        <v>479</v>
+      </c>
+      <c r="E54" t="s">
+        <v>480</v>
+      </c>
+      <c r="F54" t="s">
+        <v>956</v>
+      </c>
+      <c r="G54" t="s">
+        <v>474</v>
+      </c>
+      <c r="H54" t="s">
+        <v>475</v>
+      </c>
+      <c r="I54" t="s">
+        <v>870</v>
+      </c>
+      <c r="J54" t="s">
+        <v>479</v>
+      </c>
+      <c r="K54" t="s">
+        <v>480</v>
+      </c>
+      <c r="L54" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M54" t="s">
         <v>476</v>
       </c>
-      <c r="B54" t="s">
-        <v>802</v>
-      </c>
-      <c r="C54" t="s">
-        <v>860</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="N54" t="s">
         <v>477</v>
-      </c>
-      <c r="E54" t="s">
-        <v>478</v>
-      </c>
-      <c r="F54" t="s">
-        <v>944</v>
-      </c>
-      <c r="G54" t="s">
-        <v>469</v>
-      </c>
-      <c r="H54" t="s">
-        <v>470</v>
-      </c>
-      <c r="I54" t="s">
-        <v>860</v>
-      </c>
-      <c r="J54" t="s">
-        <v>477</v>
-      </c>
-      <c r="K54" t="s">
-        <v>478</v>
-      </c>
-      <c r="L54" t="s">
-        <v>1049</v>
-      </c>
-      <c r="M54" t="s">
-        <v>471</v>
-      </c>
-      <c r="N54" t="s">
-        <v>472</v>
       </c>
       <c r="P54"/>
       <c r="Q54"/>
       <c r="R54" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="S54" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="T54" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="C55" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="D55" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E55" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F55" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="G55" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="H55" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="I55" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="J55" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K55" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L55" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
       <c r="M55" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N55" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="P55"/>
       <c r="Q55"/>
       <c r="R55" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="S55" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="T55" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="C56" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="D56" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E56" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F56" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="G56" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="H56" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="I56" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="J56" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K56" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L56" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="M56" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="N56" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="P56"/>
       <c r="Q56"/>
       <c r="R56" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="S56" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="T56" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>487</v>
+      </c>
+      <c r="B57" t="s">
+        <v>813</v>
+      </c>
+      <c r="C57" t="s">
+        <v>873</v>
+      </c>
+      <c r="D57" t="s">
+        <v>488</v>
+      </c>
+      <c r="E57" t="s">
         <v>489</v>
       </c>
-      <c r="B57" t="s">
-        <v>805</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="F57" t="s">
+        <v>956</v>
+      </c>
+      <c r="G57" t="s">
+        <v>474</v>
+      </c>
+      <c r="H57" t="s">
+        <v>475</v>
+      </c>
+      <c r="I57" t="s">
+        <v>873</v>
+      </c>
+      <c r="J57" t="s">
+        <v>488</v>
+      </c>
+      <c r="K57" t="s">
+        <v>489</v>
+      </c>
+      <c r="L57" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M57" t="s">
+        <v>490</v>
+      </c>
+      <c r="N57" t="s">
         <v>491</v>
       </c>
-      <c r="D57" t="s">
-        <v>490</v>
-      </c>
-      <c r="E57" t="s">
-        <v>491</v>
-      </c>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57" t="s">
-        <v>492</v>
-      </c>
-      <c r="J57" t="s">
-        <v>492</v>
-      </c>
-      <c r="K57" t="s">
-        <v>492</v>
-      </c>
-      <c r="M57"/>
-      <c r="N57"/>
       <c r="P57"/>
       <c r="Q57"/>
-      <c r="S57"/>
-      <c r="T57"/>
+      <c r="R57" t="s">
+        <v>1133</v>
+      </c>
+      <c r="S57" t="s">
+        <v>492</v>
+      </c>
+      <c r="T57" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="C58" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="D58" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E58" t="s">
+        <v>496</v>
+      </c>
+      <c r="F58" t="s">
+        <v>956</v>
+      </c>
+      <c r="G58" t="s">
+        <v>474</v>
+      </c>
+      <c r="H58" t="s">
+        <v>475</v>
+      </c>
+      <c r="I58" t="s">
+        <v>874</v>
+      </c>
+      <c r="J58" t="s">
         <v>495</v>
       </c>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58" t="s">
-        <v>863</v>
-      </c>
-      <c r="J58" t="s">
-        <v>494</v>
-      </c>
       <c r="K58" t="s">
-        <v>495</v>
-      </c>
-      <c r="M58"/>
-      <c r="N58"/>
+        <v>496</v>
+      </c>
+      <c r="L58" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M58" t="s">
+        <v>490</v>
+      </c>
+      <c r="N58" t="s">
+        <v>491</v>
+      </c>
       <c r="P58"/>
       <c r="Q58"/>
-      <c r="S58"/>
-      <c r="T58"/>
+      <c r="R58" t="s">
+        <v>1133</v>
+      </c>
+      <c r="S58" t="s">
+        <v>492</v>
+      </c>
+      <c r="T58" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B59" t="s">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="C59" t="s">
-        <v>864</v>
+        <v>499</v>
       </c>
       <c r="D59" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E59" t="s">
-        <v>498</v>
-      </c>
-      <c r="F59" t="s">
-        <v>945</v>
-      </c>
-      <c r="G59" t="s">
         <v>499</v>
       </c>
-      <c r="H59" t="s">
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59" t="s">
         <v>500</v>
       </c>
-      <c r="I59" t="s">
-        <v>864</v>
-      </c>
       <c r="J59" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K59" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M59"/>
       <c r="N59"/>
@@ -6648,10 +6722,10 @@
         <v>501</v>
       </c>
       <c r="B60" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="C60" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="D60" t="s">
         <v>502</v>
@@ -6659,17 +6733,10 @@
       <c r="E60" t="s">
         <v>503</v>
       </c>
-      <c r="F60" t="s">
-        <v>946</v>
-      </c>
-      <c r="G60" t="s">
-        <v>504</v>
-      </c>
-      <c r="H60" t="s">
-        <v>505</v>
-      </c>
+      <c r="G60"/>
+      <c r="H60"/>
       <c r="I60" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="J60" t="s">
         <v>502</v>
@@ -6686,47 +6753,40 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>504</v>
+      </c>
+      <c r="B61" t="s">
+        <v>813</v>
+      </c>
+      <c r="C61" t="s">
+        <v>876</v>
+      </c>
+      <c r="D61" t="s">
+        <v>505</v>
+      </c>
+      <c r="E61" t="s">
         <v>506</v>
       </c>
-      <c r="B61" t="s">
-        <v>790</v>
-      </c>
-      <c r="C61" t="s">
-        <v>866</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
+        <v>957</v>
+      </c>
+      <c r="G61" t="s">
         <v>507</v>
       </c>
-      <c r="E61" t="s">
+      <c r="H61" t="s">
         <v>508</v>
       </c>
-      <c r="F61" t="s">
-        <v>947</v>
-      </c>
-      <c r="G61" t="s">
-        <v>509</v>
-      </c>
-      <c r="H61" t="s">
-        <v>510</v>
-      </c>
       <c r="I61" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="J61" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K61" t="s">
-        <v>508</v>
-      </c>
-      <c r="L61" t="s">
-        <v>1051</v>
-      </c>
-      <c r="M61" t="s">
-        <v>511</v>
-      </c>
-      <c r="N61" t="s">
-        <v>512</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="M61"/>
+      <c r="N61"/>
       <c r="P61"/>
       <c r="Q61"/>
       <c r="S61"/>
@@ -6734,101 +6794,87 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>509</v>
+      </c>
+      <c r="B62" t="s">
+        <v>816</v>
+      </c>
+      <c r="C62" t="s">
+        <v>877</v>
+      </c>
+      <c r="D62" t="s">
+        <v>510</v>
+      </c>
+      <c r="E62" t="s">
+        <v>511</v>
+      </c>
+      <c r="F62" t="s">
+        <v>958</v>
+      </c>
+      <c r="G62" t="s">
+        <v>512</v>
+      </c>
+      <c r="H62" t="s">
         <v>513</v>
       </c>
-      <c r="B62" t="s">
-        <v>794</v>
-      </c>
-      <c r="C62" t="s">
-        <v>515</v>
-      </c>
-      <c r="D62" t="s">
-        <v>514</v>
-      </c>
-      <c r="E62" t="s">
-        <v>515</v>
-      </c>
-      <c r="F62" t="s">
-        <v>948</v>
-      </c>
-      <c r="G62" t="s">
-        <v>516</v>
-      </c>
-      <c r="H62" t="s">
-        <v>517</v>
-      </c>
       <c r="I62" t="s">
-        <v>515</v>
+        <v>877</v>
       </c>
       <c r="J62" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="K62" t="s">
-        <v>515</v>
-      </c>
-      <c r="L62" t="s">
-        <v>1052</v>
-      </c>
-      <c r="M62" t="s">
-        <v>518</v>
-      </c>
-      <c r="N62" t="s">
-        <v>519</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="M62"/>
+      <c r="N62"/>
       <c r="P62"/>
       <c r="Q62"/>
-      <c r="R62" t="s">
-        <v>1121</v>
-      </c>
-      <c r="S62" t="s">
-        <v>520</v>
-      </c>
-      <c r="T62" t="s">
-        <v>521</v>
-      </c>
+      <c r="S62"/>
+      <c r="T62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="C63" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="D63" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E63" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="F63" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="G63" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="H63" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="I63" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="J63" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="K63" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L63" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="M63" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="N63" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="P63"/>
       <c r="Q63"/>
@@ -6837,94 +6883,101 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B64" t="s">
-        <v>790</v>
+        <v>803</v>
       </c>
       <c r="C64" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D64" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E64" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="F64" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="G64" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="H64" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="I64" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="J64" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="K64" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="L64" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="M64" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="N64" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="P64"/>
       <c r="Q64"/>
-      <c r="S64"/>
-      <c r="T64"/>
+      <c r="R64" t="s">
+        <v>1134</v>
+      </c>
+      <c r="S64" t="s">
+        <v>528</v>
+      </c>
+      <c r="T64" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>530</v>
+      </c>
+      <c r="B65" t="s">
+        <v>799</v>
+      </c>
+      <c r="C65" t="s">
+        <v>879</v>
+      </c>
+      <c r="D65" t="s">
+        <v>531</v>
+      </c>
+      <c r="E65" t="s">
+        <v>532</v>
+      </c>
+      <c r="F65" t="s">
+        <v>961</v>
+      </c>
+      <c r="G65" t="s">
+        <v>533</v>
+      </c>
+      <c r="H65" t="s">
+        <v>534</v>
+      </c>
+      <c r="I65" t="s">
+        <v>879</v>
+      </c>
+      <c r="J65" t="s">
+        <v>531</v>
+      </c>
+      <c r="K65" t="s">
+        <v>532</v>
+      </c>
+      <c r="L65" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M65" t="s">
+        <v>535</v>
+      </c>
+      <c r="N65" t="s">
         <v>536</v>
-      </c>
-      <c r="B65" t="s">
-        <v>807</v>
-      </c>
-      <c r="C65" t="s">
-        <v>868</v>
-      </c>
-      <c r="D65" t="s">
-        <v>537</v>
-      </c>
-      <c r="E65" t="s">
-        <v>538</v>
-      </c>
-      <c r="F65" t="s">
-        <v>951</v>
-      </c>
-      <c r="G65" t="s">
-        <v>539</v>
-      </c>
-      <c r="H65" t="s">
-        <v>540</v>
-      </c>
-      <c r="I65" t="s">
-        <v>868</v>
-      </c>
-      <c r="J65" t="s">
-        <v>537</v>
-      </c>
-      <c r="K65" t="s">
-        <v>538</v>
-      </c>
-      <c r="L65" t="s">
-        <v>1055</v>
-      </c>
-      <c r="M65" t="s">
-        <v>541</v>
-      </c>
-      <c r="N65" t="s">
-        <v>542</v>
       </c>
       <c r="P65"/>
       <c r="Q65"/>
@@ -6933,101 +6986,94 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>537</v>
+      </c>
+      <c r="B66" t="s">
+        <v>799</v>
+      </c>
+      <c r="C66" t="s">
+        <v>539</v>
+      </c>
+      <c r="D66" t="s">
+        <v>538</v>
+      </c>
+      <c r="E66" t="s">
+        <v>539</v>
+      </c>
+      <c r="F66" t="s">
+        <v>962</v>
+      </c>
+      <c r="G66" t="s">
+        <v>540</v>
+      </c>
+      <c r="H66" t="s">
+        <v>541</v>
+      </c>
+      <c r="I66" t="s">
+        <v>539</v>
+      </c>
+      <c r="J66" t="s">
+        <v>538</v>
+      </c>
+      <c r="K66" t="s">
+        <v>539</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M66" t="s">
+        <v>542</v>
+      </c>
+      <c r="N66" t="s">
         <v>543</v>
-      </c>
-      <c r="B66" t="s">
-        <v>800</v>
-      </c>
-      <c r="C66" t="s">
-        <v>869</v>
-      </c>
-      <c r="D66" t="s">
-        <v>544</v>
-      </c>
-      <c r="E66" t="s">
-        <v>545</v>
-      </c>
-      <c r="F66" t="s">
-        <v>952</v>
-      </c>
-      <c r="G66" t="s">
-        <v>546</v>
-      </c>
-      <c r="H66" t="s">
-        <v>547</v>
-      </c>
-      <c r="I66" t="s">
-        <v>869</v>
-      </c>
-      <c r="J66" t="s">
-        <v>544</v>
-      </c>
-      <c r="K66" t="s">
-        <v>545</v>
-      </c>
-      <c r="L66" t="s">
-        <v>1056</v>
-      </c>
-      <c r="M66" t="s">
-        <v>548</v>
-      </c>
-      <c r="N66" t="s">
-        <v>549</v>
       </c>
       <c r="P66"/>
       <c r="Q66"/>
-      <c r="R66" t="s">
-        <v>1122</v>
-      </c>
-      <c r="S66" t="s">
-        <v>550</v>
-      </c>
-      <c r="T66" t="s">
-        <v>551</v>
-      </c>
+      <c r="S66"/>
+      <c r="T66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s">
-        <v>790</v>
+        <v>817</v>
       </c>
       <c r="C67" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="D67" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="E67" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="F67" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="G67" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="H67" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="I67" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="J67" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="K67" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="L67" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="M67" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="N67" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="P67"/>
       <c r="Q67"/>
@@ -7036,737 +7082,744 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B68" t="s">
-        <v>791</v>
+        <v>809</v>
       </c>
       <c r="C68" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="D68" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E68" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="F68" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="G68" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="H68" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="I68" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="J68" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="K68" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="L68" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="M68" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="N68" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="P68"/>
       <c r="Q68"/>
-      <c r="S68"/>
-      <c r="T68"/>
+      <c r="R68" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S68" t="s">
+        <v>558</v>
+      </c>
+      <c r="T68" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>560</v>
+      </c>
+      <c r="B69" t="s">
+        <v>799</v>
+      </c>
+      <c r="C69" t="s">
+        <v>882</v>
+      </c>
+      <c r="D69" t="s">
+        <v>561</v>
+      </c>
+      <c r="E69" t="s">
+        <v>562</v>
+      </c>
+      <c r="F69" t="s">
+        <v>965</v>
+      </c>
+      <c r="G69" t="s">
+        <v>563</v>
+      </c>
+      <c r="H69" t="s">
+        <v>564</v>
+      </c>
+      <c r="I69" t="s">
+        <v>882</v>
+      </c>
+      <c r="J69" t="s">
+        <v>561</v>
+      </c>
+      <c r="K69" t="s">
+        <v>562</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M69" t="s">
+        <v>565</v>
+      </c>
+      <c r="N69" t="s">
         <v>566</v>
-      </c>
-      <c r="B69" t="s">
-        <v>783</v>
-      </c>
-      <c r="C69" t="s">
-        <v>872</v>
-      </c>
-      <c r="D69" t="s">
-        <v>567</v>
-      </c>
-      <c r="E69" t="s">
-        <v>568</v>
-      </c>
-      <c r="F69" t="s">
-        <v>955</v>
-      </c>
-      <c r="G69" t="s">
-        <v>569</v>
-      </c>
-      <c r="H69" t="s">
-        <v>570</v>
-      </c>
-      <c r="I69" t="s">
-        <v>989</v>
-      </c>
-      <c r="J69" t="s">
-        <v>571</v>
-      </c>
-      <c r="K69" t="s">
-        <v>572</v>
-      </c>
-      <c r="L69" t="s">
-        <v>1059</v>
-      </c>
-      <c r="M69" t="s">
-        <v>573</v>
-      </c>
-      <c r="N69" t="s">
-        <v>574</v>
       </c>
       <c r="P69"/>
       <c r="Q69"/>
-      <c r="R69" t="s">
-        <v>1123</v>
-      </c>
-      <c r="S69" t="s">
-        <v>575</v>
-      </c>
-      <c r="T69" t="s">
-        <v>576</v>
-      </c>
+      <c r="S69"/>
+      <c r="T69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="B70" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="C70" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="D70" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="E70" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="F70" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="G70" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="H70" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="I70" t="s">
-        <v>990</v>
+        <v>883</v>
       </c>
       <c r="J70" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="K70" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="L70" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="M70" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="N70" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="P70"/>
       <c r="Q70"/>
-      <c r="R70" t="s">
-        <v>1124</v>
-      </c>
-      <c r="S70" t="s">
-        <v>586</v>
-      </c>
-      <c r="T70" t="s">
-        <v>587</v>
-      </c>
+      <c r="S70"/>
+      <c r="T70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="B71" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C71" t="s">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="D71" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="E71" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="F71" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="G71" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="H71" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="I71" t="s">
-        <v>874</v>
+        <v>1001</v>
       </c>
       <c r="J71" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="K71" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="L71" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="M71" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="N71" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="P71"/>
       <c r="Q71"/>
       <c r="R71" t="s">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="S71" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="T71" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B72" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C72" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="D72" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="E72" t="s">
-        <v>599</v>
-      </c>
-      <c r="G72"/>
-      <c r="H72"/>
+        <v>587</v>
+      </c>
+      <c r="F72" t="s">
+        <v>968</v>
+      </c>
+      <c r="G72" t="s">
+        <v>588</v>
+      </c>
+      <c r="H72" t="s">
+        <v>589</v>
+      </c>
       <c r="I72" t="s">
-        <v>875</v>
+        <v>1002</v>
       </c>
       <c r="J72" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K72" t="s">
-        <v>599</v>
-      </c>
-      <c r="M72"/>
-      <c r="N72"/>
+        <v>591</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M72" t="s">
+        <v>592</v>
+      </c>
+      <c r="N72" t="s">
+        <v>593</v>
+      </c>
       <c r="P72"/>
       <c r="Q72"/>
-      <c r="S72"/>
-      <c r="T72"/>
+      <c r="R72" t="s">
+        <v>1137</v>
+      </c>
+      <c r="S72" t="s">
+        <v>594</v>
+      </c>
+      <c r="T72" t="s">
+        <v>595</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>596</v>
+      </c>
+      <c r="B73" t="s">
+        <v>792</v>
+      </c>
+      <c r="C73" t="s">
+        <v>886</v>
+      </c>
+      <c r="D73" t="s">
+        <v>597</v>
+      </c>
+      <c r="E73" t="s">
+        <v>598</v>
+      </c>
+      <c r="F73" t="s">
+        <v>969</v>
+      </c>
+      <c r="G73" t="s">
+        <v>599</v>
+      </c>
+      <c r="H73" t="s">
         <v>600</v>
       </c>
-      <c r="B73" t="s">
-        <v>808</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="I73" t="s">
+        <v>886</v>
+      </c>
+      <c r="J73" t="s">
+        <v>597</v>
+      </c>
+      <c r="K73" t="s">
+        <v>598</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1074</v>
+      </c>
+      <c r="M73" t="s">
+        <v>601</v>
+      </c>
+      <c r="N73" t="s">
         <v>602</v>
-      </c>
-      <c r="D73" t="s">
-        <v>601</v>
-      </c>
-      <c r="E73" t="s">
-        <v>602</v>
-      </c>
-      <c r="F73" t="s">
-        <v>958</v>
-      </c>
-      <c r="G73" t="s">
-        <v>603</v>
-      </c>
-      <c r="H73" t="s">
-        <v>604</v>
-      </c>
-      <c r="I73" t="s">
-        <v>602</v>
-      </c>
-      <c r="J73" t="s">
-        <v>601</v>
-      </c>
-      <c r="K73" t="s">
-        <v>602</v>
-      </c>
-      <c r="L73" t="s">
-        <v>1062</v>
-      </c>
-      <c r="M73" t="s">
-        <v>605</v>
-      </c>
-      <c r="N73" t="s">
-        <v>606</v>
       </c>
       <c r="P73"/>
       <c r="Q73"/>
       <c r="R73" t="s">
-        <v>1126</v>
+        <v>1138</v>
       </c>
       <c r="S73" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="T73" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B74" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C74" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="D74" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E74" t="s">
-        <v>611</v>
-      </c>
-      <c r="F74" t="s">
-        <v>959</v>
-      </c>
-      <c r="G74" t="s">
-        <v>612</v>
-      </c>
-      <c r="H74" t="s">
-        <v>613</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="G74"/>
+      <c r="H74"/>
       <c r="I74" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="J74" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="K74" t="s">
-        <v>611</v>
-      </c>
-      <c r="L74" t="s">
-        <v>1063</v>
-      </c>
-      <c r="M74" t="s">
-        <v>614</v>
-      </c>
-      <c r="N74" t="s">
-        <v>615</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="M74"/>
+      <c r="N74"/>
       <c r="P74"/>
       <c r="Q74"/>
-      <c r="R74" t="s">
-        <v>1127</v>
-      </c>
-      <c r="S74" t="s">
-        <v>616</v>
-      </c>
-      <c r="T74" t="s">
-        <v>617</v>
-      </c>
+      <c r="S74"/>
+      <c r="T74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="B75" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="C75" t="s">
-        <v>877</v>
+        <v>610</v>
       </c>
       <c r="D75" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="E75" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="F75" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="G75" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="H75" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="I75" t="s">
-        <v>991</v>
+        <v>610</v>
       </c>
       <c r="J75" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="K75" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="L75" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="M75" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="N75" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="P75"/>
       <c r="Q75"/>
       <c r="R75" t="s">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="S75" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="T75" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B76" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C76" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="D76" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="E76" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="F76" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="G76" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="H76" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="I76" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="J76" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="K76" t="s">
-        <v>631</v>
-      </c>
-      <c r="M76"/>
-      <c r="N76"/>
+        <v>619</v>
+      </c>
+      <c r="L76" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M76" t="s">
+        <v>622</v>
+      </c>
+      <c r="N76" t="s">
+        <v>623</v>
+      </c>
       <c r="P76"/>
       <c r="Q76"/>
-      <c r="S76"/>
-      <c r="T76"/>
+      <c r="R76" t="s">
+        <v>1140</v>
+      </c>
+      <c r="S76" t="s">
+        <v>624</v>
+      </c>
+      <c r="T76" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="B77" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="C77" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="D77" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="E77" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F77" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="G77" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="H77" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="I77" t="s">
-        <v>879</v>
+        <v>1003</v>
       </c>
       <c r="J77" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="K77" t="s">
-        <v>637</v>
-      </c>
-      <c r="M77"/>
-      <c r="N77"/>
+        <v>632</v>
+      </c>
+      <c r="L77" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M77" t="s">
+        <v>633</v>
+      </c>
+      <c r="N77" t="s">
+        <v>634</v>
+      </c>
       <c r="P77"/>
       <c r="Q77"/>
-      <c r="S77"/>
-      <c r="T77"/>
+      <c r="R77" t="s">
+        <v>1141</v>
+      </c>
+      <c r="S77" t="s">
+        <v>635</v>
+      </c>
+      <c r="T77" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>637</v>
+      </c>
+      <c r="B78" t="s">
+        <v>792</v>
+      </c>
+      <c r="C78" t="s">
+        <v>890</v>
+      </c>
+      <c r="D78" t="s">
+        <v>638</v>
+      </c>
+      <c r="E78" t="s">
+        <v>639</v>
+      </c>
+      <c r="F78" t="s">
+        <v>973</v>
+      </c>
+      <c r="G78" t="s">
         <v>640</v>
       </c>
-      <c r="B78" t="s">
-        <v>783</v>
-      </c>
-      <c r="C78" t="s">
-        <v>880</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="H78" t="s">
         <v>641</v>
       </c>
-      <c r="E78" t="s">
+      <c r="I78" t="s">
+        <v>890</v>
+      </c>
+      <c r="J78" t="s">
         <v>642</v>
       </c>
-      <c r="F78" t="s">
-        <v>963</v>
-      </c>
-      <c r="G78" t="s">
-        <v>643</v>
-      </c>
-      <c r="H78" t="s">
-        <v>644</v>
-      </c>
-      <c r="I78" t="s">
-        <v>880</v>
-      </c>
-      <c r="J78" t="s">
-        <v>641</v>
-      </c>
       <c r="K78" t="s">
-        <v>642</v>
-      </c>
-      <c r="L78" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M78" t="s">
-        <v>645</v>
-      </c>
-      <c r="N78" t="s">
-        <v>646</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="M78"/>
+      <c r="N78"/>
       <c r="P78"/>
       <c r="Q78"/>
-      <c r="R78" t="s">
-        <v>1129</v>
-      </c>
-      <c r="S78" t="s">
-        <v>647</v>
-      </c>
-      <c r="T78" t="s">
-        <v>648</v>
-      </c>
+      <c r="S78"/>
+      <c r="T78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B79" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="C79" t="s">
-        <v>881</v>
+        <v>891</v>
       </c>
       <c r="D79" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E79" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="F79" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="G79" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="H79" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="I79" t="s">
-        <v>992</v>
+        <v>891</v>
       </c>
       <c r="J79" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="K79" t="s">
-        <v>655</v>
-      </c>
-      <c r="L79" t="s">
-        <v>1066</v>
-      </c>
-      <c r="M79" t="s">
-        <v>656</v>
-      </c>
-      <c r="N79" t="s">
-        <v>657</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="M79"/>
+      <c r="N79"/>
       <c r="P79"/>
       <c r="Q79"/>
-      <c r="R79" t="s">
-        <v>1130</v>
-      </c>
-      <c r="S79" t="s">
-        <v>658</v>
-      </c>
-      <c r="T79" t="s">
-        <v>659</v>
-      </c>
+      <c r="S79"/>
+      <c r="T79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="B80" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="C80" t="s">
-        <v>882</v>
+        <v>892</v>
       </c>
       <c r="D80" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="E80" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="F80" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="G80" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="H80" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="I80" t="s">
-        <v>882</v>
+        <v>892</v>
       </c>
       <c r="J80" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="K80" t="s">
-        <v>662</v>
-      </c>
-      <c r="M80"/>
-      <c r="N80"/>
+        <v>650</v>
+      </c>
+      <c r="L80" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M80" t="s">
+        <v>653</v>
+      </c>
+      <c r="N80" t="s">
+        <v>654</v>
+      </c>
       <c r="P80"/>
       <c r="Q80"/>
-      <c r="S80"/>
-      <c r="T80"/>
+      <c r="R80" t="s">
+        <v>1142</v>
+      </c>
+      <c r="S80" t="s">
+        <v>655</v>
+      </c>
+      <c r="T80" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>657</v>
+      </c>
+      <c r="B81" t="s">
+        <v>821</v>
+      </c>
+      <c r="C81" t="s">
+        <v>893</v>
+      </c>
+      <c r="D81" t="s">
+        <v>658</v>
+      </c>
+      <c r="E81" t="s">
+        <v>659</v>
+      </c>
+      <c r="F81" t="s">
+        <v>976</v>
+      </c>
+      <c r="G81" t="s">
+        <v>660</v>
+      </c>
+      <c r="H81" t="s">
+        <v>661</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J81" t="s">
+        <v>662</v>
+      </c>
+      <c r="K81" t="s">
+        <v>663</v>
+      </c>
+      <c r="L81" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M81" t="s">
+        <v>664</v>
+      </c>
+      <c r="N81" t="s">
         <v>665</v>
       </c>
-      <c r="B81" t="s">
-        <v>783</v>
-      </c>
-      <c r="C81" t="s">
-        <v>883</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81" t="s">
+        <v>1143</v>
+      </c>
+      <c r="S81" t="s">
         <v>666</v>
       </c>
-      <c r="E81" t="s">
+      <c r="T81" t="s">
         <v>667</v>
       </c>
-      <c r="F81" t="s">
-        <v>966</v>
-      </c>
-      <c r="G81" t="s">
-        <v>668</v>
-      </c>
-      <c r="H81" t="s">
-        <v>669</v>
-      </c>
-      <c r="I81" t="s">
-        <v>993</v>
-      </c>
-      <c r="J81" t="s">
-        <v>670</v>
-      </c>
-      <c r="K81" t="s">
-        <v>671</v>
-      </c>
-      <c r="L81" t="s">
-        <v>1067</v>
-      </c>
-      <c r="M81" t="s">
-        <v>672</v>
-      </c>
-      <c r="N81" t="s">
-        <v>673</v>
-      </c>
-      <c r="O81" t="s">
-        <v>1076</v>
-      </c>
-      <c r="P81" t="s">
-        <v>674</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>675</v>
-      </c>
-      <c r="S81"/>
-      <c r="T81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B82" t="s">
-        <v>783</v>
+        <v>822</v>
       </c>
       <c r="C82" t="s">
-        <v>678</v>
+        <v>894</v>
       </c>
       <c r="D82" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="E82" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F82" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="G82" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="H82" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="I82" t="s">
-        <v>994</v>
+        <v>894</v>
       </c>
       <c r="J82" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="K82" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="M82"/>
       <c r="N82"/>
@@ -7777,78 +7830,92 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>673</v>
+      </c>
+      <c r="B83" t="s">
+        <v>792</v>
+      </c>
+      <c r="C83" t="s">
+        <v>895</v>
+      </c>
+      <c r="D83" t="s">
+        <v>674</v>
+      </c>
+      <c r="E83" t="s">
+        <v>675</v>
+      </c>
+      <c r="F83" t="s">
+        <v>978</v>
+      </c>
+      <c r="G83" t="s">
+        <v>676</v>
+      </c>
+      <c r="H83" t="s">
+        <v>677</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J83" t="s">
+        <v>678</v>
+      </c>
+      <c r="K83" t="s">
+        <v>679</v>
+      </c>
+      <c r="L83" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M83" t="s">
+        <v>680</v>
+      </c>
+      <c r="N83" t="s">
+        <v>681</v>
+      </c>
+      <c r="O83" t="s">
+        <v>1089</v>
+      </c>
+      <c r="P83" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q83" t="s">
         <v>683</v>
       </c>
-      <c r="B83" t="s">
-        <v>783</v>
-      </c>
-      <c r="C83" t="s">
-        <v>884</v>
-      </c>
-      <c r="D83" t="s">
-        <v>175</v>
-      </c>
-      <c r="E83" t="s">
-        <v>684</v>
-      </c>
-      <c r="F83" t="s">
-        <v>968</v>
-      </c>
-      <c r="G83" t="s">
-        <v>685</v>
-      </c>
-      <c r="H83" t="s">
-        <v>686</v>
-      </c>
-      <c r="I83" t="s">
-        <v>492</v>
-      </c>
-      <c r="J83" t="s">
-        <v>492</v>
-      </c>
-      <c r="K83" t="s">
-        <v>492</v>
-      </c>
-      <c r="M83"/>
-      <c r="N83"/>
-      <c r="P83"/>
-      <c r="Q83"/>
       <c r="S83"/>
       <c r="T83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>684</v>
+      </c>
+      <c r="B84" t="s">
+        <v>792</v>
+      </c>
+      <c r="C84" t="s">
+        <v>686</v>
+      </c>
+      <c r="D84" t="s">
+        <v>685</v>
+      </c>
+      <c r="E84" t="s">
+        <v>686</v>
+      </c>
+      <c r="F84" t="s">
+        <v>979</v>
+      </c>
+      <c r="G84" t="s">
         <v>687</v>
       </c>
-      <c r="B84" t="s">
-        <v>787</v>
-      </c>
-      <c r="C84" t="s">
-        <v>885</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="H84" t="s">
         <v>688</v>
       </c>
-      <c r="E84" t="s">
+      <c r="I84" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J84" t="s">
         <v>689</v>
       </c>
-      <c r="F84" t="s">
-        <v>969</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="K84" t="s">
         <v>690</v>
-      </c>
-      <c r="H84" t="s">
-        <v>691</v>
-      </c>
-      <c r="I84" t="s">
-        <v>995</v>
-      </c>
-      <c r="J84" t="s">
-        <v>692</v>
-      </c>
-      <c r="K84" t="s">
-        <v>693</v>
       </c>
       <c r="M84"/>
       <c r="N84"/>
@@ -7859,85 +7926,78 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>691</v>
+      </c>
+      <c r="B85" t="s">
+        <v>792</v>
+      </c>
+      <c r="C85" t="s">
+        <v>896</v>
+      </c>
+      <c r="D85" t="s">
+        <v>180</v>
+      </c>
+      <c r="E85" t="s">
+        <v>692</v>
+      </c>
+      <c r="F85" t="s">
+        <v>980</v>
+      </c>
+      <c r="G85" t="s">
+        <v>693</v>
+      </c>
+      <c r="H85" t="s">
         <v>694</v>
       </c>
-      <c r="B85" t="s">
-        <v>783</v>
-      </c>
-      <c r="C85" t="s">
-        <v>119</v>
-      </c>
-      <c r="D85" t="s">
-        <v>118</v>
-      </c>
-      <c r="E85" t="s">
-        <v>119</v>
-      </c>
-      <c r="F85" t="s">
-        <v>970</v>
-      </c>
-      <c r="G85" t="s">
-        <v>695</v>
-      </c>
-      <c r="H85" t="s">
-        <v>696</v>
-      </c>
       <c r="I85" t="s">
-        <v>996</v>
+        <v>500</v>
       </c>
       <c r="J85" t="s">
-        <v>697</v>
+        <v>500</v>
       </c>
       <c r="K85" t="s">
-        <v>698</v>
-      </c>
-      <c r="L85" t="s">
-        <v>1068</v>
-      </c>
-      <c r="M85" t="s">
-        <v>699</v>
-      </c>
-      <c r="N85" t="s">
-        <v>700</v>
-      </c>
-      <c r="O85" t="s">
-        <v>1077</v>
-      </c>
-      <c r="P85" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>702</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="M85"/>
+      <c r="N85"/>
+      <c r="P85"/>
+      <c r="Q85"/>
       <c r="S85"/>
       <c r="T85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B86" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="C86" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="D86" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="E86" t="s">
-        <v>705</v>
-      </c>
-      <c r="G86"/>
-      <c r="H86"/>
+        <v>697</v>
+      </c>
+      <c r="F86" t="s">
+        <v>981</v>
+      </c>
+      <c r="G86" t="s">
+        <v>698</v>
+      </c>
+      <c r="H86" t="s">
+        <v>699</v>
+      </c>
       <c r="I86" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="J86" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="K86" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="M86"/>
       <c r="N86"/>
@@ -7948,71 +8008,85 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>702</v>
+      </c>
+      <c r="B87" t="s">
+        <v>792</v>
+      </c>
+      <c r="C87" t="s">
+        <v>124</v>
+      </c>
+      <c r="D87" t="s">
+        <v>123</v>
+      </c>
+      <c r="E87" t="s">
+        <v>124</v>
+      </c>
+      <c r="F87" t="s">
+        <v>982</v>
+      </c>
+      <c r="G87" t="s">
+        <v>703</v>
+      </c>
+      <c r="H87" t="s">
+        <v>704</v>
+      </c>
+      <c r="I87" t="s">
+        <v>1008</v>
+      </c>
+      <c r="J87" t="s">
+        <v>705</v>
+      </c>
+      <c r="K87" t="s">
+        <v>706</v>
+      </c>
+      <c r="L87" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M87" t="s">
+        <v>707</v>
+      </c>
+      <c r="N87" t="s">
         <v>708</v>
       </c>
-      <c r="B87" t="s">
-        <v>783</v>
-      </c>
-      <c r="C87" t="s">
-        <v>887</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="O87" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P87" t="s">
         <v>709</v>
       </c>
-      <c r="E87" t="s">
+      <c r="Q87" t="s">
         <v>710</v>
       </c>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87" t="s">
-        <v>998</v>
-      </c>
-      <c r="J87" t="s">
-        <v>711</v>
-      </c>
-      <c r="K87" t="s">
-        <v>712</v>
-      </c>
-      <c r="M87"/>
-      <c r="N87"/>
-      <c r="P87"/>
-      <c r="Q87"/>
       <c r="S87"/>
       <c r="T87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>711</v>
+      </c>
+      <c r="B88" t="s">
+        <v>792</v>
+      </c>
+      <c r="C88" t="s">
+        <v>898</v>
+      </c>
+      <c r="D88" t="s">
+        <v>712</v>
+      </c>
+      <c r="E88" t="s">
         <v>713</v>
       </c>
-      <c r="B88" t="s">
-        <v>783</v>
-      </c>
-      <c r="C88" t="s">
-        <v>888</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J88" t="s">
         <v>714</v>
       </c>
-      <c r="E88" t="s">
+      <c r="K88" t="s">
         <v>715</v>
-      </c>
-      <c r="F88" t="s">
-        <v>971</v>
-      </c>
-      <c r="G88" t="s">
-        <v>716</v>
-      </c>
-      <c r="H88" t="s">
-        <v>717</v>
-      </c>
-      <c r="I88" t="s">
-        <v>999</v>
-      </c>
-      <c r="J88" t="s">
-        <v>718</v>
-      </c>
-      <c r="K88" t="s">
-        <v>719</v>
       </c>
       <c r="M88"/>
       <c r="N88"/>
@@ -8023,24 +8097,31 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B89" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C89" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="D89" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="E89" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
-      <c r="J89"/>
-      <c r="K89"/>
+      <c r="I89" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J89" t="s">
+        <v>719</v>
+      </c>
+      <c r="K89" t="s">
+        <v>720</v>
+      </c>
       <c r="M89"/>
       <c r="N89"/>
       <c r="P89"/>
@@ -8050,24 +8131,31 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>721</v>
+      </c>
+      <c r="B90" t="s">
+        <v>792</v>
+      </c>
+      <c r="C90" t="s">
+        <v>900</v>
+      </c>
+      <c r="D90" t="s">
+        <v>722</v>
+      </c>
+      <c r="E90" t="s">
         <v>723</v>
       </c>
-      <c r="B90" t="s">
-        <v>783</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="F90" t="s">
+        <v>983</v>
+      </c>
+      <c r="G90" t="s">
+        <v>724</v>
+      </c>
+      <c r="H90" t="s">
         <v>725</v>
       </c>
-      <c r="D90" t="s">
-        <v>724</v>
-      </c>
-      <c r="E90" t="s">
-        <v>725</v>
-      </c>
-      <c r="G90"/>
-      <c r="H90"/>
       <c r="I90" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="J90" t="s">
         <v>726</v>
@@ -8087,28 +8175,21 @@
         <v>728</v>
       </c>
       <c r="B91" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C91" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="D91" t="s">
-        <v>704</v>
+        <v>729</v>
       </c>
       <c r="E91" t="s">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
-      <c r="I91" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J91" t="s">
-        <v>729</v>
-      </c>
-      <c r="K91" t="s">
-        <v>730</v>
-      </c>
+      <c r="J91"/>
+      <c r="K91"/>
       <c r="M91"/>
       <c r="N91"/>
       <c r="P91"/>
@@ -8121,10 +8202,10 @@
         <v>731</v>
       </c>
       <c r="B92" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="C92" t="s">
-        <v>890</v>
+        <v>733</v>
       </c>
       <c r="D92" t="s">
         <v>732</v>
@@ -8132,78 +8213,50 @@
       <c r="E92" t="s">
         <v>733</v>
       </c>
-      <c r="F92" t="s">
-        <v>972</v>
-      </c>
-      <c r="G92" t="s">
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J92" t="s">
         <v>734</v>
       </c>
-      <c r="H92" t="s">
+      <c r="K92" t="s">
         <v>735</v>
       </c>
-      <c r="I92" t="s">
-        <v>890</v>
-      </c>
-      <c r="J92" t="s">
-        <v>732</v>
-      </c>
-      <c r="K92" t="s">
-        <v>733</v>
-      </c>
-      <c r="L92" t="s">
-        <v>1069</v>
-      </c>
-      <c r="M92" t="s">
-        <v>736</v>
-      </c>
-      <c r="N92" t="s">
-        <v>737</v>
-      </c>
+      <c r="M92"/>
+      <c r="N92"/>
       <c r="P92"/>
       <c r="Q92"/>
-      <c r="R92" t="s">
-        <v>1122</v>
-      </c>
-      <c r="S92" t="s">
-        <v>550</v>
-      </c>
-      <c r="T92" t="s">
-        <v>551</v>
-      </c>
+      <c r="S92"/>
+      <c r="T92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>736</v>
+      </c>
+      <c r="B93" t="s">
+        <v>796</v>
+      </c>
+      <c r="C93" t="s">
+        <v>898</v>
+      </c>
+      <c r="D93" t="s">
+        <v>712</v>
+      </c>
+      <c r="E93" t="s">
+        <v>713</v>
+      </c>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="I93" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J93" t="s">
+        <v>737</v>
+      </c>
+      <c r="K93" t="s">
         <v>738</v>
-      </c>
-      <c r="B93" t="s">
-        <v>814</v>
-      </c>
-      <c r="C93" t="s">
-        <v>891</v>
-      </c>
-      <c r="D93" t="s">
-        <v>739</v>
-      </c>
-      <c r="E93" t="s">
-        <v>740</v>
-      </c>
-      <c r="F93" t="s">
-        <v>973</v>
-      </c>
-      <c r="G93" t="s">
-        <v>741</v>
-      </c>
-      <c r="H93" t="s">
-        <v>742</v>
-      </c>
-      <c r="I93" t="s">
-        <v>891</v>
-      </c>
-      <c r="J93" t="s">
-        <v>739</v>
-      </c>
-      <c r="K93" t="s">
-        <v>740</v>
       </c>
       <c r="M93"/>
       <c r="N93"/>
@@ -8214,242 +8267,338 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>739</v>
+      </c>
+      <c r="B94" t="s">
+        <v>823</v>
+      </c>
+      <c r="C94" t="s">
+        <v>902</v>
+      </c>
+      <c r="D94" t="s">
+        <v>740</v>
+      </c>
+      <c r="E94" t="s">
+        <v>741</v>
+      </c>
+      <c r="F94" t="s">
+        <v>984</v>
+      </c>
+      <c r="G94" t="s">
+        <v>742</v>
+      </c>
+      <c r="H94" t="s">
         <v>743</v>
       </c>
-      <c r="B94" t="s">
-        <v>815</v>
-      </c>
-      <c r="C94" t="s">
-        <v>892</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="I94" t="s">
+        <v>902</v>
+      </c>
+      <c r="J94" t="s">
+        <v>740</v>
+      </c>
+      <c r="K94" t="s">
+        <v>741</v>
+      </c>
+      <c r="L94" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M94" t="s">
         <v>744</v>
       </c>
-      <c r="E94" t="s">
+      <c r="N94" t="s">
         <v>745</v>
-      </c>
-      <c r="F94" t="s">
-        <v>974</v>
-      </c>
-      <c r="G94" t="s">
-        <v>746</v>
-      </c>
-      <c r="H94" t="s">
-        <v>747</v>
-      </c>
-      <c r="J94"/>
-      <c r="K94"/>
-      <c r="L94" t="s">
-        <v>1070</v>
-      </c>
-      <c r="M94" t="s">
-        <v>748</v>
-      </c>
-      <c r="N94" t="s">
-        <v>749</v>
       </c>
       <c r="P94"/>
       <c r="Q94"/>
       <c r="R94" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="S94" t="s">
-        <v>750</v>
+        <v>558</v>
       </c>
       <c r="T94" t="s">
-        <v>751</v>
+        <v>559</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B95" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="C95" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="D95" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="E95" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="F95" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="G95" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="H95" t="s">
-        <v>756</v>
-      </c>
-      <c r="J95"/>
-      <c r="K95"/>
-      <c r="L95" t="s">
-        <v>1071</v>
-      </c>
-      <c r="M95" t="s">
-        <v>757</v>
-      </c>
-      <c r="N95" t="s">
-        <v>758</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="I95" t="s">
+        <v>903</v>
+      </c>
+      <c r="J95" t="s">
+        <v>747</v>
+      </c>
+      <c r="K95" t="s">
+        <v>748</v>
+      </c>
+      <c r="M95"/>
+      <c r="N95"/>
       <c r="P95"/>
       <c r="Q95"/>
-      <c r="R95" t="s">
-        <v>1131</v>
-      </c>
-      <c r="S95" t="s">
-        <v>750</v>
-      </c>
-      <c r="T95" t="s">
-        <v>751</v>
-      </c>
+      <c r="S95"/>
+      <c r="T95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B96" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="C96" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="D96" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E96" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="F96" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="G96" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="H96" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
       <c r="M96" t="s">
+        <v>756</v>
+      </c>
+      <c r="N96" t="s">
         <v>757</v>
-      </c>
-      <c r="N96" t="s">
-        <v>758</v>
       </c>
       <c r="P96"/>
       <c r="Q96"/>
       <c r="R96" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="S96" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="T96" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>760</v>
+      </c>
+      <c r="B97" t="s">
+        <v>825</v>
+      </c>
+      <c r="C97" t="s">
+        <v>905</v>
+      </c>
+      <c r="D97" t="s">
+        <v>761</v>
+      </c>
+      <c r="E97" t="s">
+        <v>762</v>
+      </c>
+      <c r="F97" t="s">
+        <v>987</v>
+      </c>
+      <c r="G97" t="s">
+        <v>763</v>
+      </c>
+      <c r="H97" t="s">
         <v>764</v>
-      </c>
-      <c r="B97" t="s">
-        <v>816</v>
-      </c>
-      <c r="C97" t="s">
-        <v>895</v>
-      </c>
-      <c r="D97" t="s">
-        <v>765</v>
-      </c>
-      <c r="E97" t="s">
-        <v>766</v>
-      </c>
-      <c r="F97" t="s">
-        <v>977</v>
-      </c>
-      <c r="G97" t="s">
-        <v>767</v>
-      </c>
-      <c r="H97" t="s">
-        <v>768</v>
       </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="M97" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="N97" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="P97"/>
       <c r="Q97"/>
       <c r="R97" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="S97" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="T97" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>767</v>
+      </c>
+      <c r="B98" t="s">
+        <v>825</v>
+      </c>
+      <c r="C98" t="s">
+        <v>906</v>
+      </c>
+      <c r="D98" t="s">
+        <v>768</v>
+      </c>
+      <c r="E98" t="s">
+        <v>769</v>
+      </c>
+      <c r="F98" t="s">
+        <v>988</v>
+      </c>
+      <c r="G98" t="s">
+        <v>770</v>
+      </c>
+      <c r="H98" t="s">
         <v>771</v>
-      </c>
-      <c r="B98" t="s">
-        <v>816</v>
-      </c>
-      <c r="C98" t="s">
-        <v>896</v>
-      </c>
-      <c r="D98" t="s">
-        <v>772</v>
-      </c>
-      <c r="E98" t="s">
-        <v>773</v>
-      </c>
-      <c r="F98" t="s">
-        <v>978</v>
-      </c>
-      <c r="G98" t="s">
-        <v>774</v>
-      </c>
-      <c r="H98" t="s">
-        <v>775</v>
       </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="M98" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="N98" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="P98"/>
       <c r="Q98"/>
       <c r="R98" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="S98" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="T98" t="s">
-        <v>751</v>
+        <v>759</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>772</v>
+      </c>
+      <c r="B99" t="s">
+        <v>826</v>
+      </c>
+      <c r="C99" t="s">
+        <v>907</v>
+      </c>
+      <c r="D99" t="s">
+        <v>773</v>
+      </c>
+      <c r="E99" t="s">
+        <v>774</v>
+      </c>
+      <c r="F99" t="s">
+        <v>989</v>
+      </c>
+      <c r="G99" t="s">
+        <v>775</v>
+      </c>
+      <c r="H99" t="s">
+        <v>776</v>
+      </c>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M99" t="s">
+        <v>777</v>
+      </c>
+      <c r="N99" t="s">
+        <v>778</v>
+      </c>
+      <c r="P99"/>
+      <c r="Q99"/>
+      <c r="R99" t="s">
+        <v>1144</v>
+      </c>
+      <c r="S99" t="s">
+        <v>758</v>
+      </c>
+      <c r="T99" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>779</v>
+      </c>
+      <c r="B100" t="s">
+        <v>826</v>
+      </c>
+      <c r="C100" t="s">
+        <v>908</v>
+      </c>
+      <c r="D100" t="s">
+        <v>780</v>
+      </c>
+      <c r="E100" t="s">
+        <v>781</v>
+      </c>
+      <c r="F100" t="s">
+        <v>990</v>
+      </c>
+      <c r="G100" t="s">
+        <v>782</v>
+      </c>
+      <c r="H100" t="s">
+        <v>783</v>
+      </c>
+      <c r="J100"/>
+      <c r="K100"/>
+      <c r="L100" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M100" t="s">
+        <v>784</v>
+      </c>
+      <c r="N100" t="s">
+        <v>785</v>
+      </c>
+      <c r="P100"/>
+      <c r="Q100"/>
+      <c r="R100" t="s">
+        <v>1144</v>
+      </c>
+      <c r="S100" t="s">
+        <v>758</v>
+      </c>
+      <c r="T100" t="s">
+        <v>759</v>
       </c>
     </row>
   </sheetData>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">55</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Taunt</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="1150">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">55</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Taunt</t>
@@ -1503,6 +1503,15 @@
   </si>
   <si>
     <t xml:space="preserve">#1は擬態を解いた！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human Guise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">擬人</t>
   </si>
   <si>
     <t xml:space="preserve">105</t>
@@ -2487,6 +2496,9 @@
     <t xml:space="preserve">EA 23.257</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.291</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.268</t>
   </si>
   <si>
@@ -2665,6 +2677,9 @@
   </si>
   <si>
     <t xml:space="preserve">拟态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拟人</t>
   </si>
   <si>
     <t xml:space="preserve">身缠暗影</t>
@@ -3657,10 +3672,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C3" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3669,7 +3684,7 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="G3" t="s">
         <v>24</v>
@@ -3678,7 +3693,7 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="J3" t="s">
         <v>26</v>
@@ -3687,7 +3702,7 @@
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -3698,7 +3713,7 @@
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="S3" t="s">
         <v>30</v>
@@ -3712,10 +3727,10 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C4" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -3724,7 +3739,7 @@
         <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
@@ -3733,7 +3748,7 @@
         <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="J4" t="s">
         <v>33</v>
@@ -3742,7 +3757,7 @@
         <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -3753,7 +3768,7 @@
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="S4" t="s">
         <v>39</v>
@@ -3767,10 +3782,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
@@ -3779,7 +3794,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="G5" t="s">
         <v>44</v>
@@ -3788,7 +3803,7 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="J5" t="s">
         <v>42</v>
@@ -3797,7 +3812,7 @@
         <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -3808,7 +3823,7 @@
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="S5" t="s">
         <v>48</v>
@@ -3822,10 +3837,10 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C6" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -3834,7 +3849,7 @@
         <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="G6" t="s">
         <v>53</v>
@@ -3843,7 +3858,7 @@
         <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="J6" t="s">
         <v>51</v>
@@ -3852,7 +3867,7 @@
         <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="M6" t="s">
         <v>55</v>
@@ -3863,7 +3878,7 @@
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="S6" t="s">
         <v>57</v>
@@ -3877,10 +3892,10 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C7" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -3889,7 +3904,7 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="G7" t="s">
         <v>62</v>
@@ -3898,7 +3913,7 @@
         <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="J7" t="s">
         <v>60</v>
@@ -3907,7 +3922,7 @@
         <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="M7" t="s">
         <v>64</v>
@@ -3918,7 +3933,7 @@
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="S7" t="s">
         <v>66</v>
@@ -3932,10 +3947,10 @@
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C8" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="D8" t="s">
         <v>69</v>
@@ -3944,7 +3959,7 @@
         <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="G8" t="s">
         <v>71</v>
@@ -3953,7 +3968,7 @@
         <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="J8" t="s">
         <v>69</v>
@@ -3962,7 +3977,7 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="M8" t="s">
         <v>73</v>
@@ -3973,7 +3988,7 @@
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="S8" t="s">
         <v>66</v>
@@ -3987,10 +4002,10 @@
         <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C9" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D9" t="s">
         <v>76</v>
@@ -3999,7 +4014,7 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="G9" t="s">
         <v>71</v>
@@ -4008,7 +4023,7 @@
         <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="J9" t="s">
         <v>76</v>
@@ -4017,7 +4032,7 @@
         <v>77</v>
       </c>
       <c r="L9" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="M9" t="s">
         <v>78</v>
@@ -4028,7 +4043,7 @@
       <c r="P9"/>
       <c r="Q9"/>
       <c r="R9" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="S9" t="s">
         <v>66</v>
@@ -4042,7 +4057,7 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C10" t="s">
         <v>82</v>
@@ -4054,7 +4069,7 @@
         <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="G10" t="s">
         <v>83</v>
@@ -4063,7 +4078,7 @@
         <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="J10" t="s">
         <v>85</v>
@@ -4072,7 +4087,7 @@
         <v>86</v>
       </c>
       <c r="L10" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="M10" t="s">
         <v>87</v>
@@ -4081,7 +4096,7 @@
         <v>88</v>
       </c>
       <c r="O10" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="P10" t="s">
         <v>89</v>
@@ -4090,7 +4105,7 @@
         <v>90</v>
       </c>
       <c r="R10" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="S10" t="s">
         <v>91</v>
@@ -4104,10 +4119,10 @@
         <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C11" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -4116,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="G11" t="s">
         <v>96</v>
@@ -4125,7 +4140,7 @@
         <v>97</v>
       </c>
       <c r="I11" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="J11" t="s">
         <v>98</v>
@@ -4134,7 +4149,7 @@
         <v>99</v>
       </c>
       <c r="L11" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="M11" t="s">
         <v>100</v>
@@ -4143,7 +4158,7 @@
         <v>101</v>
       </c>
       <c r="O11" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="P11" t="s">
         <v>102</v>
@@ -4159,10 +4174,10 @@
         <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C12" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D12" t="s">
         <v>105</v>
@@ -4171,7 +4186,7 @@
         <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="G12" t="s">
         <v>107</v>
@@ -4180,7 +4195,7 @@
         <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="J12" t="s">
         <v>105</v>
@@ -4189,7 +4204,7 @@
         <v>106</v>
       </c>
       <c r="L12" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="M12" t="s">
         <v>109</v>
@@ -4200,7 +4215,7 @@
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="S12" t="s">
         <v>111</v>
@@ -4214,10 +4229,10 @@
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C13" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="D13" t="s">
         <v>114</v>
@@ -4226,7 +4241,7 @@
         <v>115</v>
       </c>
       <c r="F13" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="G13" t="s">
         <v>116</v>
@@ -4235,7 +4250,7 @@
         <v>117</v>
       </c>
       <c r="I13" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="J13" t="s">
         <v>114</v>
@@ -4244,7 +4259,7 @@
         <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="M13" t="s">
         <v>118</v>
@@ -4255,7 +4270,7 @@
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="S13" t="s">
         <v>120</v>
@@ -4269,7 +4284,7 @@
         <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C14" t="s">
         <v>124</v>
@@ -4281,7 +4296,7 @@
         <v>124</v>
       </c>
       <c r="F14" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="G14" t="s">
         <v>125</v>
@@ -4299,7 +4314,7 @@
         <v>124</v>
       </c>
       <c r="L14" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="M14" t="s">
         <v>128</v>
@@ -4310,7 +4325,7 @@
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="S14" t="s">
         <v>130</v>
@@ -4324,10 +4339,10 @@
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C15" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -4336,7 +4351,7 @@
         <v>134</v>
       </c>
       <c r="F15" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="G15" t="s">
         <v>135</v>
@@ -4345,7 +4360,7 @@
         <v>136</v>
       </c>
       <c r="I15" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="J15" t="s">
         <v>137</v>
@@ -4354,7 +4369,7 @@
         <v>134</v>
       </c>
       <c r="L15" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="M15" t="s">
         <v>138</v>
@@ -4365,7 +4380,7 @@
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="S15" t="s">
         <v>140</v>
@@ -4379,7 +4394,7 @@
         <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C16" t="s">
         <v>144</v>
@@ -4391,7 +4406,7 @@
         <v>144</v>
       </c>
       <c r="F16" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="G16" t="s">
         <v>145</v>
@@ -4409,7 +4424,7 @@
         <v>144</v>
       </c>
       <c r="L16" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="M16" t="s">
         <v>148</v>
@@ -4420,7 +4435,7 @@
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="S16" t="s">
         <v>150</v>
@@ -4434,10 +4449,10 @@
         <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C17" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D17" t="s">
         <v>153</v>
@@ -4446,7 +4461,7 @@
         <v>154</v>
       </c>
       <c r="F17" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="G17" t="s">
         <v>135</v>
@@ -4455,7 +4470,7 @@
         <v>136</v>
       </c>
       <c r="I17" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="J17" t="s">
         <v>155</v>
@@ -4464,7 +4479,7 @@
         <v>154</v>
       </c>
       <c r="L17" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="M17" t="s">
         <v>156</v>
@@ -4475,7 +4490,7 @@
       <c r="P17"/>
       <c r="Q17"/>
       <c r="R17" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="S17" t="s">
         <v>158</v>
@@ -4489,7 +4504,7 @@
         <v>160</v>
       </c>
       <c r="B18" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C18" t="s">
         <v>162</v>
@@ -4501,7 +4516,7 @@
         <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="G18" t="s">
         <v>163</v>
@@ -4519,7 +4534,7 @@
         <v>162</v>
       </c>
       <c r="L18" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="M18" t="s">
         <v>166</v>
@@ -4530,7 +4545,7 @@
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="S18" t="s">
         <v>168</v>
@@ -4544,10 +4559,10 @@
         <v>170</v>
       </c>
       <c r="B19" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C19" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D19" t="s">
         <v>171</v>
@@ -4556,7 +4571,7 @@
         <v>172</v>
       </c>
       <c r="F19" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="G19" t="s">
         <v>173</v>
@@ -4565,7 +4580,7 @@
         <v>174</v>
       </c>
       <c r="I19" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="J19" t="s">
         <v>171</v>
@@ -4574,7 +4589,7 @@
         <v>172</v>
       </c>
       <c r="L19" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="M19" t="s">
         <v>175</v>
@@ -4585,7 +4600,7 @@
       <c r="P19"/>
       <c r="Q19"/>
       <c r="R19" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="S19" t="s">
         <v>177</v>
@@ -4599,10 +4614,10 @@
         <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C20" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D20" t="s">
         <v>180</v>
@@ -4611,7 +4626,7 @@
         <v>181</v>
       </c>
       <c r="F20" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="G20" t="s">
         <v>182</v>
@@ -4620,7 +4635,7 @@
         <v>183</v>
       </c>
       <c r="I20" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="J20" t="s">
         <v>184</v>
@@ -4629,7 +4644,7 @@
         <v>185</v>
       </c>
       <c r="L20" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="M20" t="s">
         <v>186</v>
@@ -4640,7 +4655,7 @@
       <c r="P20"/>
       <c r="Q20"/>
       <c r="R20" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="S20" t="s">
         <v>188</v>
@@ -4654,7 +4669,7 @@
         <v>190</v>
       </c>
       <c r="B21" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C21" t="s">
         <v>192</v>
@@ -4666,7 +4681,7 @@
         <v>192</v>
       </c>
       <c r="F21" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="G21" t="s">
         <v>193</v>
@@ -4675,7 +4690,7 @@
         <v>194</v>
       </c>
       <c r="I21" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="s">
         <v>195</v>
@@ -4684,7 +4699,7 @@
         <v>196</v>
       </c>
       <c r="L21" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="M21" t="s">
         <v>197</v>
@@ -4695,7 +4710,7 @@
       <c r="P21"/>
       <c r="Q21"/>
       <c r="R21" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="S21" t="s">
         <v>199</v>
@@ -4709,10 +4724,10 @@
         <v>201</v>
       </c>
       <c r="B22" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C22" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="D22" t="s">
         <v>202</v>
@@ -4721,7 +4736,7 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="G22" t="s">
         <v>204</v>
@@ -4730,7 +4745,7 @@
         <v>205</v>
       </c>
       <c r="I22" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="J22" t="s">
         <v>206</v>
@@ -4739,7 +4754,7 @@
         <v>207</v>
       </c>
       <c r="L22" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="M22" t="s">
         <v>208</v>
@@ -4750,7 +4765,7 @@
       <c r="P22"/>
       <c r="Q22"/>
       <c r="R22" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="S22" t="s">
         <v>210</v>
@@ -4764,10 +4779,10 @@
         <v>212</v>
       </c>
       <c r="B23" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C23" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D23" t="s">
         <v>213</v>
@@ -4776,7 +4791,7 @@
         <v>214</v>
       </c>
       <c r="F23" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="G23" t="s">
         <v>215</v>
@@ -4785,7 +4800,7 @@
         <v>216</v>
       </c>
       <c r="I23" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="J23" t="s">
         <v>217</v>
@@ -4794,7 +4809,7 @@
         <v>218</v>
       </c>
       <c r="L23" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="M23" t="s">
         <v>219</v>
@@ -4805,7 +4820,7 @@
       <c r="P23"/>
       <c r="Q23"/>
       <c r="R23" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="S23" t="s">
         <v>221</v>
@@ -4819,10 +4834,10 @@
         <v>223</v>
       </c>
       <c r="B24" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C24" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D24" t="s">
         <v>224</v>
@@ -4831,7 +4846,7 @@
         <v>225</v>
       </c>
       <c r="F24" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="G24" t="s">
         <v>226</v>
@@ -4840,7 +4855,7 @@
         <v>227</v>
       </c>
       <c r="I24" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="J24" t="s">
         <v>228</v>
@@ -4849,7 +4864,7 @@
         <v>229</v>
       </c>
       <c r="L24" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="M24" t="s">
         <v>230</v>
@@ -4860,7 +4875,7 @@
       <c r="P24"/>
       <c r="Q24"/>
       <c r="R24" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="S24" t="s">
         <v>232</v>
@@ -4874,10 +4889,10 @@
         <v>234</v>
       </c>
       <c r="B25" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C25" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D25" t="s">
         <v>235</v>
@@ -4886,7 +4901,7 @@
         <v>236</v>
       </c>
       <c r="F25" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="G25" t="s">
         <v>237</v>
@@ -4895,7 +4910,7 @@
         <v>238</v>
       </c>
       <c r="I25" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="J25" t="s">
         <v>235</v>
@@ -4904,7 +4919,7 @@
         <v>236</v>
       </c>
       <c r="L25" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="M25" t="s">
         <v>239</v>
@@ -4915,7 +4930,7 @@
       <c r="P25"/>
       <c r="Q25"/>
       <c r="R25" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="S25" t="s">
         <v>241</v>
@@ -4929,10 +4944,10 @@
         <v>243</v>
       </c>
       <c r="B26" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C26" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="D26" t="s">
         <v>244</v>
@@ -4941,7 +4956,7 @@
         <v>245</v>
       </c>
       <c r="F26" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="G26" t="s">
         <v>246</v>
@@ -4950,7 +4965,7 @@
         <v>247</v>
       </c>
       <c r="I26" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="J26" t="s">
         <v>244</v>
@@ -4959,7 +4974,7 @@
         <v>245</v>
       </c>
       <c r="L26" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="M26" t="s">
         <v>248</v>
@@ -4977,10 +4992,10 @@
         <v>250</v>
       </c>
       <c r="B27" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C27" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D27" t="s">
         <v>251</v>
@@ -4989,7 +5004,7 @@
         <v>252</v>
       </c>
       <c r="F27" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="G27" t="s">
         <v>253</v>
@@ -4998,7 +5013,7 @@
         <v>254</v>
       </c>
       <c r="I27" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="J27" t="s">
         <v>251</v>
@@ -5007,7 +5022,7 @@
         <v>252</v>
       </c>
       <c r="L27" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="M27" t="s">
         <v>255</v>
@@ -5018,7 +5033,7 @@
       <c r="P27"/>
       <c r="Q27"/>
       <c r="R27" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="S27" t="s">
         <v>257</v>
@@ -5032,10 +5047,10 @@
         <v>259</v>
       </c>
       <c r="B28" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C28" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D28" t="s">
         <v>260</v>
@@ -5044,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="F28" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="G28" t="s">
         <v>262</v>
@@ -5053,7 +5068,7 @@
         <v>263</v>
       </c>
       <c r="I28" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="J28" t="s">
         <v>260</v>
@@ -5062,7 +5077,7 @@
         <v>261</v>
       </c>
       <c r="L28" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="M28" t="s">
         <v>264</v>
@@ -5073,7 +5088,7 @@
       <c r="P28"/>
       <c r="Q28"/>
       <c r="R28" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="S28" t="s">
         <v>266</v>
@@ -5087,10 +5102,10 @@
         <v>268</v>
       </c>
       <c r="B29" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C29" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D29" t="s">
         <v>269</v>
@@ -5099,7 +5114,7 @@
         <v>270</v>
       </c>
       <c r="F29" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="G29" t="s">
         <v>271</v>
@@ -5108,7 +5123,7 @@
         <v>272</v>
       </c>
       <c r="I29" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="J29" t="s">
         <v>269</v>
@@ -5117,7 +5132,7 @@
         <v>270</v>
       </c>
       <c r="L29" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="M29" t="s">
         <v>273</v>
@@ -5128,7 +5143,7 @@
       <c r="P29"/>
       <c r="Q29"/>
       <c r="R29" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="S29" t="s">
         <v>275</v>
@@ -5142,10 +5157,10 @@
         <v>277</v>
       </c>
       <c r="B30" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C30" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="D30" t="s">
         <v>278</v>
@@ -5154,7 +5169,7 @@
         <v>279</v>
       </c>
       <c r="F30" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="G30" t="s">
         <v>280</v>
@@ -5163,7 +5178,7 @@
         <v>281</v>
       </c>
       <c r="I30" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="J30" t="s">
         <v>278</v>
@@ -5172,7 +5187,7 @@
         <v>279</v>
       </c>
       <c r="L30" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="M30" t="s">
         <v>282</v>
@@ -5183,7 +5198,7 @@
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="S30" t="s">
         <v>284</v>
@@ -5197,7 +5212,7 @@
         <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C31" t="s">
         <v>288</v>
@@ -5209,7 +5224,7 @@
         <v>288</v>
       </c>
       <c r="F31" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="G31" t="s">
         <v>289</v>
@@ -5227,7 +5242,7 @@
         <v>288</v>
       </c>
       <c r="L31" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="M31" t="s">
         <v>291</v>
@@ -5238,7 +5253,7 @@
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="S31" t="s">
         <v>293</v>
@@ -5252,10 +5267,10 @@
         <v>295</v>
       </c>
       <c r="B32" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C32" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D32" t="s">
         <v>296</v>
@@ -5264,7 +5279,7 @@
         <v>297</v>
       </c>
       <c r="F32" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="G32" t="s">
         <v>298</v>
@@ -5273,7 +5288,7 @@
         <v>299</v>
       </c>
       <c r="I32" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="J32" t="s">
         <v>296</v>
@@ -5282,7 +5297,7 @@
         <v>297</v>
       </c>
       <c r="L32" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="M32" t="s">
         <v>300</v>
@@ -5293,7 +5308,7 @@
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="S32" t="s">
         <v>302</v>
@@ -5307,10 +5322,10 @@
         <v>304</v>
       </c>
       <c r="B33" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C33" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D33" t="s">
         <v>305</v>
@@ -5319,7 +5334,7 @@
         <v>306</v>
       </c>
       <c r="F33" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="G33" t="s">
         <v>307</v>
@@ -5328,7 +5343,7 @@
         <v>308</v>
       </c>
       <c r="I33" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="J33" t="s">
         <v>305</v>
@@ -5337,7 +5352,7 @@
         <v>306</v>
       </c>
       <c r="L33" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="M33" t="s">
         <v>309</v>
@@ -5348,7 +5363,7 @@
       <c r="P33"/>
       <c r="Q33"/>
       <c r="R33" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="S33" t="s">
         <v>311</v>
@@ -5362,10 +5377,10 @@
         <v>313</v>
       </c>
       <c r="B34" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C34" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D34" t="s">
         <v>314</v>
@@ -5374,7 +5389,7 @@
         <v>315</v>
       </c>
       <c r="F34" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="G34" t="s">
         <v>316</v>
@@ -5383,7 +5398,7 @@
         <v>317</v>
       </c>
       <c r="I34" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="J34" t="s">
         <v>318</v>
@@ -5392,7 +5407,7 @@
         <v>319</v>
       </c>
       <c r="L34" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="M34" t="s">
         <v>320</v>
@@ -5403,7 +5418,7 @@
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="S34" t="s">
         <v>322</v>
@@ -5417,10 +5432,10 @@
         <v>324</v>
       </c>
       <c r="B35" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C35" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D35" t="s">
         <v>325</v>
@@ -5429,7 +5444,7 @@
         <v>326</v>
       </c>
       <c r="F35" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="G35" t="s">
         <v>327</v>
@@ -5438,7 +5453,7 @@
         <v>328</v>
       </c>
       <c r="I35" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="J35" t="s">
         <v>325</v>
@@ -5447,7 +5462,7 @@
         <v>326</v>
       </c>
       <c r="L35" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="M35" t="s">
         <v>329</v>
@@ -5458,7 +5473,7 @@
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="S35" t="s">
         <v>331</v>
@@ -5472,10 +5487,10 @@
         <v>333</v>
       </c>
       <c r="B36" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C36" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D36" t="s">
         <v>334</v>
@@ -5484,7 +5499,7 @@
         <v>335</v>
       </c>
       <c r="F36" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="G36" t="s">
         <v>336</v>
@@ -5493,7 +5508,7 @@
         <v>337</v>
       </c>
       <c r="I36" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="J36" t="s">
         <v>334</v>
@@ -5502,7 +5517,7 @@
         <v>335</v>
       </c>
       <c r="L36" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="M36" t="s">
         <v>338</v>
@@ -5513,7 +5528,7 @@
       <c r="P36"/>
       <c r="Q36"/>
       <c r="R36" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="S36" t="s">
         <v>340</v>
@@ -5527,10 +5542,10 @@
         <v>342</v>
       </c>
       <c r="B37" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C37" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D37" t="s">
         <v>343</v>
@@ -5539,7 +5554,7 @@
         <v>344</v>
       </c>
       <c r="F37" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="G37" t="s">
         <v>345</v>
@@ -5548,7 +5563,7 @@
         <v>346</v>
       </c>
       <c r="I37" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="J37" t="s">
         <v>347</v>
@@ -5557,7 +5572,7 @@
         <v>344</v>
       </c>
       <c r="L37" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="M37" t="s">
         <v>348</v>
@@ -5568,7 +5583,7 @@
       <c r="P37"/>
       <c r="Q37"/>
       <c r="R37" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="S37" t="s">
         <v>350</v>
@@ -5582,7 +5597,7 @@
         <v>352</v>
       </c>
       <c r="B38" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C38" t="s">
         <v>354</v>
@@ -5594,7 +5609,7 @@
         <v>354</v>
       </c>
       <c r="F38" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="G38" t="s">
         <v>355</v>
@@ -5612,7 +5627,7 @@
         <v>354</v>
       </c>
       <c r="L38" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="M38" t="s">
         <v>357</v>
@@ -5623,7 +5638,7 @@
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="S38" t="s">
         <v>359</v>
@@ -5637,10 +5652,10 @@
         <v>361</v>
       </c>
       <c r="B39" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C39" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D39" t="s">
         <v>362</v>
@@ -5649,7 +5664,7 @@
         <v>363</v>
       </c>
       <c r="F39" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="G39" t="s">
         <v>364</v>
@@ -5658,7 +5673,7 @@
         <v>365</v>
       </c>
       <c r="I39" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="J39" t="s">
         <v>366</v>
@@ -5667,7 +5682,7 @@
         <v>363</v>
       </c>
       <c r="L39" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="M39" t="s">
         <v>367</v>
@@ -5678,7 +5693,7 @@
       <c r="P39"/>
       <c r="Q39"/>
       <c r="R39" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="S39" t="s">
         <v>369</v>
@@ -5692,10 +5707,10 @@
         <v>371</v>
       </c>
       <c r="B40" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C40" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D40" t="s">
         <v>372</v>
@@ -5704,7 +5719,7 @@
         <v>373</v>
       </c>
       <c r="F40" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="G40" t="s">
         <v>374</v>
@@ -5713,7 +5728,7 @@
         <v>375</v>
       </c>
       <c r="I40" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="J40" t="s">
         <v>372</v>
@@ -5722,7 +5737,7 @@
         <v>373</v>
       </c>
       <c r="L40" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="M40" t="s">
         <v>376</v>
@@ -5733,7 +5748,7 @@
       <c r="P40"/>
       <c r="Q40"/>
       <c r="R40" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="S40" t="s">
         <v>378</v>
@@ -5747,10 +5762,10 @@
         <v>380</v>
       </c>
       <c r="B41" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C41" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D41" t="s">
         <v>381</v>
@@ -5759,7 +5774,7 @@
         <v>382</v>
       </c>
       <c r="F41" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="G41" t="s">
         <v>383</v>
@@ -5768,7 +5783,7 @@
         <v>384</v>
       </c>
       <c r="I41" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="J41" t="s">
         <v>381</v>
@@ -5777,7 +5792,7 @@
         <v>382</v>
       </c>
       <c r="L41" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="M41" t="s">
         <v>385</v>
@@ -5788,7 +5803,7 @@
       <c r="P41"/>
       <c r="Q41"/>
       <c r="R41" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="S41" t="s">
         <v>387</v>
@@ -5802,10 +5817,10 @@
         <v>389</v>
       </c>
       <c r="B42" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C42" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D42" t="s">
         <v>390</v>
@@ -5814,7 +5829,7 @@
         <v>391</v>
       </c>
       <c r="F42" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="G42" t="s">
         <v>392</v>
@@ -5823,7 +5838,7 @@
         <v>393</v>
       </c>
       <c r="I42" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J42" t="s">
         <v>390</v>
@@ -5832,7 +5847,7 @@
         <v>391</v>
       </c>
       <c r="L42" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="M42" t="s">
         <v>394</v>
@@ -5850,10 +5865,10 @@
         <v>396</v>
       </c>
       <c r="B43" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C43" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D43" t="s">
         <v>397</v>
@@ -5862,7 +5877,7 @@
         <v>398</v>
       </c>
       <c r="F43" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="G43" t="s">
         <v>399</v>
@@ -5871,7 +5886,7 @@
         <v>400</v>
       </c>
       <c r="I43" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="J43" t="s">
         <v>397</v>
@@ -5891,10 +5906,10 @@
         <v>401</v>
       </c>
       <c r="B44" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C44" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D44" t="s">
         <v>402</v>
@@ -5903,7 +5918,7 @@
         <v>403</v>
       </c>
       <c r="F44" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="G44" t="s">
         <v>404</v>
@@ -5912,7 +5927,7 @@
         <v>405</v>
       </c>
       <c r="I44" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="J44" t="s">
         <v>402</v>
@@ -5932,10 +5947,10 @@
         <v>406</v>
       </c>
       <c r="B45" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C45" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D45" t="s">
         <v>407</v>
@@ -5944,7 +5959,7 @@
         <v>408</v>
       </c>
       <c r="F45" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="G45" t="s">
         <v>409</v>
@@ -5953,7 +5968,7 @@
         <v>410</v>
       </c>
       <c r="I45" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="J45" t="s">
         <v>407</v>
@@ -5962,7 +5977,7 @@
         <v>408</v>
       </c>
       <c r="L45" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="M45" t="s">
         <v>411</v>
@@ -5973,7 +5988,7 @@
       <c r="P45"/>
       <c r="Q45"/>
       <c r="R45" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="S45" t="s">
         <v>413</v>
@@ -5987,10 +6002,10 @@
         <v>415</v>
       </c>
       <c r="B46" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C46" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D46" t="s">
         <v>416</v>
@@ -5999,7 +6014,7 @@
         <v>417</v>
       </c>
       <c r="F46" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="G46" t="s">
         <v>418</v>
@@ -6008,7 +6023,7 @@
         <v>419</v>
       </c>
       <c r="I46" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="J46" t="s">
         <v>420</v>
@@ -6017,7 +6032,7 @@
         <v>417</v>
       </c>
       <c r="L46" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="M46" t="s">
         <v>421</v>
@@ -6028,7 +6043,7 @@
       <c r="P46"/>
       <c r="Q46"/>
       <c r="R46" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="S46" t="s">
         <v>423</v>
@@ -6042,10 +6057,10 @@
         <v>425</v>
       </c>
       <c r="B47" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C47" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D47" t="s">
         <v>426</v>
@@ -6054,7 +6069,7 @@
         <v>427</v>
       </c>
       <c r="F47" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="G47" t="s">
         <v>428</v>
@@ -6063,7 +6078,7 @@
         <v>429</v>
       </c>
       <c r="I47" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="J47" t="s">
         <v>426</v>
@@ -6072,7 +6087,7 @@
         <v>427</v>
       </c>
       <c r="L47" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="M47" t="s">
         <v>430</v>
@@ -6083,7 +6098,7 @@
       <c r="P47"/>
       <c r="Q47"/>
       <c r="R47" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="S47" t="s">
         <v>331</v>
@@ -6097,10 +6112,10 @@
         <v>432</v>
       </c>
       <c r="B48" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C48" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D48" t="s">
         <v>433</v>
@@ -6109,7 +6124,7 @@
         <v>434</v>
       </c>
       <c r="F48" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="G48" t="s">
         <v>435</v>
@@ -6118,7 +6133,7 @@
         <v>436</v>
       </c>
       <c r="I48" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="J48" t="s">
         <v>433</v>
@@ -6127,7 +6142,7 @@
         <v>434</v>
       </c>
       <c r="L48" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="M48" t="s">
         <v>437</v>
@@ -6138,7 +6153,7 @@
       <c r="P48"/>
       <c r="Q48"/>
       <c r="R48" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="S48" t="s">
         <v>439</v>
@@ -6152,7 +6167,7 @@
         <v>441</v>
       </c>
       <c r="B49" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C49" t="s">
         <v>443</v>
@@ -6164,7 +6179,7 @@
         <v>443</v>
       </c>
       <c r="F49" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="G49" t="s">
         <v>444</v>
@@ -6182,7 +6197,7 @@
         <v>443</v>
       </c>
       <c r="L49" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="M49" t="s">
         <v>446</v>
@@ -6200,10 +6215,10 @@
         <v>448</v>
       </c>
       <c r="B50" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C50" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D50" t="s">
         <v>449</v>
@@ -6212,7 +6227,7 @@
         <v>450</v>
       </c>
       <c r="F50" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="G50" t="s">
         <v>451</v>
@@ -6221,7 +6236,7 @@
         <v>452</v>
       </c>
       <c r="I50" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="J50" t="s">
         <v>449</v>
@@ -6230,7 +6245,7 @@
         <v>450</v>
       </c>
       <c r="L50" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="M50" t="s">
         <v>453</v>
@@ -6248,10 +6263,10 @@
         <v>455</v>
       </c>
       <c r="B51" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C51" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D51" t="s">
         <v>456</v>
@@ -6260,7 +6275,7 @@
         <v>457</v>
       </c>
       <c r="F51" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G51" t="s">
         <v>458</v>
@@ -6269,7 +6284,7 @@
         <v>459</v>
       </c>
       <c r="I51" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="J51" t="s">
         <v>456</v>
@@ -6278,7 +6293,7 @@
         <v>457</v>
       </c>
       <c r="L51" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="M51" t="s">
         <v>460</v>
@@ -6289,7 +6304,7 @@
       <c r="P51"/>
       <c r="Q51"/>
       <c r="R51" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="S51" t="s">
         <v>462</v>
@@ -6303,10 +6318,10 @@
         <v>464</v>
       </c>
       <c r="B52" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C52" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D52" t="s">
         <v>465</v>
@@ -6315,7 +6330,7 @@
         <v>466</v>
       </c>
       <c r="F52" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G52" t="s">
         <v>458</v>
@@ -6324,7 +6339,7 @@
         <v>459</v>
       </c>
       <c r="I52" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="J52" t="s">
         <v>465</v>
@@ -6333,7 +6348,7 @@
         <v>466</v>
       </c>
       <c r="L52" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="M52" t="s">
         <v>467</v>
@@ -6344,7 +6359,7 @@
       <c r="P52"/>
       <c r="Q52"/>
       <c r="R52" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="S52" t="s">
         <v>469</v>
@@ -6358,10 +6373,10 @@
         <v>471</v>
       </c>
       <c r="B53" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C53" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D53" t="s">
         <v>472</v>
@@ -6370,7 +6385,7 @@
         <v>473</v>
       </c>
       <c r="F53" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G53" t="s">
         <v>474</v>
@@ -6379,7 +6394,7 @@
         <v>475</v>
       </c>
       <c r="I53" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="J53" t="s">
         <v>472</v>
@@ -6388,7 +6403,7 @@
         <v>473</v>
       </c>
       <c r="L53" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="M53" t="s">
         <v>476</v>
@@ -6399,7 +6414,7 @@
       <c r="P53"/>
       <c r="Q53"/>
       <c r="R53" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="S53" t="s">
         <v>462</v>
@@ -6413,10 +6428,10 @@
         <v>478</v>
       </c>
       <c r="B54" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C54" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D54" t="s">
         <v>479</v>
@@ -6425,7 +6440,7 @@
         <v>480</v>
       </c>
       <c r="F54" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G54" t="s">
         <v>474</v>
@@ -6434,7 +6449,7 @@
         <v>475</v>
       </c>
       <c r="I54" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="J54" t="s">
         <v>479</v>
@@ -6443,7 +6458,7 @@
         <v>480</v>
       </c>
       <c r="L54" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="M54" t="s">
         <v>476</v>
@@ -6454,7 +6469,7 @@
       <c r="P54"/>
       <c r="Q54"/>
       <c r="R54" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="S54" t="s">
         <v>462</v>
@@ -6468,10 +6483,10 @@
         <v>481</v>
       </c>
       <c r="B55" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C55" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D55" t="s">
         <v>482</v>
@@ -6480,7 +6495,7 @@
         <v>483</v>
       </c>
       <c r="F55" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G55" t="s">
         <v>474</v>
@@ -6489,7 +6504,7 @@
         <v>475</v>
       </c>
       <c r="I55" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="J55" t="s">
         <v>482</v>
@@ -6498,7 +6513,7 @@
         <v>483</v>
       </c>
       <c r="L55" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="M55" t="s">
         <v>476</v>
@@ -6509,7 +6524,7 @@
       <c r="P55"/>
       <c r="Q55"/>
       <c r="R55" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="S55" t="s">
         <v>462</v>
@@ -6523,10 +6538,10 @@
         <v>484</v>
       </c>
       <c r="B56" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C56" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D56" t="s">
         <v>485</v>
@@ -6535,7 +6550,7 @@
         <v>486</v>
       </c>
       <c r="F56" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G56" t="s">
         <v>474</v>
@@ -6544,7 +6559,7 @@
         <v>475</v>
       </c>
       <c r="I56" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="J56" t="s">
         <v>485</v>
@@ -6553,7 +6568,7 @@
         <v>486</v>
       </c>
       <c r="L56" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="M56" t="s">
         <v>476</v>
@@ -6564,7 +6579,7 @@
       <c r="P56"/>
       <c r="Q56"/>
       <c r="R56" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="S56" t="s">
         <v>462</v>
@@ -6578,10 +6593,10 @@
         <v>487</v>
       </c>
       <c r="B57" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C57" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D57" t="s">
         <v>488</v>
@@ -6590,7 +6605,7 @@
         <v>489</v>
       </c>
       <c r="F57" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G57" t="s">
         <v>474</v>
@@ -6599,7 +6614,7 @@
         <v>475</v>
       </c>
       <c r="I57" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="J57" t="s">
         <v>488</v>
@@ -6608,7 +6623,7 @@
         <v>489</v>
       </c>
       <c r="L57" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="M57" t="s">
         <v>490</v>
@@ -6619,7 +6634,7 @@
       <c r="P57"/>
       <c r="Q57"/>
       <c r="R57" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="S57" t="s">
         <v>492</v>
@@ -6633,10 +6648,10 @@
         <v>494</v>
       </c>
       <c r="B58" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C58" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D58" t="s">
         <v>495</v>
@@ -6645,7 +6660,7 @@
         <v>496</v>
       </c>
       <c r="F58" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G58" t="s">
         <v>474</v>
@@ -6654,7 +6669,7 @@
         <v>475</v>
       </c>
       <c r="I58" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="J58" t="s">
         <v>495</v>
@@ -6663,7 +6678,7 @@
         <v>496</v>
       </c>
       <c r="L58" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="M58" t="s">
         <v>490</v>
@@ -6674,7 +6689,7 @@
       <c r="P58"/>
       <c r="Q58"/>
       <c r="R58" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="S58" t="s">
         <v>492</v>
@@ -6688,10 +6703,10 @@
         <v>497</v>
       </c>
       <c r="B59" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C59" t="s">
-        <v>499</v>
+        <v>879</v>
       </c>
       <c r="D59" t="s">
         <v>498</v>
@@ -6699,47 +6714,68 @@
       <c r="E59" t="s">
         <v>499</v>
       </c>
-      <c r="G59"/>
-      <c r="H59"/>
+      <c r="F59" t="s">
+        <v>961</v>
+      </c>
+      <c r="G59" t="s">
+        <v>474</v>
+      </c>
+      <c r="H59" t="s">
+        <v>475</v>
+      </c>
       <c r="I59" t="s">
-        <v>500</v>
+        <v>879</v>
       </c>
       <c r="J59" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K59" t="s">
-        <v>500</v>
-      </c>
-      <c r="M59"/>
-      <c r="N59"/>
+        <v>499</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M59" t="s">
+        <v>490</v>
+      </c>
+      <c r="N59" t="s">
+        <v>491</v>
+      </c>
       <c r="P59"/>
       <c r="Q59"/>
-      <c r="S59"/>
-      <c r="T59"/>
+      <c r="R59" t="s">
+        <v>1138</v>
+      </c>
+      <c r="S59" t="s">
+        <v>492</v>
+      </c>
+      <c r="T59" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>500</v>
+      </c>
+      <c r="B60" t="s">
+        <v>819</v>
+      </c>
+      <c r="C60" t="s">
+        <v>502</v>
+      </c>
+      <c r="D60" t="s">
         <v>501</v>
       </c>
-      <c r="B60" t="s">
-        <v>813</v>
-      </c>
-      <c r="C60" t="s">
-        <v>875</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>502</v>
-      </c>
-      <c r="E60" t="s">
-        <v>503</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
       <c r="I60" t="s">
-        <v>875</v>
+        <v>503</v>
       </c>
       <c r="J60" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K60" t="s">
         <v>503</v>
@@ -6756,10 +6792,10 @@
         <v>504</v>
       </c>
       <c r="B61" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C61" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D61" t="s">
         <v>505</v>
@@ -6767,17 +6803,10 @@
       <c r="E61" t="s">
         <v>506</v>
       </c>
-      <c r="F61" t="s">
-        <v>957</v>
-      </c>
-      <c r="G61" t="s">
-        <v>507</v>
-      </c>
-      <c r="H61" t="s">
-        <v>508</v>
-      </c>
+      <c r="G61"/>
+      <c r="H61"/>
       <c r="I61" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="J61" t="s">
         <v>505</v>
@@ -6794,37 +6823,37 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s">
         <v>816</v>
       </c>
       <c r="C62" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D62" t="s">
+        <v>508</v>
+      </c>
+      <c r="E62" t="s">
+        <v>509</v>
+      </c>
+      <c r="F62" t="s">
+        <v>962</v>
+      </c>
+      <c r="G62" t="s">
         <v>510</v>
       </c>
-      <c r="E62" t="s">
+      <c r="H62" t="s">
         <v>511</v>
       </c>
-      <c r="F62" t="s">
-        <v>958</v>
-      </c>
-      <c r="G62" t="s">
-        <v>512</v>
-      </c>
-      <c r="H62" t="s">
-        <v>513</v>
-      </c>
       <c r="I62" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="J62" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K62" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="M62"/>
       <c r="N62"/>
@@ -6835,47 +6864,40 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>512</v>
+      </c>
+      <c r="B63" t="s">
+        <v>820</v>
+      </c>
+      <c r="C63" t="s">
+        <v>882</v>
+      </c>
+      <c r="D63" t="s">
+        <v>513</v>
+      </c>
+      <c r="E63" t="s">
         <v>514</v>
       </c>
-      <c r="B63" t="s">
-        <v>799</v>
-      </c>
-      <c r="C63" t="s">
-        <v>878</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
+        <v>963</v>
+      </c>
+      <c r="G63" t="s">
         <v>515</v>
       </c>
-      <c r="E63" t="s">
+      <c r="H63" t="s">
         <v>516</v>
       </c>
-      <c r="F63" t="s">
-        <v>959</v>
-      </c>
-      <c r="G63" t="s">
-        <v>517</v>
-      </c>
-      <c r="H63" t="s">
-        <v>518</v>
-      </c>
       <c r="I63" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="J63" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K63" t="s">
-        <v>516</v>
-      </c>
-      <c r="L63" t="s">
-        <v>1064</v>
-      </c>
-      <c r="M63" t="s">
-        <v>519</v>
-      </c>
-      <c r="N63" t="s">
-        <v>520</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="M63"/>
+      <c r="N63"/>
       <c r="P63"/>
       <c r="Q63"/>
       <c r="S63"/>
@@ -6883,149 +6905,149 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>517</v>
+      </c>
+      <c r="B64" t="s">
+        <v>802</v>
+      </c>
+      <c r="C64" t="s">
+        <v>883</v>
+      </c>
+      <c r="D64" t="s">
+        <v>518</v>
+      </c>
+      <c r="E64" t="s">
+        <v>519</v>
+      </c>
+      <c r="F64" t="s">
+        <v>964</v>
+      </c>
+      <c r="G64" t="s">
+        <v>520</v>
+      </c>
+      <c r="H64" t="s">
         <v>521</v>
       </c>
-      <c r="B64" t="s">
-        <v>803</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="I64" t="s">
+        <v>883</v>
+      </c>
+      <c r="J64" t="s">
+        <v>518</v>
+      </c>
+      <c r="K64" t="s">
+        <v>519</v>
+      </c>
+      <c r="L64" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M64" t="s">
+        <v>522</v>
+      </c>
+      <c r="N64" t="s">
         <v>523</v>
-      </c>
-      <c r="D64" t="s">
-        <v>522</v>
-      </c>
-      <c r="E64" t="s">
-        <v>523</v>
-      </c>
-      <c r="F64" t="s">
-        <v>960</v>
-      </c>
-      <c r="G64" t="s">
-        <v>524</v>
-      </c>
-      <c r="H64" t="s">
-        <v>525</v>
-      </c>
-      <c r="I64" t="s">
-        <v>523</v>
-      </c>
-      <c r="J64" t="s">
-        <v>522</v>
-      </c>
-      <c r="K64" t="s">
-        <v>523</v>
-      </c>
-      <c r="L64" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M64" t="s">
-        <v>526</v>
-      </c>
-      <c r="N64" t="s">
-        <v>527</v>
       </c>
       <c r="P64"/>
       <c r="Q64"/>
-      <c r="R64" t="s">
-        <v>1134</v>
-      </c>
-      <c r="S64" t="s">
-        <v>528</v>
-      </c>
-      <c r="T64" t="s">
-        <v>529</v>
-      </c>
+      <c r="S64"/>
+      <c r="T64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>524</v>
+      </c>
+      <c r="B65" t="s">
+        <v>806</v>
+      </c>
+      <c r="C65" t="s">
+        <v>526</v>
+      </c>
+      <c r="D65" t="s">
+        <v>525</v>
+      </c>
+      <c r="E65" t="s">
+        <v>526</v>
+      </c>
+      <c r="F65" t="s">
+        <v>965</v>
+      </c>
+      <c r="G65" t="s">
+        <v>527</v>
+      </c>
+      <c r="H65" t="s">
+        <v>528</v>
+      </c>
+      <c r="I65" t="s">
+        <v>526</v>
+      </c>
+      <c r="J65" t="s">
+        <v>525</v>
+      </c>
+      <c r="K65" t="s">
+        <v>526</v>
+      </c>
+      <c r="L65" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M65" t="s">
+        <v>529</v>
+      </c>
+      <c r="N65" t="s">
         <v>530</v>
-      </c>
-      <c r="B65" t="s">
-        <v>799</v>
-      </c>
-      <c r="C65" t="s">
-        <v>879</v>
-      </c>
-      <c r="D65" t="s">
-        <v>531</v>
-      </c>
-      <c r="E65" t="s">
-        <v>532</v>
-      </c>
-      <c r="F65" t="s">
-        <v>961</v>
-      </c>
-      <c r="G65" t="s">
-        <v>533</v>
-      </c>
-      <c r="H65" t="s">
-        <v>534</v>
-      </c>
-      <c r="I65" t="s">
-        <v>879</v>
-      </c>
-      <c r="J65" t="s">
-        <v>531</v>
-      </c>
-      <c r="K65" t="s">
-        <v>532</v>
-      </c>
-      <c r="L65" t="s">
-        <v>1066</v>
-      </c>
-      <c r="M65" t="s">
-        <v>535</v>
-      </c>
-      <c r="N65" t="s">
-        <v>536</v>
       </c>
       <c r="P65"/>
       <c r="Q65"/>
-      <c r="S65"/>
-      <c r="T65"/>
+      <c r="R65" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S65" t="s">
+        <v>531</v>
+      </c>
+      <c r="T65" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>533</v>
+      </c>
+      <c r="B66" t="s">
+        <v>802</v>
+      </c>
+      <c r="C66" t="s">
+        <v>884</v>
+      </c>
+      <c r="D66" t="s">
+        <v>534</v>
+      </c>
+      <c r="E66" t="s">
+        <v>535</v>
+      </c>
+      <c r="F66" t="s">
+        <v>966</v>
+      </c>
+      <c r="G66" t="s">
+        <v>536</v>
+      </c>
+      <c r="H66" t="s">
         <v>537</v>
       </c>
-      <c r="B66" t="s">
-        <v>799</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="I66" t="s">
+        <v>884</v>
+      </c>
+      <c r="J66" t="s">
+        <v>534</v>
+      </c>
+      <c r="K66" t="s">
+        <v>535</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1071</v>
+      </c>
+      <c r="M66" t="s">
+        <v>538</v>
+      </c>
+      <c r="N66" t="s">
         <v>539</v>
-      </c>
-      <c r="D66" t="s">
-        <v>538</v>
-      </c>
-      <c r="E66" t="s">
-        <v>539</v>
-      </c>
-      <c r="F66" t="s">
-        <v>962</v>
-      </c>
-      <c r="G66" t="s">
-        <v>540</v>
-      </c>
-      <c r="H66" t="s">
-        <v>541</v>
-      </c>
-      <c r="I66" t="s">
-        <v>539</v>
-      </c>
-      <c r="J66" t="s">
-        <v>538</v>
-      </c>
-      <c r="K66" t="s">
-        <v>539</v>
-      </c>
-      <c r="L66" t="s">
-        <v>1067</v>
-      </c>
-      <c r="M66" t="s">
-        <v>542</v>
-      </c>
-      <c r="N66" t="s">
-        <v>543</v>
       </c>
       <c r="P66"/>
       <c r="Q66"/>
@@ -7034,46 +7056,46 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>540</v>
+      </c>
+      <c r="B67" t="s">
+        <v>802</v>
+      </c>
+      <c r="C67" t="s">
+        <v>542</v>
+      </c>
+      <c r="D67" t="s">
+        <v>541</v>
+      </c>
+      <c r="E67" t="s">
+        <v>542</v>
+      </c>
+      <c r="F67" t="s">
+        <v>967</v>
+      </c>
+      <c r="G67" t="s">
+        <v>543</v>
+      </c>
+      <c r="H67" t="s">
         <v>544</v>
       </c>
-      <c r="B67" t="s">
-        <v>817</v>
-      </c>
-      <c r="C67" t="s">
-        <v>880</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="I67" t="s">
+        <v>542</v>
+      </c>
+      <c r="J67" t="s">
+        <v>541</v>
+      </c>
+      <c r="K67" t="s">
+        <v>542</v>
+      </c>
+      <c r="L67" t="s">
+        <v>1072</v>
+      </c>
+      <c r="M67" t="s">
         <v>545</v>
       </c>
-      <c r="E67" t="s">
+      <c r="N67" t="s">
         <v>546</v>
-      </c>
-      <c r="F67" t="s">
-        <v>963</v>
-      </c>
-      <c r="G67" t="s">
-        <v>547</v>
-      </c>
-      <c r="H67" t="s">
-        <v>548</v>
-      </c>
-      <c r="I67" t="s">
-        <v>880</v>
-      </c>
-      <c r="J67" t="s">
-        <v>545</v>
-      </c>
-      <c r="K67" t="s">
-        <v>546</v>
-      </c>
-      <c r="L67" t="s">
-        <v>1068</v>
-      </c>
-      <c r="M67" t="s">
-        <v>549</v>
-      </c>
-      <c r="N67" t="s">
-        <v>550</v>
       </c>
       <c r="P67"/>
       <c r="Q67"/>
@@ -7082,149 +7104,149 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>547</v>
+      </c>
+      <c r="B68" t="s">
+        <v>821</v>
+      </c>
+      <c r="C68" t="s">
+        <v>885</v>
+      </c>
+      <c r="D68" t="s">
+        <v>548</v>
+      </c>
+      <c r="E68" t="s">
+        <v>549</v>
+      </c>
+      <c r="F68" t="s">
+        <v>968</v>
+      </c>
+      <c r="G68" t="s">
+        <v>550</v>
+      </c>
+      <c r="H68" t="s">
         <v>551</v>
       </c>
-      <c r="B68" t="s">
-        <v>809</v>
-      </c>
-      <c r="C68" t="s">
-        <v>881</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="I68" t="s">
+        <v>885</v>
+      </c>
+      <c r="J68" t="s">
+        <v>548</v>
+      </c>
+      <c r="K68" t="s">
+        <v>549</v>
+      </c>
+      <c r="L68" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M68" t="s">
         <v>552</v>
       </c>
-      <c r="E68" t="s">
+      <c r="N68" t="s">
         <v>553</v>
-      </c>
-      <c r="F68" t="s">
-        <v>964</v>
-      </c>
-      <c r="G68" t="s">
-        <v>554</v>
-      </c>
-      <c r="H68" t="s">
-        <v>555</v>
-      </c>
-      <c r="I68" t="s">
-        <v>881</v>
-      </c>
-      <c r="J68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K68" t="s">
-        <v>553</v>
-      </c>
-      <c r="L68" t="s">
-        <v>1069</v>
-      </c>
-      <c r="M68" t="s">
-        <v>556</v>
-      </c>
-      <c r="N68" t="s">
-        <v>557</v>
       </c>
       <c r="P68"/>
       <c r="Q68"/>
-      <c r="R68" t="s">
-        <v>1135</v>
-      </c>
-      <c r="S68" t="s">
-        <v>558</v>
-      </c>
-      <c r="T68" t="s">
-        <v>559</v>
-      </c>
+      <c r="S68"/>
+      <c r="T68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>554</v>
+      </c>
+      <c r="B69" t="s">
+        <v>812</v>
+      </c>
+      <c r="C69" t="s">
+        <v>886</v>
+      </c>
+      <c r="D69" t="s">
+        <v>555</v>
+      </c>
+      <c r="E69" t="s">
+        <v>556</v>
+      </c>
+      <c r="F69" t="s">
+        <v>969</v>
+      </c>
+      <c r="G69" t="s">
+        <v>557</v>
+      </c>
+      <c r="H69" t="s">
+        <v>558</v>
+      </c>
+      <c r="I69" t="s">
+        <v>886</v>
+      </c>
+      <c r="J69" t="s">
+        <v>555</v>
+      </c>
+      <c r="K69" t="s">
+        <v>556</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1074</v>
+      </c>
+      <c r="M69" t="s">
+        <v>559</v>
+      </c>
+      <c r="N69" t="s">
         <v>560</v>
-      </c>
-      <c r="B69" t="s">
-        <v>799</v>
-      </c>
-      <c r="C69" t="s">
-        <v>882</v>
-      </c>
-      <c r="D69" t="s">
-        <v>561</v>
-      </c>
-      <c r="E69" t="s">
-        <v>562</v>
-      </c>
-      <c r="F69" t="s">
-        <v>965</v>
-      </c>
-      <c r="G69" t="s">
-        <v>563</v>
-      </c>
-      <c r="H69" t="s">
-        <v>564</v>
-      </c>
-      <c r="I69" t="s">
-        <v>882</v>
-      </c>
-      <c r="J69" t="s">
-        <v>561</v>
-      </c>
-      <c r="K69" t="s">
-        <v>562</v>
-      </c>
-      <c r="L69" t="s">
-        <v>1070</v>
-      </c>
-      <c r="M69" t="s">
-        <v>565</v>
-      </c>
-      <c r="N69" t="s">
-        <v>566</v>
       </c>
       <c r="P69"/>
       <c r="Q69"/>
-      <c r="S69"/>
-      <c r="T69"/>
+      <c r="R69" t="s">
+        <v>1140</v>
+      </c>
+      <c r="S69" t="s">
+        <v>561</v>
+      </c>
+      <c r="T69" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>563</v>
+      </c>
+      <c r="B70" t="s">
+        <v>802</v>
+      </c>
+      <c r="C70" t="s">
+        <v>887</v>
+      </c>
+      <c r="D70" t="s">
+        <v>564</v>
+      </c>
+      <c r="E70" t="s">
+        <v>565</v>
+      </c>
+      <c r="F70" t="s">
+        <v>970</v>
+      </c>
+      <c r="G70" t="s">
+        <v>566</v>
+      </c>
+      <c r="H70" t="s">
         <v>567</v>
       </c>
-      <c r="B70" t="s">
-        <v>800</v>
-      </c>
-      <c r="C70" t="s">
-        <v>883</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="I70" t="s">
+        <v>887</v>
+      </c>
+      <c r="J70" t="s">
+        <v>564</v>
+      </c>
+      <c r="K70" t="s">
+        <v>565</v>
+      </c>
+      <c r="L70" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M70" t="s">
         <v>568</v>
       </c>
-      <c r="E70" t="s">
+      <c r="N70" t="s">
         <v>569</v>
-      </c>
-      <c r="F70" t="s">
-        <v>966</v>
-      </c>
-      <c r="G70" t="s">
-        <v>570</v>
-      </c>
-      <c r="H70" t="s">
-        <v>571</v>
-      </c>
-      <c r="I70" t="s">
-        <v>883</v>
-      </c>
-      <c r="J70" t="s">
-        <v>568</v>
-      </c>
-      <c r="K70" t="s">
-        <v>569</v>
-      </c>
-      <c r="L70" t="s">
-        <v>1071</v>
-      </c>
-      <c r="M70" t="s">
-        <v>572</v>
-      </c>
-      <c r="N70" t="s">
-        <v>573</v>
       </c>
       <c r="P70"/>
       <c r="Q70"/>
@@ -7233,212 +7255,226 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>570</v>
+      </c>
+      <c r="B71" t="s">
+        <v>803</v>
+      </c>
+      <c r="C71" t="s">
+        <v>888</v>
+      </c>
+      <c r="D71" t="s">
+        <v>571</v>
+      </c>
+      <c r="E71" t="s">
+        <v>572</v>
+      </c>
+      <c r="F71" t="s">
+        <v>971</v>
+      </c>
+      <c r="G71" t="s">
+        <v>573</v>
+      </c>
+      <c r="H71" t="s">
         <v>574</v>
       </c>
-      <c r="B71" t="s">
-        <v>792</v>
-      </c>
-      <c r="C71" t="s">
-        <v>884</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="I71" t="s">
+        <v>888</v>
+      </c>
+      <c r="J71" t="s">
+        <v>571</v>
+      </c>
+      <c r="K71" t="s">
+        <v>572</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M71" t="s">
         <v>575</v>
       </c>
-      <c r="E71" t="s">
+      <c r="N71" t="s">
         <v>576</v>
-      </c>
-      <c r="F71" t="s">
-        <v>967</v>
-      </c>
-      <c r="G71" t="s">
-        <v>577</v>
-      </c>
-      <c r="H71" t="s">
-        <v>578</v>
-      </c>
-      <c r="I71" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J71" t="s">
-        <v>579</v>
-      </c>
-      <c r="K71" t="s">
-        <v>580</v>
-      </c>
-      <c r="L71" t="s">
-        <v>1072</v>
-      </c>
-      <c r="M71" t="s">
-        <v>581</v>
-      </c>
-      <c r="N71" t="s">
-        <v>582</v>
       </c>
       <c r="P71"/>
       <c r="Q71"/>
-      <c r="R71" t="s">
-        <v>1136</v>
-      </c>
-      <c r="S71" t="s">
-        <v>583</v>
-      </c>
-      <c r="T71" t="s">
-        <v>584</v>
-      </c>
+      <c r="S71"/>
+      <c r="T71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>577</v>
+      </c>
+      <c r="B72" t="s">
+        <v>795</v>
+      </c>
+      <c r="C72" t="s">
+        <v>889</v>
+      </c>
+      <c r="D72" t="s">
+        <v>578</v>
+      </c>
+      <c r="E72" t="s">
+        <v>579</v>
+      </c>
+      <c r="F72" t="s">
+        <v>972</v>
+      </c>
+      <c r="G72" t="s">
+        <v>580</v>
+      </c>
+      <c r="H72" t="s">
+        <v>581</v>
+      </c>
+      <c r="I72" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J72" t="s">
+        <v>582</v>
+      </c>
+      <c r="K72" t="s">
+        <v>583</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M72" t="s">
+        <v>584</v>
+      </c>
+      <c r="N72" t="s">
         <v>585</v>
-      </c>
-      <c r="B72" t="s">
-        <v>792</v>
-      </c>
-      <c r="C72" t="s">
-        <v>885</v>
-      </c>
-      <c r="D72" t="s">
-        <v>586</v>
-      </c>
-      <c r="E72" t="s">
-        <v>587</v>
-      </c>
-      <c r="F72" t="s">
-        <v>968</v>
-      </c>
-      <c r="G72" t="s">
-        <v>588</v>
-      </c>
-      <c r="H72" t="s">
-        <v>589</v>
-      </c>
-      <c r="I72" t="s">
-        <v>1002</v>
-      </c>
-      <c r="J72" t="s">
-        <v>590</v>
-      </c>
-      <c r="K72" t="s">
-        <v>591</v>
-      </c>
-      <c r="L72" t="s">
-        <v>1073</v>
-      </c>
-      <c r="M72" t="s">
-        <v>592</v>
-      </c>
-      <c r="N72" t="s">
-        <v>593</v>
       </c>
       <c r="P72"/>
       <c r="Q72"/>
       <c r="R72" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="S72" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="T72" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>588</v>
+      </c>
+      <c r="B73" t="s">
+        <v>795</v>
+      </c>
+      <c r="C73" t="s">
+        <v>890</v>
+      </c>
+      <c r="D73" t="s">
+        <v>589</v>
+      </c>
+      <c r="E73" t="s">
+        <v>590</v>
+      </c>
+      <c r="F73" t="s">
+        <v>973</v>
+      </c>
+      <c r="G73" t="s">
+        <v>591</v>
+      </c>
+      <c r="H73" t="s">
+        <v>592</v>
+      </c>
+      <c r="I73" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J73" t="s">
+        <v>593</v>
+      </c>
+      <c r="K73" t="s">
+        <v>594</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M73" t="s">
+        <v>595</v>
+      </c>
+      <c r="N73" t="s">
         <v>596</v>
-      </c>
-      <c r="B73" t="s">
-        <v>792</v>
-      </c>
-      <c r="C73" t="s">
-        <v>886</v>
-      </c>
-      <c r="D73" t="s">
-        <v>597</v>
-      </c>
-      <c r="E73" t="s">
-        <v>598</v>
-      </c>
-      <c r="F73" t="s">
-        <v>969</v>
-      </c>
-      <c r="G73" t="s">
-        <v>599</v>
-      </c>
-      <c r="H73" t="s">
-        <v>600</v>
-      </c>
-      <c r="I73" t="s">
-        <v>886</v>
-      </c>
-      <c r="J73" t="s">
-        <v>597</v>
-      </c>
-      <c r="K73" t="s">
-        <v>598</v>
-      </c>
-      <c r="L73" t="s">
-        <v>1074</v>
-      </c>
-      <c r="M73" t="s">
-        <v>601</v>
-      </c>
-      <c r="N73" t="s">
-        <v>602</v>
       </c>
       <c r="P73"/>
       <c r="Q73"/>
       <c r="R73" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="S73" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="T73" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>599</v>
+      </c>
+      <c r="B74" t="s">
+        <v>795</v>
+      </c>
+      <c r="C74" t="s">
+        <v>891</v>
+      </c>
+      <c r="D74" t="s">
+        <v>600</v>
+      </c>
+      <c r="E74" t="s">
+        <v>601</v>
+      </c>
+      <c r="F74" t="s">
+        <v>974</v>
+      </c>
+      <c r="G74" t="s">
+        <v>602</v>
+      </c>
+      <c r="H74" t="s">
+        <v>603</v>
+      </c>
+      <c r="I74" t="s">
+        <v>891</v>
+      </c>
+      <c r="J74" t="s">
+        <v>600</v>
+      </c>
+      <c r="K74" t="s">
+        <v>601</v>
+      </c>
+      <c r="L74" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M74" t="s">
+        <v>604</v>
+      </c>
+      <c r="N74" t="s">
         <v>605</v>
       </c>
-      <c r="B74" t="s">
-        <v>792</v>
-      </c>
-      <c r="C74" t="s">
-        <v>887</v>
-      </c>
-      <c r="D74" t="s">
-        <v>606</v>
-      </c>
-      <c r="E74" t="s">
-        <v>607</v>
-      </c>
-      <c r="G74"/>
-      <c r="H74"/>
-      <c r="I74" t="s">
-        <v>887</v>
-      </c>
-      <c r="J74" t="s">
-        <v>606</v>
-      </c>
-      <c r="K74" t="s">
-        <v>607</v>
-      </c>
-      <c r="M74"/>
-      <c r="N74"/>
       <c r="P74"/>
       <c r="Q74"/>
-      <c r="S74"/>
-      <c r="T74"/>
+      <c r="R74" t="s">
+        <v>1143</v>
+      </c>
+      <c r="S74" t="s">
+        <v>606</v>
+      </c>
+      <c r="T74" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
         <v>608</v>
       </c>
       <c r="B75" t="s">
-        <v>818</v>
+        <v>795</v>
       </c>
       <c r="C75" t="s">
-        <v>610</v>
+        <v>892</v>
       </c>
       <c r="D75" t="s">
         <v>609</v>
@@ -7446,17 +7482,10 @@
       <c r="E75" t="s">
         <v>610</v>
       </c>
-      <c r="F75" t="s">
-        <v>970</v>
-      </c>
-      <c r="G75" t="s">
-        <v>611</v>
-      </c>
-      <c r="H75" t="s">
-        <v>612</v>
-      </c>
+      <c r="G75"/>
+      <c r="H75"/>
       <c r="I75" t="s">
-        <v>610</v>
+        <v>892</v>
       </c>
       <c r="J75" t="s">
         <v>609</v>
@@ -7464,211 +7493,211 @@
       <c r="K75" t="s">
         <v>610</v>
       </c>
-      <c r="L75" t="s">
-        <v>1075</v>
-      </c>
-      <c r="M75" t="s">
-        <v>613</v>
-      </c>
-      <c r="N75" t="s">
-        <v>614</v>
-      </c>
+      <c r="M75"/>
+      <c r="N75"/>
       <c r="P75"/>
       <c r="Q75"/>
-      <c r="R75" t="s">
-        <v>1139</v>
-      </c>
-      <c r="S75" t="s">
-        <v>615</v>
-      </c>
-      <c r="T75" t="s">
-        <v>616</v>
-      </c>
+      <c r="S75"/>
+      <c r="T75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>611</v>
+      </c>
+      <c r="B76" t="s">
+        <v>822</v>
+      </c>
+      <c r="C76" t="s">
+        <v>613</v>
+      </c>
+      <c r="D76" t="s">
+        <v>612</v>
+      </c>
+      <c r="E76" t="s">
+        <v>613</v>
+      </c>
+      <c r="F76" t="s">
+        <v>975</v>
+      </c>
+      <c r="G76" t="s">
+        <v>614</v>
+      </c>
+      <c r="H76" t="s">
+        <v>615</v>
+      </c>
+      <c r="I76" t="s">
+        <v>613</v>
+      </c>
+      <c r="J76" t="s">
+        <v>612</v>
+      </c>
+      <c r="K76" t="s">
+        <v>613</v>
+      </c>
+      <c r="L76" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M76" t="s">
+        <v>616</v>
+      </c>
+      <c r="N76" t="s">
         <v>617</v>
-      </c>
-      <c r="B76" t="s">
-        <v>792</v>
-      </c>
-      <c r="C76" t="s">
-        <v>888</v>
-      </c>
-      <c r="D76" t="s">
-        <v>618</v>
-      </c>
-      <c r="E76" t="s">
-        <v>619</v>
-      </c>
-      <c r="F76" t="s">
-        <v>971</v>
-      </c>
-      <c r="G76" t="s">
-        <v>620</v>
-      </c>
-      <c r="H76" t="s">
-        <v>621</v>
-      </c>
-      <c r="I76" t="s">
-        <v>888</v>
-      </c>
-      <c r="J76" t="s">
-        <v>618</v>
-      </c>
-      <c r="K76" t="s">
-        <v>619</v>
-      </c>
-      <c r="L76" t="s">
-        <v>1076</v>
-      </c>
-      <c r="M76" t="s">
-        <v>622</v>
-      </c>
-      <c r="N76" t="s">
-        <v>623</v>
       </c>
       <c r="P76"/>
       <c r="Q76"/>
       <c r="R76" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="S76" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="T76" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>620</v>
+      </c>
+      <c r="B77" t="s">
+        <v>795</v>
+      </c>
+      <c r="C77" t="s">
+        <v>893</v>
+      </c>
+      <c r="D77" t="s">
+        <v>621</v>
+      </c>
+      <c r="E77" t="s">
+        <v>622</v>
+      </c>
+      <c r="F77" t="s">
+        <v>976</v>
+      </c>
+      <c r="G77" t="s">
+        <v>623</v>
+      </c>
+      <c r="H77" t="s">
+        <v>624</v>
+      </c>
+      <c r="I77" t="s">
+        <v>893</v>
+      </c>
+      <c r="J77" t="s">
+        <v>621</v>
+      </c>
+      <c r="K77" t="s">
+        <v>622</v>
+      </c>
+      <c r="L77" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M77" t="s">
+        <v>625</v>
+      </c>
+      <c r="N77" t="s">
         <v>626</v>
-      </c>
-      <c r="B77" t="s">
-        <v>819</v>
-      </c>
-      <c r="C77" t="s">
-        <v>889</v>
-      </c>
-      <c r="D77" t="s">
-        <v>627</v>
-      </c>
-      <c r="E77" t="s">
-        <v>628</v>
-      </c>
-      <c r="F77" t="s">
-        <v>972</v>
-      </c>
-      <c r="G77" t="s">
-        <v>629</v>
-      </c>
-      <c r="H77" t="s">
-        <v>630</v>
-      </c>
-      <c r="I77" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J77" t="s">
-        <v>631</v>
-      </c>
-      <c r="K77" t="s">
-        <v>632</v>
-      </c>
-      <c r="L77" t="s">
-        <v>1077</v>
-      </c>
-      <c r="M77" t="s">
-        <v>633</v>
-      </c>
-      <c r="N77" t="s">
-        <v>634</v>
       </c>
       <c r="P77"/>
       <c r="Q77"/>
       <c r="R77" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="S77" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="T77" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>629</v>
+      </c>
+      <c r="B78" t="s">
+        <v>823</v>
+      </c>
+      <c r="C78" t="s">
+        <v>894</v>
+      </c>
+      <c r="D78" t="s">
+        <v>630</v>
+      </c>
+      <c r="E78" t="s">
+        <v>631</v>
+      </c>
+      <c r="F78" t="s">
+        <v>977</v>
+      </c>
+      <c r="G78" t="s">
+        <v>632</v>
+      </c>
+      <c r="H78" t="s">
+        <v>633</v>
+      </c>
+      <c r="I78" t="s">
+        <v>1008</v>
+      </c>
+      <c r="J78" t="s">
+        <v>634</v>
+      </c>
+      <c r="K78" t="s">
+        <v>635</v>
+      </c>
+      <c r="L78" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M78" t="s">
+        <v>636</v>
+      </c>
+      <c r="N78" t="s">
         <v>637</v>
       </c>
-      <c r="B78" t="s">
-        <v>792</v>
-      </c>
-      <c r="C78" t="s">
-        <v>890</v>
-      </c>
-      <c r="D78" t="s">
-        <v>638</v>
-      </c>
-      <c r="E78" t="s">
-        <v>639</v>
-      </c>
-      <c r="F78" t="s">
-        <v>973</v>
-      </c>
-      <c r="G78" t="s">
-        <v>640</v>
-      </c>
-      <c r="H78" t="s">
-        <v>641</v>
-      </c>
-      <c r="I78" t="s">
-        <v>890</v>
-      </c>
-      <c r="J78" t="s">
-        <v>642</v>
-      </c>
-      <c r="K78" t="s">
-        <v>639</v>
-      </c>
-      <c r="M78"/>
-      <c r="N78"/>
       <c r="P78"/>
       <c r="Q78"/>
-      <c r="S78"/>
-      <c r="T78"/>
+      <c r="R78" t="s">
+        <v>1146</v>
+      </c>
+      <c r="S78" t="s">
+        <v>638</v>
+      </c>
+      <c r="T78" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>640</v>
+      </c>
+      <c r="B79" t="s">
+        <v>795</v>
+      </c>
+      <c r="C79" t="s">
+        <v>895</v>
+      </c>
+      <c r="D79" t="s">
+        <v>641</v>
+      </c>
+      <c r="E79" t="s">
+        <v>642</v>
+      </c>
+      <c r="F79" t="s">
+        <v>978</v>
+      </c>
+      <c r="G79" t="s">
         <v>643</v>
       </c>
-      <c r="B79" t="s">
-        <v>820</v>
-      </c>
-      <c r="C79" t="s">
-        <v>891</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="H79" t="s">
         <v>644</v>
       </c>
-      <c r="E79" t="s">
+      <c r="I79" t="s">
+        <v>895</v>
+      </c>
+      <c r="J79" t="s">
         <v>645</v>
       </c>
-      <c r="F79" t="s">
-        <v>974</v>
-      </c>
-      <c r="G79" t="s">
-        <v>646</v>
-      </c>
-      <c r="H79" t="s">
-        <v>647</v>
-      </c>
-      <c r="I79" t="s">
-        <v>891</v>
-      </c>
-      <c r="J79" t="s">
-        <v>644</v>
-      </c>
       <c r="K79" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="M79"/>
       <c r="N79"/>
@@ -7679,284 +7708,284 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>646</v>
+      </c>
+      <c r="B80" t="s">
+        <v>824</v>
+      </c>
+      <c r="C80" t="s">
+        <v>896</v>
+      </c>
+      <c r="D80" t="s">
+        <v>647</v>
+      </c>
+      <c r="E80" t="s">
         <v>648</v>
       </c>
-      <c r="B80" t="s">
-        <v>792</v>
-      </c>
-      <c r="C80" t="s">
-        <v>892</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="F80" t="s">
+        <v>979</v>
+      </c>
+      <c r="G80" t="s">
         <v>649</v>
       </c>
-      <c r="E80" t="s">
+      <c r="H80" t="s">
         <v>650</v>
       </c>
-      <c r="F80" t="s">
-        <v>975</v>
-      </c>
-      <c r="G80" t="s">
-        <v>651</v>
-      </c>
-      <c r="H80" t="s">
-        <v>652</v>
-      </c>
       <c r="I80" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="J80" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K80" t="s">
-        <v>650</v>
-      </c>
-      <c r="L80" t="s">
-        <v>1078</v>
-      </c>
-      <c r="M80" t="s">
-        <v>653</v>
-      </c>
-      <c r="N80" t="s">
-        <v>654</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="M80"/>
+      <c r="N80"/>
       <c r="P80"/>
       <c r="Q80"/>
-      <c r="R80" t="s">
-        <v>1142</v>
-      </c>
-      <c r="S80" t="s">
-        <v>655</v>
-      </c>
-      <c r="T80" t="s">
-        <v>656</v>
-      </c>
+      <c r="S80"/>
+      <c r="T80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>651</v>
+      </c>
+      <c r="B81" t="s">
+        <v>795</v>
+      </c>
+      <c r="C81" t="s">
+        <v>897</v>
+      </c>
+      <c r="D81" t="s">
+        <v>652</v>
+      </c>
+      <c r="E81" t="s">
+        <v>653</v>
+      </c>
+      <c r="F81" t="s">
+        <v>980</v>
+      </c>
+      <c r="G81" t="s">
+        <v>654</v>
+      </c>
+      <c r="H81" t="s">
+        <v>655</v>
+      </c>
+      <c r="I81" t="s">
+        <v>897</v>
+      </c>
+      <c r="J81" t="s">
+        <v>652</v>
+      </c>
+      <c r="K81" t="s">
+        <v>653</v>
+      </c>
+      <c r="L81" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M81" t="s">
+        <v>656</v>
+      </c>
+      <c r="N81" t="s">
         <v>657</v>
-      </c>
-      <c r="B81" t="s">
-        <v>821</v>
-      </c>
-      <c r="C81" t="s">
-        <v>893</v>
-      </c>
-      <c r="D81" t="s">
-        <v>658</v>
-      </c>
-      <c r="E81" t="s">
-        <v>659</v>
-      </c>
-      <c r="F81" t="s">
-        <v>976</v>
-      </c>
-      <c r="G81" t="s">
-        <v>660</v>
-      </c>
-      <c r="H81" t="s">
-        <v>661</v>
-      </c>
-      <c r="I81" t="s">
-        <v>1004</v>
-      </c>
-      <c r="J81" t="s">
-        <v>662</v>
-      </c>
-      <c r="K81" t="s">
-        <v>663</v>
-      </c>
-      <c r="L81" t="s">
-        <v>1079</v>
-      </c>
-      <c r="M81" t="s">
-        <v>664</v>
-      </c>
-      <c r="N81" t="s">
-        <v>665</v>
       </c>
       <c r="P81"/>
       <c r="Q81"/>
       <c r="R81" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="S81" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="T81" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>660</v>
+      </c>
+      <c r="B82" t="s">
+        <v>825</v>
+      </c>
+      <c r="C82" t="s">
+        <v>898</v>
+      </c>
+      <c r="D82" t="s">
+        <v>661</v>
+      </c>
+      <c r="E82" t="s">
+        <v>662</v>
+      </c>
+      <c r="F82" t="s">
+        <v>981</v>
+      </c>
+      <c r="G82" t="s">
+        <v>663</v>
+      </c>
+      <c r="H82" t="s">
+        <v>664</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J82" t="s">
+        <v>665</v>
+      </c>
+      <c r="K82" t="s">
+        <v>666</v>
+      </c>
+      <c r="L82" t="s">
+        <v>1084</v>
+      </c>
+      <c r="M82" t="s">
+        <v>667</v>
+      </c>
+      <c r="N82" t="s">
         <v>668</v>
       </c>
-      <c r="B82" t="s">
-        <v>822</v>
-      </c>
-      <c r="C82" t="s">
-        <v>894</v>
-      </c>
-      <c r="D82" t="s">
-        <v>669</v>
-      </c>
-      <c r="E82" t="s">
-        <v>670</v>
-      </c>
-      <c r="F82" t="s">
-        <v>977</v>
-      </c>
-      <c r="G82" t="s">
-        <v>671</v>
-      </c>
-      <c r="H82" t="s">
-        <v>672</v>
-      </c>
-      <c r="I82" t="s">
-        <v>894</v>
-      </c>
-      <c r="J82" t="s">
-        <v>669</v>
-      </c>
-      <c r="K82" t="s">
-        <v>670</v>
-      </c>
-      <c r="M82"/>
-      <c r="N82"/>
       <c r="P82"/>
       <c r="Q82"/>
-      <c r="S82"/>
-      <c r="T82"/>
+      <c r="R82" t="s">
+        <v>1148</v>
+      </c>
+      <c r="S82" t="s">
+        <v>669</v>
+      </c>
+      <c r="T82" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>671</v>
+      </c>
+      <c r="B83" t="s">
+        <v>826</v>
+      </c>
+      <c r="C83" t="s">
+        <v>899</v>
+      </c>
+      <c r="D83" t="s">
+        <v>672</v>
+      </c>
+      <c r="E83" t="s">
         <v>673</v>
       </c>
-      <c r="B83" t="s">
-        <v>792</v>
-      </c>
-      <c r="C83" t="s">
-        <v>895</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="F83" t="s">
+        <v>982</v>
+      </c>
+      <c r="G83" t="s">
         <v>674</v>
       </c>
-      <c r="E83" t="s">
+      <c r="H83" t="s">
         <v>675</v>
       </c>
-      <c r="F83" t="s">
-        <v>978</v>
-      </c>
-      <c r="G83" t="s">
-        <v>676</v>
-      </c>
-      <c r="H83" t="s">
-        <v>677</v>
-      </c>
       <c r="I83" t="s">
-        <v>1005</v>
+        <v>899</v>
       </c>
       <c r="J83" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="K83" t="s">
-        <v>679</v>
-      </c>
-      <c r="L83" t="s">
-        <v>1080</v>
-      </c>
-      <c r="M83" t="s">
-        <v>680</v>
-      </c>
-      <c r="N83" t="s">
-        <v>681</v>
-      </c>
-      <c r="O83" t="s">
-        <v>1089</v>
-      </c>
-      <c r="P83" t="s">
-        <v>682</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>683</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="M83"/>
+      <c r="N83"/>
+      <c r="P83"/>
+      <c r="Q83"/>
       <c r="S83"/>
       <c r="T83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>676</v>
+      </c>
+      <c r="B84" t="s">
+        <v>795</v>
+      </c>
+      <c r="C84" t="s">
+        <v>900</v>
+      </c>
+      <c r="D84" t="s">
+        <v>677</v>
+      </c>
+      <c r="E84" t="s">
+        <v>678</v>
+      </c>
+      <c r="F84" t="s">
+        <v>983</v>
+      </c>
+      <c r="G84" t="s">
+        <v>679</v>
+      </c>
+      <c r="H84" t="s">
+        <v>680</v>
+      </c>
+      <c r="I84" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J84" t="s">
+        <v>681</v>
+      </c>
+      <c r="K84" t="s">
+        <v>682</v>
+      </c>
+      <c r="L84" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M84" t="s">
+        <v>683</v>
+      </c>
+      <c r="N84" t="s">
         <v>684</v>
       </c>
-      <c r="B84" t="s">
-        <v>792</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="O84" t="s">
+        <v>1094</v>
+      </c>
+      <c r="P84" t="s">
+        <v>685</v>
+      </c>
+      <c r="Q84" t="s">
         <v>686</v>
       </c>
-      <c r="D84" t="s">
-        <v>685</v>
-      </c>
-      <c r="E84" t="s">
-        <v>686</v>
-      </c>
-      <c r="F84" t="s">
-        <v>979</v>
-      </c>
-      <c r="G84" t="s">
-        <v>687</v>
-      </c>
-      <c r="H84" t="s">
-        <v>688</v>
-      </c>
-      <c r="I84" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J84" t="s">
-        <v>689</v>
-      </c>
-      <c r="K84" t="s">
-        <v>690</v>
-      </c>
-      <c r="M84"/>
-      <c r="N84"/>
-      <c r="P84"/>
-      <c r="Q84"/>
       <c r="S84"/>
       <c r="T84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>687</v>
+      </c>
+      <c r="B85" t="s">
+        <v>795</v>
+      </c>
+      <c r="C85" t="s">
+        <v>689</v>
+      </c>
+      <c r="D85" t="s">
+        <v>688</v>
+      </c>
+      <c r="E85" t="s">
+        <v>689</v>
+      </c>
+      <c r="F85" t="s">
+        <v>984</v>
+      </c>
+      <c r="G85" t="s">
+        <v>690</v>
+      </c>
+      <c r="H85" t="s">
         <v>691</v>
       </c>
-      <c r="B85" t="s">
-        <v>792</v>
-      </c>
-      <c r="C85" t="s">
-        <v>896</v>
-      </c>
-      <c r="D85" t="s">
-        <v>180</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="I85" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J85" t="s">
         <v>692</v>
       </c>
-      <c r="F85" t="s">
-        <v>980</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="K85" t="s">
         <v>693</v>
-      </c>
-      <c r="H85" t="s">
-        <v>694</v>
-      </c>
-      <c r="I85" t="s">
-        <v>500</v>
-      </c>
-      <c r="J85" t="s">
-        <v>500</v>
-      </c>
-      <c r="K85" t="s">
-        <v>500</v>
       </c>
       <c r="M85"/>
       <c r="N85"/>
@@ -7967,37 +7996,37 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>694</v>
+      </c>
+      <c r="B86" t="s">
+        <v>795</v>
+      </c>
+      <c r="C86" t="s">
+        <v>901</v>
+      </c>
+      <c r="D86" t="s">
+        <v>180</v>
+      </c>
+      <c r="E86" t="s">
         <v>695</v>
       </c>
-      <c r="B86" t="s">
-        <v>796</v>
-      </c>
-      <c r="C86" t="s">
-        <v>897</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="F86" t="s">
+        <v>985</v>
+      </c>
+      <c r="G86" t="s">
         <v>696</v>
       </c>
-      <c r="E86" t="s">
+      <c r="H86" t="s">
         <v>697</v>
       </c>
-      <c r="F86" t="s">
-        <v>981</v>
-      </c>
-      <c r="G86" t="s">
-        <v>698</v>
-      </c>
-      <c r="H86" t="s">
-        <v>699</v>
-      </c>
       <c r="I86" t="s">
-        <v>1007</v>
+        <v>503</v>
       </c>
       <c r="J86" t="s">
-        <v>700</v>
+        <v>503</v>
       </c>
       <c r="K86" t="s">
-        <v>701</v>
+        <v>503</v>
       </c>
       <c r="M86"/>
       <c r="N86"/>
@@ -8008,119 +8037,126 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>698</v>
+      </c>
+      <c r="B87" t="s">
+        <v>799</v>
+      </c>
+      <c r="C87" t="s">
+        <v>902</v>
+      </c>
+      <c r="D87" t="s">
+        <v>699</v>
+      </c>
+      <c r="E87" t="s">
+        <v>700</v>
+      </c>
+      <c r="F87" t="s">
+        <v>986</v>
+      </c>
+      <c r="G87" t="s">
+        <v>701</v>
+      </c>
+      <c r="H87" t="s">
         <v>702</v>
       </c>
-      <c r="B87" t="s">
-        <v>792</v>
-      </c>
-      <c r="C87" t="s">
-        <v>124</v>
-      </c>
-      <c r="D87" t="s">
-        <v>123</v>
-      </c>
-      <c r="E87" t="s">
-        <v>124</v>
-      </c>
-      <c r="F87" t="s">
-        <v>982</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="I87" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J87" t="s">
         <v>703</v>
       </c>
-      <c r="H87" t="s">
+      <c r="K87" t="s">
         <v>704</v>
       </c>
-      <c r="I87" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J87" t="s">
-        <v>705</v>
-      </c>
-      <c r="K87" t="s">
-        <v>706</v>
-      </c>
-      <c r="L87" t="s">
-        <v>1081</v>
-      </c>
-      <c r="M87" t="s">
-        <v>707</v>
-      </c>
-      <c r="N87" t="s">
-        <v>708</v>
-      </c>
-      <c r="O87" t="s">
-        <v>1090</v>
-      </c>
-      <c r="P87" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>710</v>
-      </c>
+      <c r="M87"/>
+      <c r="N87"/>
+      <c r="P87"/>
+      <c r="Q87"/>
       <c r="S87"/>
       <c r="T87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>705</v>
+      </c>
+      <c r="B88" t="s">
+        <v>795</v>
+      </c>
+      <c r="C88" t="s">
+        <v>124</v>
+      </c>
+      <c r="D88" t="s">
+        <v>123</v>
+      </c>
+      <c r="E88" t="s">
+        <v>124</v>
+      </c>
+      <c r="F88" t="s">
+        <v>987</v>
+      </c>
+      <c r="G88" t="s">
+        <v>706</v>
+      </c>
+      <c r="H88" t="s">
+        <v>707</v>
+      </c>
+      <c r="I88" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J88" t="s">
+        <v>708</v>
+      </c>
+      <c r="K88" t="s">
+        <v>709</v>
+      </c>
+      <c r="L88" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M88" t="s">
+        <v>710</v>
+      </c>
+      <c r="N88" t="s">
         <v>711</v>
       </c>
-      <c r="B88" t="s">
-        <v>792</v>
-      </c>
-      <c r="C88" t="s">
-        <v>898</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="O88" t="s">
+        <v>1095</v>
+      </c>
+      <c r="P88" t="s">
         <v>712</v>
       </c>
-      <c r="E88" t="s">
+      <c r="Q88" t="s">
         <v>713</v>
       </c>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88" t="s">
-        <v>1009</v>
-      </c>
-      <c r="J88" t="s">
-        <v>714</v>
-      </c>
-      <c r="K88" t="s">
-        <v>715</v>
-      </c>
-      <c r="M88"/>
-      <c r="N88"/>
-      <c r="P88"/>
-      <c r="Q88"/>
       <c r="S88"/>
       <c r="T88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>714</v>
+      </c>
+      <c r="B89" t="s">
+        <v>795</v>
+      </c>
+      <c r="C89" t="s">
+        <v>903</v>
+      </c>
+      <c r="D89" t="s">
+        <v>715</v>
+      </c>
+      <c r="E89" t="s">
         <v>716</v>
-      </c>
-      <c r="B89" t="s">
-        <v>792</v>
-      </c>
-      <c r="C89" t="s">
-        <v>899</v>
-      </c>
-      <c r="D89" t="s">
-        <v>717</v>
-      </c>
-      <c r="E89" t="s">
-        <v>718</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
       <c r="I89" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="J89" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="K89" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="M89"/>
       <c r="N89"/>
@@ -8131,37 +8167,30 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>719</v>
+      </c>
+      <c r="B90" t="s">
+        <v>795</v>
+      </c>
+      <c r="C90" t="s">
+        <v>904</v>
+      </c>
+      <c r="D90" t="s">
+        <v>720</v>
+      </c>
+      <c r="E90" t="s">
         <v>721</v>
       </c>
-      <c r="B90" t="s">
-        <v>792</v>
-      </c>
-      <c r="C90" t="s">
-        <v>900</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90" t="s">
+        <v>1015</v>
+      </c>
+      <c r="J90" t="s">
         <v>722</v>
       </c>
-      <c r="E90" t="s">
+      <c r="K90" t="s">
         <v>723</v>
-      </c>
-      <c r="F90" t="s">
-        <v>983</v>
-      </c>
-      <c r="G90" t="s">
-        <v>724</v>
-      </c>
-      <c r="H90" t="s">
-        <v>725</v>
-      </c>
-      <c r="I90" t="s">
-        <v>1011</v>
-      </c>
-      <c r="J90" t="s">
-        <v>726</v>
-      </c>
-      <c r="K90" t="s">
-        <v>727</v>
       </c>
       <c r="M90"/>
       <c r="N90"/>
@@ -8172,24 +8201,38 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>724</v>
+      </c>
+      <c r="B91" t="s">
+        <v>795</v>
+      </c>
+      <c r="C91" t="s">
+        <v>905</v>
+      </c>
+      <c r="D91" t="s">
+        <v>725</v>
+      </c>
+      <c r="E91" t="s">
+        <v>726</v>
+      </c>
+      <c r="F91" t="s">
+        <v>988</v>
+      </c>
+      <c r="G91" t="s">
+        <v>727</v>
+      </c>
+      <c r="H91" t="s">
         <v>728</v>
       </c>
-      <c r="B91" t="s">
-        <v>792</v>
-      </c>
-      <c r="C91" t="s">
-        <v>901</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="I91" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J91" t="s">
         <v>729</v>
       </c>
-      <c r="E91" t="s">
+      <c r="K91" t="s">
         <v>730</v>
       </c>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="J91"/>
-      <c r="K91"/>
       <c r="M91"/>
       <c r="N91"/>
       <c r="P91"/>
@@ -8202,10 +8245,10 @@
         <v>731</v>
       </c>
       <c r="B92" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C92" t="s">
-        <v>733</v>
+        <v>906</v>
       </c>
       <c r="D92" t="s">
         <v>732</v>
@@ -8215,15 +8258,8 @@
       </c>
       <c r="G92"/>
       <c r="H92"/>
-      <c r="I92" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J92" t="s">
-        <v>734</v>
-      </c>
-      <c r="K92" t="s">
-        <v>735</v>
-      </c>
+      <c r="J92"/>
+      <c r="K92"/>
       <c r="M92"/>
       <c r="N92"/>
       <c r="P92"/>
@@ -8233,24 +8269,24 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>734</v>
+      </c>
+      <c r="B93" t="s">
+        <v>795</v>
+      </c>
+      <c r="C93" t="s">
         <v>736</v>
       </c>
-      <c r="B93" t="s">
-        <v>796</v>
-      </c>
-      <c r="C93" t="s">
-        <v>898</v>
-      </c>
       <c r="D93" t="s">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="E93" t="s">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
       <c r="I93" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="J93" t="s">
         <v>737</v>
@@ -8270,28 +8306,21 @@
         <v>739</v>
       </c>
       <c r="B94" t="s">
-        <v>823</v>
+        <v>799</v>
       </c>
       <c r="C94" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D94" t="s">
-        <v>740</v>
+        <v>715</v>
       </c>
       <c r="E94" t="s">
-        <v>741</v>
-      </c>
-      <c r="F94" t="s">
-        <v>984</v>
-      </c>
-      <c r="G94" t="s">
-        <v>742</v>
-      </c>
-      <c r="H94" t="s">
-        <v>743</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="G94"/>
+      <c r="H94"/>
       <c r="I94" t="s">
-        <v>902</v>
+        <v>1018</v>
       </c>
       <c r="J94" t="s">
         <v>740</v>
@@ -8299,306 +8328,347 @@
       <c r="K94" t="s">
         <v>741</v>
       </c>
-      <c r="L94" t="s">
-        <v>1082</v>
-      </c>
-      <c r="M94" t="s">
-        <v>744</v>
-      </c>
-      <c r="N94" t="s">
-        <v>745</v>
-      </c>
+      <c r="M94"/>
+      <c r="N94"/>
       <c r="P94"/>
       <c r="Q94"/>
-      <c r="R94" t="s">
-        <v>1135</v>
-      </c>
-      <c r="S94" t="s">
-        <v>558</v>
-      </c>
-      <c r="T94" t="s">
-        <v>559</v>
-      </c>
+      <c r="S94"/>
+      <c r="T94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>742</v>
+      </c>
+      <c r="B95" t="s">
+        <v>827</v>
+      </c>
+      <c r="C95" t="s">
+        <v>907</v>
+      </c>
+      <c r="D95" t="s">
+        <v>743</v>
+      </c>
+      <c r="E95" t="s">
+        <v>744</v>
+      </c>
+      <c r="F95" t="s">
+        <v>989</v>
+      </c>
+      <c r="G95" t="s">
+        <v>745</v>
+      </c>
+      <c r="H95" t="s">
         <v>746</v>
       </c>
-      <c r="B95" t="s">
-        <v>824</v>
-      </c>
-      <c r="C95" t="s">
-        <v>903</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="I95" t="s">
+        <v>907</v>
+      </c>
+      <c r="J95" t="s">
+        <v>743</v>
+      </c>
+      <c r="K95" t="s">
+        <v>744</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1087</v>
+      </c>
+      <c r="M95" t="s">
         <v>747</v>
       </c>
-      <c r="E95" t="s">
+      <c r="N95" t="s">
         <v>748</v>
       </c>
-      <c r="F95" t="s">
-        <v>985</v>
-      </c>
-      <c r="G95" t="s">
-        <v>749</v>
-      </c>
-      <c r="H95" t="s">
-        <v>750</v>
-      </c>
-      <c r="I95" t="s">
-        <v>903</v>
-      </c>
-      <c r="J95" t="s">
-        <v>747</v>
-      </c>
-      <c r="K95" t="s">
-        <v>748</v>
-      </c>
-      <c r="M95"/>
-      <c r="N95"/>
       <c r="P95"/>
       <c r="Q95"/>
-      <c r="S95"/>
-      <c r="T95"/>
+      <c r="R95" t="s">
+        <v>1140</v>
+      </c>
+      <c r="S95" t="s">
+        <v>561</v>
+      </c>
+      <c r="T95" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>749</v>
+      </c>
+      <c r="B96" t="s">
+        <v>828</v>
+      </c>
+      <c r="C96" t="s">
+        <v>908</v>
+      </c>
+      <c r="D96" t="s">
+        <v>750</v>
+      </c>
+      <c r="E96" t="s">
         <v>751</v>
       </c>
-      <c r="B96" t="s">
-        <v>825</v>
-      </c>
-      <c r="C96" t="s">
-        <v>904</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
+        <v>990</v>
+      </c>
+      <c r="G96" t="s">
         <v>752</v>
       </c>
-      <c r="E96" t="s">
+      <c r="H96" t="s">
         <v>753</v>
       </c>
-      <c r="F96" t="s">
-        <v>986</v>
-      </c>
-      <c r="G96" t="s">
-        <v>754</v>
-      </c>
-      <c r="H96" t="s">
-        <v>755</v>
-      </c>
-      <c r="J96"/>
-      <c r="K96"/>
-      <c r="L96" t="s">
-        <v>1083</v>
-      </c>
-      <c r="M96" t="s">
-        <v>756</v>
-      </c>
-      <c r="N96" t="s">
-        <v>757</v>
-      </c>
+      <c r="I96" t="s">
+        <v>908</v>
+      </c>
+      <c r="J96" t="s">
+        <v>750</v>
+      </c>
+      <c r="K96" t="s">
+        <v>751</v>
+      </c>
+      <c r="M96"/>
+      <c r="N96"/>
       <c r="P96"/>
       <c r="Q96"/>
-      <c r="R96" t="s">
-        <v>1144</v>
-      </c>
-      <c r="S96" t="s">
-        <v>758</v>
-      </c>
-      <c r="T96" t="s">
-        <v>759</v>
-      </c>
+      <c r="S96"/>
+      <c r="T96"/>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="B97" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C97" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="D97" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="E97" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="F97" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="G97" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="H97" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="M97" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="N97" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="P97"/>
       <c r="Q97"/>
       <c r="R97" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="S97" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="T97" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>763</v>
+      </c>
+      <c r="B98" t="s">
+        <v>829</v>
+      </c>
+      <c r="C98" t="s">
+        <v>910</v>
+      </c>
+      <c r="D98" t="s">
+        <v>764</v>
+      </c>
+      <c r="E98" t="s">
+        <v>765</v>
+      </c>
+      <c r="F98" t="s">
+        <v>992</v>
+      </c>
+      <c r="G98" t="s">
+        <v>766</v>
+      </c>
+      <c r="H98" t="s">
         <v>767</v>
-      </c>
-      <c r="B98" t="s">
-        <v>825</v>
-      </c>
-      <c r="C98" t="s">
-        <v>906</v>
-      </c>
-      <c r="D98" t="s">
-        <v>768</v>
-      </c>
-      <c r="E98" t="s">
-        <v>769</v>
-      </c>
-      <c r="F98" t="s">
-        <v>988</v>
-      </c>
-      <c r="G98" t="s">
-        <v>770</v>
-      </c>
-      <c r="H98" t="s">
-        <v>771</v>
       </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="M98" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="N98" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="P98"/>
       <c r="Q98"/>
       <c r="R98" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="S98" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="T98" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>770</v>
+      </c>
+      <c r="B99" t="s">
+        <v>829</v>
+      </c>
+      <c r="C99" t="s">
+        <v>911</v>
+      </c>
+      <c r="D99" t="s">
+        <v>771</v>
+      </c>
+      <c r="E99" t="s">
         <v>772</v>
       </c>
-      <c r="B99" t="s">
-        <v>826</v>
-      </c>
-      <c r="C99" t="s">
-        <v>907</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
+        <v>993</v>
+      </c>
+      <c r="G99" t="s">
         <v>773</v>
       </c>
-      <c r="E99" t="s">
+      <c r="H99" t="s">
         <v>774</v>
-      </c>
-      <c r="F99" t="s">
-        <v>989</v>
-      </c>
-      <c r="G99" t="s">
-        <v>775</v>
-      </c>
-      <c r="H99" t="s">
-        <v>776</v>
       </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="M99" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="N99" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="P99"/>
       <c r="Q99"/>
       <c r="R99" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="S99" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="T99" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>775</v>
+      </c>
+      <c r="B100" t="s">
+        <v>830</v>
+      </c>
+      <c r="C100" t="s">
+        <v>912</v>
+      </c>
+      <c r="D100" t="s">
+        <v>776</v>
+      </c>
+      <c r="E100" t="s">
+        <v>777</v>
+      </c>
+      <c r="F100" t="s">
+        <v>994</v>
+      </c>
+      <c r="G100" t="s">
+        <v>778</v>
+      </c>
+      <c r="H100" t="s">
         <v>779</v>
-      </c>
-      <c r="B100" t="s">
-        <v>826</v>
-      </c>
-      <c r="C100" t="s">
-        <v>908</v>
-      </c>
-      <c r="D100" t="s">
-        <v>780</v>
-      </c>
-      <c r="E100" t="s">
-        <v>781</v>
-      </c>
-      <c r="F100" t="s">
-        <v>990</v>
-      </c>
-      <c r="G100" t="s">
-        <v>782</v>
-      </c>
-      <c r="H100" t="s">
-        <v>783</v>
       </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="M100" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="N100" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="P100"/>
       <c r="Q100"/>
       <c r="R100" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="S100" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="T100" t="s">
-        <v>759</v>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>782</v>
+      </c>
+      <c r="B101" t="s">
+        <v>830</v>
+      </c>
+      <c r="C101" t="s">
+        <v>913</v>
+      </c>
+      <c r="D101" t="s">
+        <v>783</v>
+      </c>
+      <c r="E101" t="s">
+        <v>784</v>
+      </c>
+      <c r="F101" t="s">
+        <v>995</v>
+      </c>
+      <c r="G101" t="s">
+        <v>785</v>
+      </c>
+      <c r="H101" t="s">
+        <v>786</v>
+      </c>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M101" t="s">
+        <v>787</v>
+      </c>
+      <c r="N101" t="s">
+        <v>788</v>
+      </c>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101" t="s">
+        <v>1149</v>
+      </c>
+      <c r="S101" t="s">
+        <v>761</v>
+      </c>
+      <c r="T101" t="s">
+        <v>762</v>
       </c>
     </row>
   </sheetData>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Stat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="1145">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">55</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Taunt</t>
@@ -1503,15 +1503,6 @@
   </si>
   <si>
     <t xml:space="preserve">#1は擬態を解いた！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Guise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">擬人</t>
   </si>
   <si>
     <t xml:space="preserve">105</t>
@@ -2496,9 +2487,6 @@
     <t xml:space="preserve">EA 23.257</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.291</t>
-  </si>
-  <si>
     <t xml:space="preserve">EA 23.268</t>
   </si>
   <si>
@@ -2677,9 +2665,6 @@
   </si>
   <si>
     <t xml:space="preserve">拟态</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拟人</t>
   </si>
   <si>
     <t xml:space="preserve">身缠暗影</t>
@@ -3672,10 +3657,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C3" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3684,7 +3669,7 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="G3" t="s">
         <v>24</v>
@@ -3693,7 +3678,7 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J3" t="s">
         <v>26</v>
@@ -3702,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -3713,7 +3698,7 @@
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="S3" t="s">
         <v>30</v>
@@ -3727,10 +3712,10 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C4" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -3739,7 +3724,7 @@
         <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
@@ -3748,7 +3733,7 @@
         <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="J4" t="s">
         <v>33</v>
@@ -3757,7 +3742,7 @@
         <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -3768,7 +3753,7 @@
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="S4" t="s">
         <v>39</v>
@@ -3782,10 +3767,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C5" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
@@ -3794,7 +3779,7 @@
         <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="G5" t="s">
         <v>44</v>
@@ -3803,7 +3788,7 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="J5" t="s">
         <v>42</v>
@@ -3812,7 +3797,7 @@
         <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -3823,7 +3808,7 @@
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="S5" t="s">
         <v>48</v>
@@ -3837,10 +3822,10 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C6" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -3849,7 +3834,7 @@
         <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="G6" t="s">
         <v>53</v>
@@ -3858,7 +3843,7 @@
         <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="J6" t="s">
         <v>51</v>
@@ -3867,7 +3852,7 @@
         <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="M6" t="s">
         <v>55</v>
@@ -3878,7 +3863,7 @@
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="S6" t="s">
         <v>57</v>
@@ -3892,10 +3877,10 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C7" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -3904,7 +3889,7 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="G7" t="s">
         <v>62</v>
@@ -3913,7 +3898,7 @@
         <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J7" t="s">
         <v>60</v>
@@ -3922,7 +3907,7 @@
         <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="M7" t="s">
         <v>64</v>
@@ -3933,7 +3918,7 @@
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="S7" t="s">
         <v>66</v>
@@ -3947,10 +3932,10 @@
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C8" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="D8" t="s">
         <v>69</v>
@@ -3959,7 +3944,7 @@
         <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="G8" t="s">
         <v>71</v>
@@ -3968,7 +3953,7 @@
         <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="J8" t="s">
         <v>69</v>
@@ -3977,7 +3962,7 @@
         <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="M8" t="s">
         <v>73</v>
@@ -3988,7 +3973,7 @@
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="S8" t="s">
         <v>66</v>
@@ -4002,10 +3987,10 @@
         <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C9" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="D9" t="s">
         <v>76</v>
@@ -4014,7 +3999,7 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="G9" t="s">
         <v>71</v>
@@ -4023,7 +4008,7 @@
         <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="J9" t="s">
         <v>76</v>
@@ -4032,7 +4017,7 @@
         <v>77</v>
       </c>
       <c r="L9" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="M9" t="s">
         <v>78</v>
@@ -4043,7 +4028,7 @@
       <c r="P9"/>
       <c r="Q9"/>
       <c r="R9" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="S9" t="s">
         <v>66</v>
@@ -4057,7 +4042,7 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C10" t="s">
         <v>82</v>
@@ -4069,7 +4054,7 @@
         <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="G10" t="s">
         <v>83</v>
@@ -4078,7 +4063,7 @@
         <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="J10" t="s">
         <v>85</v>
@@ -4087,7 +4072,7 @@
         <v>86</v>
       </c>
       <c r="L10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="M10" t="s">
         <v>87</v>
@@ -4096,7 +4081,7 @@
         <v>88</v>
       </c>
       <c r="O10" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="P10" t="s">
         <v>89</v>
@@ -4105,7 +4090,7 @@
         <v>90</v>
       </c>
       <c r="R10" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="S10" t="s">
         <v>91</v>
@@ -4119,10 +4104,10 @@
         <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C11" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -4131,7 +4116,7 @@
         <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="G11" t="s">
         <v>96</v>
@@ -4140,7 +4125,7 @@
         <v>97</v>
       </c>
       <c r="I11" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="J11" t="s">
         <v>98</v>
@@ -4149,7 +4134,7 @@
         <v>99</v>
       </c>
       <c r="L11" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="M11" t="s">
         <v>100</v>
@@ -4158,7 +4143,7 @@
         <v>101</v>
       </c>
       <c r="O11" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="P11" t="s">
         <v>102</v>
@@ -4174,10 +4159,10 @@
         <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C12" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="D12" t="s">
         <v>105</v>
@@ -4186,7 +4171,7 @@
         <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="G12" t="s">
         <v>107</v>
@@ -4195,7 +4180,7 @@
         <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="J12" t="s">
         <v>105</v>
@@ -4204,7 +4189,7 @@
         <v>106</v>
       </c>
       <c r="L12" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="M12" t="s">
         <v>109</v>
@@ -4215,7 +4200,7 @@
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="S12" t="s">
         <v>111</v>
@@ -4229,10 +4214,10 @@
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C13" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="D13" t="s">
         <v>114</v>
@@ -4241,7 +4226,7 @@
         <v>115</v>
       </c>
       <c r="F13" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="G13" t="s">
         <v>116</v>
@@ -4250,7 +4235,7 @@
         <v>117</v>
       </c>
       <c r="I13" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="J13" t="s">
         <v>114</v>
@@ -4259,7 +4244,7 @@
         <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="M13" t="s">
         <v>118</v>
@@ -4270,7 +4255,7 @@
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="S13" t="s">
         <v>120</v>
@@ -4284,7 +4269,7 @@
         <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C14" t="s">
         <v>124</v>
@@ -4296,7 +4281,7 @@
         <v>124</v>
       </c>
       <c r="F14" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="G14" t="s">
         <v>125</v>
@@ -4314,7 +4299,7 @@
         <v>124</v>
       </c>
       <c r="L14" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="M14" t="s">
         <v>128</v>
@@ -4325,7 +4310,7 @@
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="S14" t="s">
         <v>130</v>
@@ -4339,10 +4324,10 @@
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C15" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -4351,7 +4336,7 @@
         <v>134</v>
       </c>
       <c r="F15" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G15" t="s">
         <v>135</v>
@@ -4360,7 +4345,7 @@
         <v>136</v>
       </c>
       <c r="I15" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="J15" t="s">
         <v>137</v>
@@ -4369,7 +4354,7 @@
         <v>134</v>
       </c>
       <c r="L15" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="M15" t="s">
         <v>138</v>
@@ -4380,7 +4365,7 @@
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="S15" t="s">
         <v>140</v>
@@ -4394,7 +4379,7 @@
         <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C16" t="s">
         <v>144</v>
@@ -4406,7 +4391,7 @@
         <v>144</v>
       </c>
       <c r="F16" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="G16" t="s">
         <v>145</v>
@@ -4424,7 +4409,7 @@
         <v>144</v>
       </c>
       <c r="L16" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="M16" t="s">
         <v>148</v>
@@ -4435,7 +4420,7 @@
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="S16" t="s">
         <v>150</v>
@@ -4449,10 +4434,10 @@
         <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C17" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D17" t="s">
         <v>153</v>
@@ -4461,7 +4446,7 @@
         <v>154</v>
       </c>
       <c r="F17" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G17" t="s">
         <v>135</v>
@@ -4470,7 +4455,7 @@
         <v>136</v>
       </c>
       <c r="I17" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="J17" t="s">
         <v>155</v>
@@ -4479,7 +4464,7 @@
         <v>154</v>
       </c>
       <c r="L17" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="M17" t="s">
         <v>156</v>
@@ -4490,7 +4475,7 @@
       <c r="P17"/>
       <c r="Q17"/>
       <c r="R17" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="S17" t="s">
         <v>158</v>
@@ -4504,7 +4489,7 @@
         <v>160</v>
       </c>
       <c r="B18" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C18" t="s">
         <v>162</v>
@@ -4516,7 +4501,7 @@
         <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="G18" t="s">
         <v>163</v>
@@ -4534,7 +4519,7 @@
         <v>162</v>
       </c>
       <c r="L18" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="M18" t="s">
         <v>166</v>
@@ -4545,7 +4530,7 @@
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="S18" t="s">
         <v>168</v>
@@ -4559,10 +4544,10 @@
         <v>170</v>
       </c>
       <c r="B19" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C19" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D19" t="s">
         <v>171</v>
@@ -4571,7 +4556,7 @@
         <v>172</v>
       </c>
       <c r="F19" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="G19" t="s">
         <v>173</v>
@@ -4580,7 +4565,7 @@
         <v>174</v>
       </c>
       <c r="I19" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="J19" t="s">
         <v>171</v>
@@ -4589,7 +4574,7 @@
         <v>172</v>
       </c>
       <c r="L19" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="M19" t="s">
         <v>175</v>
@@ -4600,7 +4585,7 @@
       <c r="P19"/>
       <c r="Q19"/>
       <c r="R19" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="S19" t="s">
         <v>177</v>
@@ -4614,10 +4599,10 @@
         <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C20" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="D20" t="s">
         <v>180</v>
@@ -4626,7 +4611,7 @@
         <v>181</v>
       </c>
       <c r="F20" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="G20" t="s">
         <v>182</v>
@@ -4635,7 +4620,7 @@
         <v>183</v>
       </c>
       <c r="I20" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J20" t="s">
         <v>184</v>
@@ -4644,7 +4629,7 @@
         <v>185</v>
       </c>
       <c r="L20" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="M20" t="s">
         <v>186</v>
@@ -4655,7 +4640,7 @@
       <c r="P20"/>
       <c r="Q20"/>
       <c r="R20" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="S20" t="s">
         <v>188</v>
@@ -4669,7 +4654,7 @@
         <v>190</v>
       </c>
       <c r="B21" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C21" t="s">
         <v>192</v>
@@ -4681,7 +4666,7 @@
         <v>192</v>
       </c>
       <c r="F21" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="G21" t="s">
         <v>193</v>
@@ -4690,7 +4675,7 @@
         <v>194</v>
       </c>
       <c r="I21" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="J21" t="s">
         <v>195</v>
@@ -4699,7 +4684,7 @@
         <v>196</v>
       </c>
       <c r="L21" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="M21" t="s">
         <v>197</v>
@@ -4710,7 +4695,7 @@
       <c r="P21"/>
       <c r="Q21"/>
       <c r="R21" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="S21" t="s">
         <v>199</v>
@@ -4724,10 +4709,10 @@
         <v>201</v>
       </c>
       <c r="B22" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C22" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="D22" t="s">
         <v>202</v>
@@ -4736,7 +4721,7 @@
         <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="G22" t="s">
         <v>204</v>
@@ -4745,7 +4730,7 @@
         <v>205</v>
       </c>
       <c r="I22" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="J22" t="s">
         <v>206</v>
@@ -4754,7 +4739,7 @@
         <v>207</v>
       </c>
       <c r="L22" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="M22" t="s">
         <v>208</v>
@@ -4765,7 +4750,7 @@
       <c r="P22"/>
       <c r="Q22"/>
       <c r="R22" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="S22" t="s">
         <v>210</v>
@@ -4779,10 +4764,10 @@
         <v>212</v>
       </c>
       <c r="B23" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C23" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D23" t="s">
         <v>213</v>
@@ -4791,7 +4776,7 @@
         <v>214</v>
       </c>
       <c r="F23" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G23" t="s">
         <v>215</v>
@@ -4800,7 +4785,7 @@
         <v>216</v>
       </c>
       <c r="I23" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J23" t="s">
         <v>217</v>
@@ -4809,7 +4794,7 @@
         <v>218</v>
       </c>
       <c r="L23" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="M23" t="s">
         <v>219</v>
@@ -4820,7 +4805,7 @@
       <c r="P23"/>
       <c r="Q23"/>
       <c r="R23" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="S23" t="s">
         <v>221</v>
@@ -4834,10 +4819,10 @@
         <v>223</v>
       </c>
       <c r="B24" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C24" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="D24" t="s">
         <v>224</v>
@@ -4846,7 +4831,7 @@
         <v>225</v>
       </c>
       <c r="F24" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="G24" t="s">
         <v>226</v>
@@ -4855,7 +4840,7 @@
         <v>227</v>
       </c>
       <c r="I24" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="J24" t="s">
         <v>228</v>
@@ -4864,7 +4849,7 @@
         <v>229</v>
       </c>
       <c r="L24" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="M24" t="s">
         <v>230</v>
@@ -4875,7 +4860,7 @@
       <c r="P24"/>
       <c r="Q24"/>
       <c r="R24" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="S24" t="s">
         <v>232</v>
@@ -4889,10 +4874,10 @@
         <v>234</v>
       </c>
       <c r="B25" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C25" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D25" t="s">
         <v>235</v>
@@ -4901,7 +4886,7 @@
         <v>236</v>
       </c>
       <c r="F25" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="G25" t="s">
         <v>237</v>
@@ -4910,7 +4895,7 @@
         <v>238</v>
       </c>
       <c r="I25" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="J25" t="s">
         <v>235</v>
@@ -4919,7 +4904,7 @@
         <v>236</v>
       </c>
       <c r="L25" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="M25" t="s">
         <v>239</v>
@@ -4930,7 +4915,7 @@
       <c r="P25"/>
       <c r="Q25"/>
       <c r="R25" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="S25" t="s">
         <v>241</v>
@@ -4944,10 +4929,10 @@
         <v>243</v>
       </c>
       <c r="B26" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C26" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D26" t="s">
         <v>244</v>
@@ -4956,7 +4941,7 @@
         <v>245</v>
       </c>
       <c r="F26" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G26" t="s">
         <v>246</v>
@@ -4965,7 +4950,7 @@
         <v>247</v>
       </c>
       <c r="I26" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="J26" t="s">
         <v>244</v>
@@ -4974,7 +4959,7 @@
         <v>245</v>
       </c>
       <c r="L26" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="M26" t="s">
         <v>248</v>
@@ -4992,10 +4977,10 @@
         <v>250</v>
       </c>
       <c r="B27" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C27" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="D27" t="s">
         <v>251</v>
@@ -5004,7 +4989,7 @@
         <v>252</v>
       </c>
       <c r="F27" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="G27" t="s">
         <v>253</v>
@@ -5013,7 +4998,7 @@
         <v>254</v>
       </c>
       <c r="I27" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="J27" t="s">
         <v>251</v>
@@ -5022,7 +5007,7 @@
         <v>252</v>
       </c>
       <c r="L27" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="M27" t="s">
         <v>255</v>
@@ -5033,7 +5018,7 @@
       <c r="P27"/>
       <c r="Q27"/>
       <c r="R27" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="S27" t="s">
         <v>257</v>
@@ -5047,10 +5032,10 @@
         <v>259</v>
       </c>
       <c r="B28" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C28" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="D28" t="s">
         <v>260</v>
@@ -5059,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="F28" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="G28" t="s">
         <v>262</v>
@@ -5068,7 +5053,7 @@
         <v>263</v>
       </c>
       <c r="I28" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="J28" t="s">
         <v>260</v>
@@ -5077,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="L28" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="M28" t="s">
         <v>264</v>
@@ -5088,7 +5073,7 @@
       <c r="P28"/>
       <c r="Q28"/>
       <c r="R28" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="S28" t="s">
         <v>266</v>
@@ -5102,10 +5087,10 @@
         <v>268</v>
       </c>
       <c r="B29" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C29" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="D29" t="s">
         <v>269</v>
@@ -5114,7 +5099,7 @@
         <v>270</v>
       </c>
       <c r="F29" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="G29" t="s">
         <v>271</v>
@@ -5123,7 +5108,7 @@
         <v>272</v>
       </c>
       <c r="I29" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="J29" t="s">
         <v>269</v>
@@ -5132,7 +5117,7 @@
         <v>270</v>
       </c>
       <c r="L29" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="M29" t="s">
         <v>273</v>
@@ -5143,7 +5128,7 @@
       <c r="P29"/>
       <c r="Q29"/>
       <c r="R29" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="S29" t="s">
         <v>275</v>
@@ -5157,10 +5142,10 @@
         <v>277</v>
       </c>
       <c r="B30" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C30" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D30" t="s">
         <v>278</v>
@@ -5169,7 +5154,7 @@
         <v>279</v>
       </c>
       <c r="F30" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="G30" t="s">
         <v>280</v>
@@ -5178,7 +5163,7 @@
         <v>281</v>
       </c>
       <c r="I30" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="J30" t="s">
         <v>278</v>
@@ -5187,7 +5172,7 @@
         <v>279</v>
       </c>
       <c r="L30" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="M30" t="s">
         <v>282</v>
@@ -5198,7 +5183,7 @@
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="S30" t="s">
         <v>284</v>
@@ -5212,7 +5197,7 @@
         <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C31" t="s">
         <v>288</v>
@@ -5224,7 +5209,7 @@
         <v>288</v>
       </c>
       <c r="F31" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G31" t="s">
         <v>289</v>
@@ -5242,7 +5227,7 @@
         <v>288</v>
       </c>
       <c r="L31" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="M31" t="s">
         <v>291</v>
@@ -5253,7 +5238,7 @@
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="S31" t="s">
         <v>293</v>
@@ -5267,10 +5252,10 @@
         <v>295</v>
       </c>
       <c r="B32" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C32" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="D32" t="s">
         <v>296</v>
@@ -5279,7 +5264,7 @@
         <v>297</v>
       </c>
       <c r="F32" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="G32" t="s">
         <v>298</v>
@@ -5288,7 +5273,7 @@
         <v>299</v>
       </c>
       <c r="I32" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="J32" t="s">
         <v>296</v>
@@ -5297,7 +5282,7 @@
         <v>297</v>
       </c>
       <c r="L32" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="M32" t="s">
         <v>300</v>
@@ -5308,7 +5293,7 @@
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="S32" t="s">
         <v>302</v>
@@ -5322,10 +5307,10 @@
         <v>304</v>
       </c>
       <c r="B33" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C33" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="D33" t="s">
         <v>305</v>
@@ -5334,7 +5319,7 @@
         <v>306</v>
       </c>
       <c r="F33" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="G33" t="s">
         <v>307</v>
@@ -5343,7 +5328,7 @@
         <v>308</v>
       </c>
       <c r="I33" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="J33" t="s">
         <v>305</v>
@@ -5352,7 +5337,7 @@
         <v>306</v>
       </c>
       <c r="L33" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="M33" t="s">
         <v>309</v>
@@ -5363,7 +5348,7 @@
       <c r="P33"/>
       <c r="Q33"/>
       <c r="R33" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="S33" t="s">
         <v>311</v>
@@ -5377,10 +5362,10 @@
         <v>313</v>
       </c>
       <c r="B34" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C34" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="D34" t="s">
         <v>314</v>
@@ -5389,7 +5374,7 @@
         <v>315</v>
       </c>
       <c r="F34" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="G34" t="s">
         <v>316</v>
@@ -5398,7 +5383,7 @@
         <v>317</v>
       </c>
       <c r="I34" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="s">
         <v>318</v>
@@ -5407,7 +5392,7 @@
         <v>319</v>
       </c>
       <c r="L34" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="M34" t="s">
         <v>320</v>
@@ -5418,7 +5403,7 @@
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="S34" t="s">
         <v>322</v>
@@ -5432,10 +5417,10 @@
         <v>324</v>
       </c>
       <c r="B35" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C35" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="D35" t="s">
         <v>325</v>
@@ -5444,7 +5429,7 @@
         <v>326</v>
       </c>
       <c r="F35" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="G35" t="s">
         <v>327</v>
@@ -5453,7 +5438,7 @@
         <v>328</v>
       </c>
       <c r="I35" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="J35" t="s">
         <v>325</v>
@@ -5462,7 +5447,7 @@
         <v>326</v>
       </c>
       <c r="L35" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="M35" t="s">
         <v>329</v>
@@ -5473,7 +5458,7 @@
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="S35" t="s">
         <v>331</v>
@@ -5487,10 +5472,10 @@
         <v>333</v>
       </c>
       <c r="B36" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C36" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="D36" t="s">
         <v>334</v>
@@ -5499,7 +5484,7 @@
         <v>335</v>
       </c>
       <c r="F36" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="G36" t="s">
         <v>336</v>
@@ -5508,7 +5493,7 @@
         <v>337</v>
       </c>
       <c r="I36" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="J36" t="s">
         <v>334</v>
@@ -5517,7 +5502,7 @@
         <v>335</v>
       </c>
       <c r="L36" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="M36" t="s">
         <v>338</v>
@@ -5528,7 +5513,7 @@
       <c r="P36"/>
       <c r="Q36"/>
       <c r="R36" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="S36" t="s">
         <v>340</v>
@@ -5542,10 +5527,10 @@
         <v>342</v>
       </c>
       <c r="B37" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C37" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="D37" t="s">
         <v>343</v>
@@ -5554,7 +5539,7 @@
         <v>344</v>
       </c>
       <c r="F37" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="G37" t="s">
         <v>345</v>
@@ -5563,7 +5548,7 @@
         <v>346</v>
       </c>
       <c r="I37" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J37" t="s">
         <v>347</v>
@@ -5572,7 +5557,7 @@
         <v>344</v>
       </c>
       <c r="L37" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="M37" t="s">
         <v>348</v>
@@ -5583,7 +5568,7 @@
       <c r="P37"/>
       <c r="Q37"/>
       <c r="R37" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="S37" t="s">
         <v>350</v>
@@ -5597,7 +5582,7 @@
         <v>352</v>
       </c>
       <c r="B38" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C38" t="s">
         <v>354</v>
@@ -5609,7 +5594,7 @@
         <v>354</v>
       </c>
       <c r="F38" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G38" t="s">
         <v>355</v>
@@ -5627,7 +5612,7 @@
         <v>354</v>
       </c>
       <c r="L38" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="M38" t="s">
         <v>357</v>
@@ -5638,7 +5623,7 @@
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="S38" t="s">
         <v>359</v>
@@ -5652,10 +5637,10 @@
         <v>361</v>
       </c>
       <c r="B39" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C39" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="D39" t="s">
         <v>362</v>
@@ -5664,7 +5649,7 @@
         <v>363</v>
       </c>
       <c r="F39" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="G39" t="s">
         <v>364</v>
@@ -5673,7 +5658,7 @@
         <v>365</v>
       </c>
       <c r="I39" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="J39" t="s">
         <v>366</v>
@@ -5682,7 +5667,7 @@
         <v>363</v>
       </c>
       <c r="L39" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="M39" t="s">
         <v>367</v>
@@ -5693,7 +5678,7 @@
       <c r="P39"/>
       <c r="Q39"/>
       <c r="R39" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="S39" t="s">
         <v>369</v>
@@ -5707,10 +5692,10 @@
         <v>371</v>
       </c>
       <c r="B40" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C40" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D40" t="s">
         <v>372</v>
@@ -5719,7 +5704,7 @@
         <v>373</v>
       </c>
       <c r="F40" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="G40" t="s">
         <v>374</v>
@@ -5728,7 +5713,7 @@
         <v>375</v>
       </c>
       <c r="I40" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="J40" t="s">
         <v>372</v>
@@ -5737,7 +5722,7 @@
         <v>373</v>
       </c>
       <c r="L40" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="M40" t="s">
         <v>376</v>
@@ -5748,7 +5733,7 @@
       <c r="P40"/>
       <c r="Q40"/>
       <c r="R40" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="S40" t="s">
         <v>378</v>
@@ -5762,10 +5747,10 @@
         <v>380</v>
       </c>
       <c r="B41" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C41" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D41" t="s">
         <v>381</v>
@@ -5774,7 +5759,7 @@
         <v>382</v>
       </c>
       <c r="F41" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="G41" t="s">
         <v>383</v>
@@ -5783,7 +5768,7 @@
         <v>384</v>
       </c>
       <c r="I41" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="J41" t="s">
         <v>381</v>
@@ -5792,7 +5777,7 @@
         <v>382</v>
       </c>
       <c r="L41" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="M41" t="s">
         <v>385</v>
@@ -5803,7 +5788,7 @@
       <c r="P41"/>
       <c r="Q41"/>
       <c r="R41" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="S41" t="s">
         <v>387</v>
@@ -5817,10 +5802,10 @@
         <v>389</v>
       </c>
       <c r="B42" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C42" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="D42" t="s">
         <v>390</v>
@@ -5829,7 +5814,7 @@
         <v>391</v>
       </c>
       <c r="F42" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="G42" t="s">
         <v>392</v>
@@ -5838,7 +5823,7 @@
         <v>393</v>
       </c>
       <c r="I42" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="J42" t="s">
         <v>390</v>
@@ -5847,7 +5832,7 @@
         <v>391</v>
       </c>
       <c r="L42" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="M42" t="s">
         <v>394</v>
@@ -5865,10 +5850,10 @@
         <v>396</v>
       </c>
       <c r="B43" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C43" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D43" t="s">
         <v>397</v>
@@ -5877,7 +5862,7 @@
         <v>398</v>
       </c>
       <c r="F43" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="G43" t="s">
         <v>399</v>
@@ -5886,7 +5871,7 @@
         <v>400</v>
       </c>
       <c r="I43" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="J43" t="s">
         <v>397</v>
@@ -5906,10 +5891,10 @@
         <v>401</v>
       </c>
       <c r="B44" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C44" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D44" t="s">
         <v>402</v>
@@ -5918,7 +5903,7 @@
         <v>403</v>
       </c>
       <c r="F44" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="G44" t="s">
         <v>404</v>
@@ -5927,7 +5912,7 @@
         <v>405</v>
       </c>
       <c r="I44" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="J44" t="s">
         <v>402</v>
@@ -5947,10 +5932,10 @@
         <v>406</v>
       </c>
       <c r="B45" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C45" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="D45" t="s">
         <v>407</v>
@@ -5959,7 +5944,7 @@
         <v>408</v>
       </c>
       <c r="F45" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G45" t="s">
         <v>409</v>
@@ -5968,7 +5953,7 @@
         <v>410</v>
       </c>
       <c r="I45" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="J45" t="s">
         <v>407</v>
@@ -5977,7 +5962,7 @@
         <v>408</v>
       </c>
       <c r="L45" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="M45" t="s">
         <v>411</v>
@@ -5988,7 +5973,7 @@
       <c r="P45"/>
       <c r="Q45"/>
       <c r="R45" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="S45" t="s">
         <v>413</v>
@@ -6002,10 +5987,10 @@
         <v>415</v>
       </c>
       <c r="B46" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C46" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D46" t="s">
         <v>416</v>
@@ -6014,7 +5999,7 @@
         <v>417</v>
       </c>
       <c r="F46" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="G46" t="s">
         <v>418</v>
@@ -6023,7 +6008,7 @@
         <v>419</v>
       </c>
       <c r="I46" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="J46" t="s">
         <v>420</v>
@@ -6032,7 +6017,7 @@
         <v>417</v>
       </c>
       <c r="L46" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="M46" t="s">
         <v>421</v>
@@ -6043,7 +6028,7 @@
       <c r="P46"/>
       <c r="Q46"/>
       <c r="R46" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="S46" t="s">
         <v>423</v>
@@ -6057,10 +6042,10 @@
         <v>425</v>
       </c>
       <c r="B47" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C47" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D47" t="s">
         <v>426</v>
@@ -6069,7 +6054,7 @@
         <v>427</v>
       </c>
       <c r="F47" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="G47" t="s">
         <v>428</v>
@@ -6078,7 +6063,7 @@
         <v>429</v>
       </c>
       <c r="I47" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="J47" t="s">
         <v>426</v>
@@ -6087,7 +6072,7 @@
         <v>427</v>
       </c>
       <c r="L47" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="M47" t="s">
         <v>430</v>
@@ -6098,7 +6083,7 @@
       <c r="P47"/>
       <c r="Q47"/>
       <c r="R47" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="S47" t="s">
         <v>331</v>
@@ -6112,10 +6097,10 @@
         <v>432</v>
       </c>
       <c r="B48" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C48" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="D48" t="s">
         <v>433</v>
@@ -6124,7 +6109,7 @@
         <v>434</v>
       </c>
       <c r="F48" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G48" t="s">
         <v>435</v>
@@ -6133,7 +6118,7 @@
         <v>436</v>
       </c>
       <c r="I48" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="J48" t="s">
         <v>433</v>
@@ -6142,7 +6127,7 @@
         <v>434</v>
       </c>
       <c r="L48" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="M48" t="s">
         <v>437</v>
@@ -6153,7 +6138,7 @@
       <c r="P48"/>
       <c r="Q48"/>
       <c r="R48" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="S48" t="s">
         <v>439</v>
@@ -6167,7 +6152,7 @@
         <v>441</v>
       </c>
       <c r="B49" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C49" t="s">
         <v>443</v>
@@ -6179,7 +6164,7 @@
         <v>443</v>
       </c>
       <c r="F49" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="G49" t="s">
         <v>444</v>
@@ -6197,7 +6182,7 @@
         <v>443</v>
       </c>
       <c r="L49" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="M49" t="s">
         <v>446</v>
@@ -6215,10 +6200,10 @@
         <v>448</v>
       </c>
       <c r="B50" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C50" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="D50" t="s">
         <v>449</v>
@@ -6227,7 +6212,7 @@
         <v>450</v>
       </c>
       <c r="F50" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="G50" t="s">
         <v>451</v>
@@ -6236,7 +6221,7 @@
         <v>452</v>
       </c>
       <c r="I50" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="J50" t="s">
         <v>449</v>
@@ -6245,7 +6230,7 @@
         <v>450</v>
       </c>
       <c r="L50" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="M50" t="s">
         <v>453</v>
@@ -6263,10 +6248,10 @@
         <v>455</v>
       </c>
       <c r="B51" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C51" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D51" t="s">
         <v>456</v>
@@ -6275,7 +6260,7 @@
         <v>457</v>
       </c>
       <c r="F51" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="G51" t="s">
         <v>458</v>
@@ -6284,7 +6269,7 @@
         <v>459</v>
       </c>
       <c r="I51" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="J51" t="s">
         <v>456</v>
@@ -6293,7 +6278,7 @@
         <v>457</v>
       </c>
       <c r="L51" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="M51" t="s">
         <v>460</v>
@@ -6304,7 +6289,7 @@
       <c r="P51"/>
       <c r="Q51"/>
       <c r="R51" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="S51" t="s">
         <v>462</v>
@@ -6318,10 +6303,10 @@
         <v>464</v>
       </c>
       <c r="B52" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C52" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D52" t="s">
         <v>465</v>
@@ -6330,7 +6315,7 @@
         <v>466</v>
       </c>
       <c r="F52" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="G52" t="s">
         <v>458</v>
@@ -6339,7 +6324,7 @@
         <v>459</v>
       </c>
       <c r="I52" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="J52" t="s">
         <v>465</v>
@@ -6348,7 +6333,7 @@
         <v>466</v>
       </c>
       <c r="L52" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="M52" t="s">
         <v>467</v>
@@ -6359,7 +6344,7 @@
       <c r="P52"/>
       <c r="Q52"/>
       <c r="R52" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="S52" t="s">
         <v>469</v>
@@ -6373,10 +6358,10 @@
         <v>471</v>
       </c>
       <c r="B53" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C53" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D53" t="s">
         <v>472</v>
@@ -6385,7 +6370,7 @@
         <v>473</v>
       </c>
       <c r="F53" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="G53" t="s">
         <v>474</v>
@@ -6394,7 +6379,7 @@
         <v>475</v>
       </c>
       <c r="I53" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="J53" t="s">
         <v>472</v>
@@ -6403,7 +6388,7 @@
         <v>473</v>
       </c>
       <c r="L53" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="M53" t="s">
         <v>476</v>
@@ -6414,7 +6399,7 @@
       <c r="P53"/>
       <c r="Q53"/>
       <c r="R53" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="S53" t="s">
         <v>462</v>
@@ -6428,10 +6413,10 @@
         <v>478</v>
       </c>
       <c r="B54" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C54" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="D54" t="s">
         <v>479</v>
@@ -6440,7 +6425,7 @@
         <v>480</v>
       </c>
       <c r="F54" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="G54" t="s">
         <v>474</v>
@@ -6449,7 +6434,7 @@
         <v>475</v>
       </c>
       <c r="I54" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J54" t="s">
         <v>479</v>
@@ -6458,7 +6443,7 @@
         <v>480</v>
       </c>
       <c r="L54" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="M54" t="s">
         <v>476</v>
@@ -6469,7 +6454,7 @@
       <c r="P54"/>
       <c r="Q54"/>
       <c r="R54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="S54" t="s">
         <v>462</v>
@@ -6483,10 +6468,10 @@
         <v>481</v>
       </c>
       <c r="B55" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C55" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D55" t="s">
         <v>482</v>
@@ -6495,7 +6480,7 @@
         <v>483</v>
       </c>
       <c r="F55" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="G55" t="s">
         <v>474</v>
@@ -6504,7 +6489,7 @@
         <v>475</v>
       </c>
       <c r="I55" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="J55" t="s">
         <v>482</v>
@@ -6513,7 +6498,7 @@
         <v>483</v>
       </c>
       <c r="L55" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="M55" t="s">
         <v>476</v>
@@ -6524,7 +6509,7 @@
       <c r="P55"/>
       <c r="Q55"/>
       <c r="R55" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="S55" t="s">
         <v>462</v>
@@ -6538,10 +6523,10 @@
         <v>484</v>
       </c>
       <c r="B56" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C56" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="D56" t="s">
         <v>485</v>
@@ -6550,7 +6535,7 @@
         <v>486</v>
       </c>
       <c r="F56" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="G56" t="s">
         <v>474</v>
@@ -6559,7 +6544,7 @@
         <v>475</v>
       </c>
       <c r="I56" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="J56" t="s">
         <v>485</v>
@@ -6568,7 +6553,7 @@
         <v>486</v>
       </c>
       <c r="L56" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="M56" t="s">
         <v>476</v>
@@ -6579,7 +6564,7 @@
       <c r="P56"/>
       <c r="Q56"/>
       <c r="R56" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="S56" t="s">
         <v>462</v>
@@ -6593,10 +6578,10 @@
         <v>487</v>
       </c>
       <c r="B57" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C57" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D57" t="s">
         <v>488</v>
@@ -6605,7 +6590,7 @@
         <v>489</v>
       </c>
       <c r="F57" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="G57" t="s">
         <v>474</v>
@@ -6614,7 +6599,7 @@
         <v>475</v>
       </c>
       <c r="I57" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="J57" t="s">
         <v>488</v>
@@ -6623,7 +6608,7 @@
         <v>489</v>
       </c>
       <c r="L57" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="M57" t="s">
         <v>490</v>
@@ -6634,7 +6619,7 @@
       <c r="P57"/>
       <c r="Q57"/>
       <c r="R57" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="S57" t="s">
         <v>492</v>
@@ -6648,10 +6633,10 @@
         <v>494</v>
       </c>
       <c r="B58" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C58" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="D58" t="s">
         <v>495</v>
@@ -6660,7 +6645,7 @@
         <v>496</v>
       </c>
       <c r="F58" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="G58" t="s">
         <v>474</v>
@@ -6669,7 +6654,7 @@
         <v>475</v>
       </c>
       <c r="I58" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="J58" t="s">
         <v>495</v>
@@ -6678,7 +6663,7 @@
         <v>496</v>
       </c>
       <c r="L58" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="M58" t="s">
         <v>490</v>
@@ -6689,7 +6674,7 @@
       <c r="P58"/>
       <c r="Q58"/>
       <c r="R58" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="S58" t="s">
         <v>492</v>
@@ -6703,10 +6688,10 @@
         <v>497</v>
       </c>
       <c r="B59" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C59" t="s">
-        <v>879</v>
+        <v>499</v>
       </c>
       <c r="D59" t="s">
         <v>498</v>
@@ -6714,68 +6699,47 @@
       <c r="E59" t="s">
         <v>499</v>
       </c>
-      <c r="F59" t="s">
-        <v>961</v>
-      </c>
-      <c r="G59" t="s">
-        <v>474</v>
-      </c>
-      <c r="H59" t="s">
-        <v>475</v>
-      </c>
+      <c r="G59"/>
+      <c r="H59"/>
       <c r="I59" t="s">
-        <v>879</v>
+        <v>500</v>
       </c>
       <c r="J59" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K59" t="s">
-        <v>499</v>
-      </c>
-      <c r="L59" t="s">
-        <v>1068</v>
-      </c>
-      <c r="M59" t="s">
-        <v>490</v>
-      </c>
-      <c r="N59" t="s">
-        <v>491</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="M59"/>
+      <c r="N59"/>
       <c r="P59"/>
       <c r="Q59"/>
-      <c r="R59" t="s">
-        <v>1138</v>
-      </c>
-      <c r="S59" t="s">
-        <v>492</v>
-      </c>
-      <c r="T59" t="s">
-        <v>493</v>
-      </c>
+      <c r="S59"/>
+      <c r="T59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="C60" t="s">
+        <v>875</v>
+      </c>
+      <c r="D60" t="s">
         <v>502</v>
       </c>
-      <c r="D60" t="s">
-        <v>501</v>
-      </c>
       <c r="E60" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
       <c r="I60" t="s">
-        <v>503</v>
+        <v>875</v>
       </c>
       <c r="J60" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K60" t="s">
         <v>503</v>
@@ -6792,10 +6756,10 @@
         <v>504</v>
       </c>
       <c r="B61" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C61" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D61" t="s">
         <v>505</v>
@@ -6803,10 +6767,17 @@
       <c r="E61" t="s">
         <v>506</v>
       </c>
-      <c r="G61"/>
-      <c r="H61"/>
+      <c r="F61" t="s">
+        <v>957</v>
+      </c>
+      <c r="G61" t="s">
+        <v>507</v>
+      </c>
+      <c r="H61" t="s">
+        <v>508</v>
+      </c>
       <c r="I61" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="J61" t="s">
         <v>505</v>
@@ -6823,37 +6794,37 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B62" t="s">
         <v>816</v>
       </c>
       <c r="C62" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="D62" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E62" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F62" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="G62" t="s">
+        <v>512</v>
+      </c>
+      <c r="H62" t="s">
+        <v>513</v>
+      </c>
+      <c r="I62" t="s">
+        <v>877</v>
+      </c>
+      <c r="J62" t="s">
         <v>510</v>
       </c>
-      <c r="H62" t="s">
+      <c r="K62" t="s">
         <v>511</v>
-      </c>
-      <c r="I62" t="s">
-        <v>881</v>
-      </c>
-      <c r="J62" t="s">
-        <v>508</v>
-      </c>
-      <c r="K62" t="s">
-        <v>509</v>
       </c>
       <c r="M62"/>
       <c r="N62"/>
@@ -6864,40 +6835,47 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
       <c r="C63" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="D63" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E63" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F63" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="G63" t="s">
+        <v>517</v>
+      </c>
+      <c r="H63" t="s">
+        <v>518</v>
+      </c>
+      <c r="I63" t="s">
+        <v>878</v>
+      </c>
+      <c r="J63" t="s">
         <v>515</v>
       </c>
-      <c r="H63" t="s">
+      <c r="K63" t="s">
         <v>516</v>
       </c>
-      <c r="I63" t="s">
-        <v>882</v>
-      </c>
-      <c r="J63" t="s">
-        <v>513</v>
-      </c>
-      <c r="K63" t="s">
-        <v>514</v>
-      </c>
-      <c r="M63"/>
-      <c r="N63"/>
+      <c r="L63" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M63" t="s">
+        <v>519</v>
+      </c>
+      <c r="N63" t="s">
+        <v>520</v>
+      </c>
       <c r="P63"/>
       <c r="Q63"/>
       <c r="S63"/>
@@ -6905,149 +6883,149 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B64" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C64" t="s">
-        <v>883</v>
+        <v>523</v>
       </c>
       <c r="D64" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E64" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F64" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="G64" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H64" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="I64" t="s">
-        <v>883</v>
+        <v>523</v>
       </c>
       <c r="J64" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="K64" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L64" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="M64" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="N64" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="P64"/>
       <c r="Q64"/>
-      <c r="S64"/>
-      <c r="T64"/>
+      <c r="R64" t="s">
+        <v>1134</v>
+      </c>
+      <c r="S64" t="s">
+        <v>528</v>
+      </c>
+      <c r="T64" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B65" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C65" t="s">
-        <v>526</v>
+        <v>879</v>
       </c>
       <c r="D65" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E65" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F65" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="G65" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="H65" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="I65" t="s">
-        <v>526</v>
+        <v>879</v>
       </c>
       <c r="J65" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="K65" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="L65" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="M65" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="N65" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="P65"/>
       <c r="Q65"/>
-      <c r="R65" t="s">
-        <v>1139</v>
-      </c>
-      <c r="S65" t="s">
-        <v>531</v>
-      </c>
-      <c r="T65" t="s">
-        <v>532</v>
-      </c>
+      <c r="S65"/>
+      <c r="T65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C66" t="s">
-        <v>884</v>
+        <v>539</v>
       </c>
       <c r="D66" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E66" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F66" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="G66" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H66" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="I66" t="s">
-        <v>884</v>
+        <v>539</v>
       </c>
       <c r="J66" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="K66" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L66" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="M66" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="N66" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="P66"/>
       <c r="Q66"/>
@@ -7056,46 +7034,46 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="C67" t="s">
-        <v>542</v>
+        <v>880</v>
       </c>
       <c r="D67" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E67" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F67" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="G67" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="H67" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I67" t="s">
-        <v>542</v>
+        <v>880</v>
       </c>
       <c r="J67" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="K67" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L67" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="M67" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="N67" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="P67"/>
       <c r="Q67"/>
@@ -7104,149 +7082,149 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B68" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="C68" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D68" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E68" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F68" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G68" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H68" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="I68" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="J68" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="K68" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L68" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="M68" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="N68" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="P68"/>
       <c r="Q68"/>
-      <c r="S68"/>
-      <c r="T68"/>
+      <c r="R68" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S68" t="s">
+        <v>558</v>
+      </c>
+      <c r="T68" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="C69" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D69" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E69" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="F69" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="G69" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="H69" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="I69" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="J69" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="K69" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L69" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="M69" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="N69" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="P69"/>
       <c r="Q69"/>
-      <c r="R69" t="s">
-        <v>1140</v>
-      </c>
-      <c r="S69" t="s">
-        <v>561</v>
-      </c>
-      <c r="T69" t="s">
-        <v>562</v>
-      </c>
+      <c r="S69"/>
+      <c r="T69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B70" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C70" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D70" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E70" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F70" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="G70" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H70" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="I70" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="J70" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="K70" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="L70" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="M70" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N70" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="P70"/>
       <c r="Q70"/>
@@ -7255,226 +7233,212 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B71" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="C71" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D71" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E71" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F71" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="G71" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H71" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I71" t="s">
-        <v>888</v>
+        <v>1001</v>
       </c>
       <c r="J71" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K71" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="L71" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="M71" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="N71" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="P71"/>
       <c r="Q71"/>
-      <c r="S71"/>
-      <c r="T71"/>
+      <c r="R71" t="s">
+        <v>1136</v>
+      </c>
+      <c r="S71" t="s">
+        <v>583</v>
+      </c>
+      <c r="T71" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B72" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C72" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D72" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="E72" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="F72" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="G72" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="H72" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="I72" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="J72" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="K72" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="L72" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="M72" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N72" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="P72"/>
       <c r="Q72"/>
       <c r="R72" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="S72" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="T72" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="B73" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C73" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D73" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="E73" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="F73" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G73" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="H73" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="I73" t="s">
-        <v>1007</v>
+        <v>886</v>
       </c>
       <c r="J73" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="K73" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L73" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="M73" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="N73" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="P73"/>
       <c r="Q73"/>
       <c r="R73" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="S73" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="T73" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B74" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C74" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D74" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="E74" t="s">
-        <v>601</v>
-      </c>
-      <c r="F74" t="s">
-        <v>974</v>
-      </c>
-      <c r="G74" t="s">
-        <v>602</v>
-      </c>
-      <c r="H74" t="s">
-        <v>603</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="G74"/>
+      <c r="H74"/>
       <c r="I74" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="J74" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="K74" t="s">
-        <v>601</v>
-      </c>
-      <c r="L74" t="s">
-        <v>1079</v>
-      </c>
-      <c r="M74" t="s">
-        <v>604</v>
-      </c>
-      <c r="N74" t="s">
-        <v>605</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="M74"/>
+      <c r="N74"/>
       <c r="P74"/>
       <c r="Q74"/>
-      <c r="R74" t="s">
-        <v>1143</v>
-      </c>
-      <c r="S74" t="s">
-        <v>606</v>
-      </c>
-      <c r="T74" t="s">
-        <v>607</v>
-      </c>
+      <c r="S74"/>
+      <c r="T74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
         <v>608</v>
       </c>
       <c r="B75" t="s">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="C75" t="s">
-        <v>892</v>
+        <v>610</v>
       </c>
       <c r="D75" t="s">
         <v>609</v>
@@ -7482,10 +7446,17 @@
       <c r="E75" t="s">
         <v>610</v>
       </c>
-      <c r="G75"/>
-      <c r="H75"/>
+      <c r="F75" t="s">
+        <v>970</v>
+      </c>
+      <c r="G75" t="s">
+        <v>611</v>
+      </c>
+      <c r="H75" t="s">
+        <v>612</v>
+      </c>
       <c r="I75" t="s">
-        <v>892</v>
+        <v>610</v>
       </c>
       <c r="J75" t="s">
         <v>609</v>
@@ -7493,211 +7464,211 @@
       <c r="K75" t="s">
         <v>610</v>
       </c>
-      <c r="M75"/>
-      <c r="N75"/>
+      <c r="L75" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M75" t="s">
+        <v>613</v>
+      </c>
+      <c r="N75" t="s">
+        <v>614</v>
+      </c>
       <c r="P75"/>
       <c r="Q75"/>
-      <c r="S75"/>
-      <c r="T75"/>
+      <c r="R75" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S75" t="s">
+        <v>615</v>
+      </c>
+      <c r="T75" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B76" t="s">
-        <v>822</v>
+        <v>792</v>
       </c>
       <c r="C76" t="s">
-        <v>613</v>
+        <v>888</v>
       </c>
       <c r="D76" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E76" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="F76" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G76" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="H76" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="I76" t="s">
-        <v>613</v>
+        <v>888</v>
       </c>
       <c r="J76" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="K76" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L76" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="M76" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="N76" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="P76"/>
       <c r="Q76"/>
       <c r="R76" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="S76" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="T76" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B77" t="s">
-        <v>795</v>
+        <v>819</v>
       </c>
       <c r="C77" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D77" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="E77" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F77" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="G77" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="H77" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I77" t="s">
-        <v>893</v>
+        <v>1003</v>
       </c>
       <c r="J77" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="K77" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="L77" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="M77" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="N77" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="P77"/>
       <c r="Q77"/>
       <c r="R77" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="S77" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="T77" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="B78" t="s">
-        <v>823</v>
+        <v>792</v>
       </c>
       <c r="C78" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="D78" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="E78" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="F78" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G78" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="H78" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="I78" t="s">
-        <v>1008</v>
+        <v>890</v>
       </c>
       <c r="J78" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="K78" t="s">
-        <v>635</v>
-      </c>
-      <c r="L78" t="s">
-        <v>1082</v>
-      </c>
-      <c r="M78" t="s">
-        <v>636</v>
-      </c>
-      <c r="N78" t="s">
-        <v>637</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="M78"/>
+      <c r="N78"/>
       <c r="P78"/>
       <c r="Q78"/>
-      <c r="R78" t="s">
-        <v>1146</v>
-      </c>
-      <c r="S78" t="s">
-        <v>638</v>
-      </c>
-      <c r="T78" t="s">
-        <v>639</v>
-      </c>
+      <c r="S78"/>
+      <c r="T78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B79" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="C79" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D79" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E79" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F79" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="G79" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H79" t="s">
+        <v>647</v>
+      </c>
+      <c r="I79" t="s">
+        <v>891</v>
+      </c>
+      <c r="J79" t="s">
         <v>644</v>
       </c>
-      <c r="I79" t="s">
-        <v>895</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>645</v>
-      </c>
-      <c r="K79" t="s">
-        <v>642</v>
       </c>
       <c r="M79"/>
       <c r="N79"/>
@@ -7708,284 +7679,284 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B80" t="s">
-        <v>824</v>
+        <v>792</v>
       </c>
       <c r="C80" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="D80" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E80" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F80" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G80" t="s">
+        <v>651</v>
+      </c>
+      <c r="H80" t="s">
+        <v>652</v>
+      </c>
+      <c r="I80" t="s">
+        <v>892</v>
+      </c>
+      <c r="J80" t="s">
         <v>649</v>
       </c>
-      <c r="H80" t="s">
+      <c r="K80" t="s">
         <v>650</v>
       </c>
-      <c r="I80" t="s">
-        <v>896</v>
-      </c>
-      <c r="J80" t="s">
-        <v>647</v>
-      </c>
-      <c r="K80" t="s">
-        <v>648</v>
-      </c>
-      <c r="M80"/>
-      <c r="N80"/>
+      <c r="L80" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M80" t="s">
+        <v>653</v>
+      </c>
+      <c r="N80" t="s">
+        <v>654</v>
+      </c>
       <c r="P80"/>
       <c r="Q80"/>
-      <c r="S80"/>
-      <c r="T80"/>
+      <c r="R80" t="s">
+        <v>1142</v>
+      </c>
+      <c r="S80" t="s">
+        <v>655</v>
+      </c>
+      <c r="T80" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B81" t="s">
-        <v>795</v>
+        <v>821</v>
       </c>
       <c r="C81" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="D81" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E81" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="F81" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="G81" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="H81" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="I81" t="s">
-        <v>897</v>
+        <v>1004</v>
       </c>
       <c r="J81" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="K81" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="L81" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="M81" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="N81" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="P81"/>
       <c r="Q81"/>
       <c r="R81" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="S81" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="T81" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B82" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C82" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D82" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="E82" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="F82" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="G82" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="H82" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="I82" t="s">
-        <v>1009</v>
+        <v>894</v>
       </c>
       <c r="J82" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="K82" t="s">
-        <v>666</v>
-      </c>
-      <c r="L82" t="s">
-        <v>1084</v>
-      </c>
-      <c r="M82" t="s">
-        <v>667</v>
-      </c>
-      <c r="N82" t="s">
-        <v>668</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="M82"/>
+      <c r="N82"/>
       <c r="P82"/>
       <c r="Q82"/>
-      <c r="R82" t="s">
-        <v>1148</v>
-      </c>
-      <c r="S82" t="s">
-        <v>669</v>
-      </c>
-      <c r="T82" t="s">
-        <v>670</v>
-      </c>
+      <c r="S82"/>
+      <c r="T82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B83" t="s">
-        <v>826</v>
+        <v>792</v>
       </c>
       <c r="C83" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="D83" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E83" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F83" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="G83" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H83" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I83" t="s">
-        <v>899</v>
+        <v>1005</v>
       </c>
       <c r="J83" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="K83" t="s">
-        <v>673</v>
-      </c>
-      <c r="M83"/>
-      <c r="N83"/>
-      <c r="P83"/>
-      <c r="Q83"/>
+        <v>679</v>
+      </c>
+      <c r="L83" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M83" t="s">
+        <v>680</v>
+      </c>
+      <c r="N83" t="s">
+        <v>681</v>
+      </c>
+      <c r="O83" t="s">
+        <v>1089</v>
+      </c>
+      <c r="P83" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>683</v>
+      </c>
       <c r="S83"/>
       <c r="T83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B84" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C84" t="s">
-        <v>900</v>
+        <v>686</v>
       </c>
       <c r="D84" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="E84" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="F84" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="G84" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="H84" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="I84" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="J84" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="K84" t="s">
-        <v>682</v>
-      </c>
-      <c r="L84" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M84" t="s">
-        <v>683</v>
-      </c>
-      <c r="N84" t="s">
-        <v>684</v>
-      </c>
-      <c r="O84" t="s">
-        <v>1094</v>
-      </c>
-      <c r="P84" t="s">
-        <v>685</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>686</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="M84"/>
+      <c r="N84"/>
+      <c r="P84"/>
+      <c r="Q84"/>
       <c r="S84"/>
       <c r="T84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B85" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C85" t="s">
-        <v>689</v>
+        <v>896</v>
       </c>
       <c r="D85" t="s">
-        <v>688</v>
+        <v>180</v>
       </c>
       <c r="E85" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F85" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="G85" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="H85" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="I85" t="s">
-        <v>1011</v>
+        <v>500</v>
       </c>
       <c r="J85" t="s">
-        <v>692</v>
+        <v>500</v>
       </c>
       <c r="K85" t="s">
-        <v>693</v>
+        <v>500</v>
       </c>
       <c r="M85"/>
       <c r="N85"/>
@@ -7996,37 +7967,37 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B86" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C86" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D86" t="s">
-        <v>180</v>
+        <v>696</v>
       </c>
       <c r="E86" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F86" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="G86" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H86" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I86" t="s">
-        <v>503</v>
+        <v>1007</v>
       </c>
       <c r="J86" t="s">
-        <v>503</v>
+        <v>700</v>
       </c>
       <c r="K86" t="s">
-        <v>503</v>
+        <v>701</v>
       </c>
       <c r="M86"/>
       <c r="N86"/>
@@ -8037,126 +8008,119 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B87" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="C87" t="s">
-        <v>902</v>
+        <v>124</v>
       </c>
       <c r="D87" t="s">
-        <v>699</v>
+        <v>123</v>
       </c>
       <c r="E87" t="s">
-        <v>700</v>
+        <v>124</v>
       </c>
       <c r="F87" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="G87" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H87" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I87" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="J87" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="K87" t="s">
-        <v>704</v>
-      </c>
-      <c r="M87"/>
-      <c r="N87"/>
-      <c r="P87"/>
-      <c r="Q87"/>
+        <v>706</v>
+      </c>
+      <c r="L87" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M87" t="s">
+        <v>707</v>
+      </c>
+      <c r="N87" t="s">
+        <v>708</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P87" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>710</v>
+      </c>
       <c r="S87"/>
       <c r="T87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B88" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C88" t="s">
-        <v>124</v>
+        <v>898</v>
       </c>
       <c r="D88" t="s">
-        <v>123</v>
+        <v>712</v>
       </c>
       <c r="E88" t="s">
-        <v>124</v>
-      </c>
-      <c r="F88" t="s">
-        <v>987</v>
-      </c>
-      <c r="G88" t="s">
-        <v>706</v>
-      </c>
-      <c r="H88" t="s">
-        <v>707</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="G88"/>
+      <c r="H88"/>
       <c r="I88" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="J88" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="K88" t="s">
-        <v>709</v>
-      </c>
-      <c r="L88" t="s">
-        <v>1086</v>
-      </c>
-      <c r="M88" t="s">
-        <v>710</v>
-      </c>
-      <c r="N88" t="s">
-        <v>711</v>
-      </c>
-      <c r="O88" t="s">
-        <v>1095</v>
-      </c>
-      <c r="P88" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>713</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="M88"/>
+      <c r="N88"/>
+      <c r="P88"/>
+      <c r="Q88"/>
       <c r="S88"/>
       <c r="T88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B89" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C89" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="D89" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E89" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
       <c r="I89" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="J89" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="K89" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="M89"/>
       <c r="N89"/>
@@ -8167,30 +8131,37 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B90" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C90" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="D90" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E90" t="s">
-        <v>721</v>
-      </c>
-      <c r="G90"/>
-      <c r="H90"/>
+        <v>723</v>
+      </c>
+      <c r="F90" t="s">
+        <v>983</v>
+      </c>
+      <c r="G90" t="s">
+        <v>724</v>
+      </c>
+      <c r="H90" t="s">
+        <v>725</v>
+      </c>
       <c r="I90" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="J90" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="K90" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="M90"/>
       <c r="N90"/>
@@ -8201,38 +8172,24 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B91" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C91" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D91" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="E91" t="s">
-        <v>726</v>
-      </c>
-      <c r="F91" t="s">
-        <v>988</v>
-      </c>
-      <c r="G91" t="s">
-        <v>727</v>
-      </c>
-      <c r="H91" t="s">
-        <v>728</v>
-      </c>
-      <c r="I91" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J91" t="s">
-        <v>729</v>
-      </c>
-      <c r="K91" t="s">
         <v>730</v>
       </c>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="J91"/>
+      <c r="K91"/>
       <c r="M91"/>
       <c r="N91"/>
       <c r="P91"/>
@@ -8245,10 +8202,10 @@
         <v>731</v>
       </c>
       <c r="B92" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C92" t="s">
-        <v>906</v>
+        <v>733</v>
       </c>
       <c r="D92" t="s">
         <v>732</v>
@@ -8258,8 +8215,15 @@
       </c>
       <c r="G92"/>
       <c r="H92"/>
-      <c r="J92"/>
-      <c r="K92"/>
+      <c r="I92" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J92" t="s">
+        <v>734</v>
+      </c>
+      <c r="K92" t="s">
+        <v>735</v>
+      </c>
       <c r="M92"/>
       <c r="N92"/>
       <c r="P92"/>
@@ -8269,24 +8233,24 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B93" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C93" t="s">
-        <v>736</v>
+        <v>898</v>
       </c>
       <c r="D93" t="s">
-        <v>735</v>
+        <v>712</v>
       </c>
       <c r="E93" t="s">
-        <v>736</v>
+        <v>713</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
       <c r="I93" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="J93" t="s">
         <v>737</v>
@@ -8306,21 +8270,28 @@
         <v>739</v>
       </c>
       <c r="B94" t="s">
-        <v>799</v>
+        <v>823</v>
       </c>
       <c r="C94" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D94" t="s">
-        <v>715</v>
+        <v>740</v>
       </c>
       <c r="E94" t="s">
-        <v>716</v>
-      </c>
-      <c r="G94"/>
-      <c r="H94"/>
+        <v>741</v>
+      </c>
+      <c r="F94" t="s">
+        <v>984</v>
+      </c>
+      <c r="G94" t="s">
+        <v>742</v>
+      </c>
+      <c r="H94" t="s">
+        <v>743</v>
+      </c>
       <c r="I94" t="s">
-        <v>1018</v>
+        <v>902</v>
       </c>
       <c r="J94" t="s">
         <v>740</v>
@@ -8328,347 +8299,306 @@
       <c r="K94" t="s">
         <v>741</v>
       </c>
-      <c r="M94"/>
-      <c r="N94"/>
+      <c r="L94" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M94" t="s">
+        <v>744</v>
+      </c>
+      <c r="N94" t="s">
+        <v>745</v>
+      </c>
       <c r="P94"/>
       <c r="Q94"/>
-      <c r="S94"/>
-      <c r="T94"/>
+      <c r="R94" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S94" t="s">
+        <v>558</v>
+      </c>
+      <c r="T94" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B95" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C95" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="D95" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E95" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F95" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G95" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="H95" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I95" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="J95" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="K95" t="s">
-        <v>744</v>
-      </c>
-      <c r="L95" t="s">
-        <v>1087</v>
-      </c>
-      <c r="M95" t="s">
-        <v>747</v>
-      </c>
-      <c r="N95" t="s">
         <v>748</v>
       </c>
+      <c r="M95"/>
+      <c r="N95"/>
       <c r="P95"/>
       <c r="Q95"/>
-      <c r="R95" t="s">
-        <v>1140</v>
-      </c>
-      <c r="S95" t="s">
-        <v>561</v>
-      </c>
-      <c r="T95" t="s">
-        <v>562</v>
-      </c>
+      <c r="S95"/>
+      <c r="T95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B96" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C96" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D96" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E96" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F96" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G96" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H96" t="s">
-        <v>753</v>
-      </c>
-      <c r="I96" t="s">
-        <v>908</v>
-      </c>
-      <c r="J96" t="s">
-        <v>750</v>
-      </c>
-      <c r="K96" t="s">
-        <v>751</v>
-      </c>
-      <c r="M96"/>
-      <c r="N96"/>
+        <v>755</v>
+      </c>
+      <c r="J96"/>
+      <c r="K96"/>
+      <c r="L96" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M96" t="s">
+        <v>756</v>
+      </c>
+      <c r="N96" t="s">
+        <v>757</v>
+      </c>
       <c r="P96"/>
       <c r="Q96"/>
-      <c r="S96"/>
-      <c r="T96"/>
+      <c r="R96" t="s">
+        <v>1144</v>
+      </c>
+      <c r="S96" t="s">
+        <v>758</v>
+      </c>
+      <c r="T96" t="s">
+        <v>759</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="B97" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C97" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D97" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E97" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="F97" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G97" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="H97" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="M97" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="N97" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="P97"/>
       <c r="Q97"/>
       <c r="R97" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="S97" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="T97" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B98" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C98" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="D98" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E98" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="F98" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G98" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="H98" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="M98" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="N98" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="P98"/>
       <c r="Q98"/>
       <c r="R98" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="S98" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="T98" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B99" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C99" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D99" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E99" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="F99" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="G99" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="H99" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="M99" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="N99" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="P99"/>
       <c r="Q99"/>
       <c r="R99" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="S99" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="T99" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B100" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C100" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="D100" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="E100" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="F100" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="G100" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="H100" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="M100" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="N100" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="P100"/>
       <c r="Q100"/>
       <c r="R100" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="S100" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="T100" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>782</v>
-      </c>
-      <c r="B101" t="s">
-        <v>830</v>
-      </c>
-      <c r="C101" t="s">
-        <v>913</v>
-      </c>
-      <c r="D101" t="s">
-        <v>783</v>
-      </c>
-      <c r="E101" t="s">
-        <v>784</v>
-      </c>
-      <c r="F101" t="s">
-        <v>995</v>
-      </c>
-      <c r="G101" t="s">
-        <v>785</v>
-      </c>
-      <c r="H101" t="s">
-        <v>786</v>
-      </c>
-      <c r="J101"/>
-      <c r="K101"/>
-      <c r="L101" t="s">
-        <v>1091</v>
-      </c>
-      <c r="M101" t="s">
-        <v>787</v>
-      </c>
-      <c r="N101" t="s">
-        <v>788</v>
-      </c>
-      <c r="P101"/>
-      <c r="Q101"/>
-      <c r="R101" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S101" t="s">
-        <v>761</v>
-      </c>
-      <c r="T101" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
